--- a/NEWS_Daily_Report/output/history/NEWS_Daily_Report_History.xlsx
+++ b/NEWS_Daily_Report/output/history/NEWS_Daily_Report_History.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q381"/>
+  <dimension ref="A1:Q401"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21.42578125" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -24274,9 +24274,6 @@
           <t>Jindal Worldwide seeks approval for ₹650 Cr rights issue at AGM - scanx.trade</t>
         </is>
       </c>
-      <c r="O362" t="inlineStr"/>
-      <c r="P362" t="inlineStr"/>
-      <c r="Q362" t="inlineStr"/>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
@@ -24341,7 +24338,6 @@
           <t>IOL Chemicals &amp; Pharmaceuticals Clears Key Resolutions at 39th AGM - TipRanks</t>
         </is>
       </c>
-      <c r="Q363" t="inlineStr"/>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
@@ -24677,8 +24673,6 @@
           <t>Momentum Stocks: NELCO, Kotyark Industries, Khandwala Securities under pressure - Moneycontrol.com</t>
         </is>
       </c>
-      <c r="P368" t="inlineStr"/>
-      <c r="Q368" t="inlineStr"/>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
@@ -24733,9 +24727,6 @@
           <t>Onix Solar Energy Limited Files Revised Disclosure for Share Encumbrance Under SEBI Regulations - scanx.trade</t>
         </is>
       </c>
-      <c r="O369" t="inlineStr"/>
-      <c r="P369" t="inlineStr"/>
-      <c r="Q369" t="inlineStr"/>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
@@ -25145,7 +25136,6 @@
           <t>RBL Bank Ltd. Share Price: Price, Valuation, Sector View - Univest</t>
         </is>
       </c>
-      <c r="Q375" t="inlineStr"/>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
@@ -25200,9 +25190,6 @@
           <t>Syncom Formulations Share Price: fundamentals and peers - Univest</t>
         </is>
       </c>
-      <c r="O376" t="inlineStr"/>
-      <c r="P376" t="inlineStr"/>
-      <c r="Q376" t="inlineStr"/>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
@@ -25336,7 +25323,6 @@
           <t>Divgi TorqTransfer Stock Surges 13% As Q1 FY27 PAT Jumps 183% To ₹25.2 Cr - Trade Brains</t>
         </is>
       </c>
-      <c r="Q378" t="inlineStr"/>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
@@ -25544,6 +25530,1282 @@
           <t>What Coastal Corporation Limited's (NSE:COASTCORP) P/E Is Not Telling You - simplywall.st</t>
         </is>
       </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>2026-09-04 06:39:20 IST</t>
+        </is>
+      </c>
+      <c r="B382" t="n">
+        <v>1</v>
+      </c>
+      <c r="C382" t="inlineStr">
+        <is>
+          <t>BIRLAPREC.NS</t>
+        </is>
+      </c>
+      <c r="D382" t="inlineStr">
+        <is>
+          <t>Birla Precision Technologies Limited</t>
+        </is>
+      </c>
+      <c r="E382" t="n">
+        <v>42.77000045776367</v>
+      </c>
+      <c r="F382" t="n">
+        <v>51.66999816894531</v>
+      </c>
+      <c r="G382" t="n">
+        <v>42.75</v>
+      </c>
+      <c r="H382" t="n">
+        <v>51.66999816894531</v>
+      </c>
+      <c r="I382" t="n">
+        <v>43.11000061035156</v>
+      </c>
+      <c r="J382" t="n">
+        <v>51.66999816894531</v>
+      </c>
+      <c r="K382" t="n">
+        <v>984427</v>
+      </c>
+      <c r="L382" t="n">
+        <v>19.86</v>
+      </c>
+      <c r="M382" t="inlineStr">
+        <is>
+          <t>Birla Precision Technologies Ltd. (BIRLAPREC) Share Price Rises 10.68% Today - Univest</t>
+        </is>
+      </c>
+      <c r="N382" t="inlineStr">
+        <is>
+          <t>Birla Precision Technologies Ltd. (BIRLAPREC) Share Price Rises 10.68% Today - Univest</t>
+        </is>
+      </c>
+      <c r="O382" t="inlineStr"/>
+      <c r="P382" t="inlineStr"/>
+      <c r="Q382" t="inlineStr"/>
+    </row>
+    <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>2026-09-04 06:39:20 IST</t>
+        </is>
+      </c>
+      <c r="B383" t="n">
+        <v>2</v>
+      </c>
+      <c r="C383" t="inlineStr">
+        <is>
+          <t>HIKAL.NS</t>
+        </is>
+      </c>
+      <c r="D383" t="inlineStr">
+        <is>
+          <t>Hikal Limited</t>
+        </is>
+      </c>
+      <c r="E383" t="n">
+        <v>201.1499938964844</v>
+      </c>
+      <c r="F383" t="n">
+        <v>240.7200012207031</v>
+      </c>
+      <c r="G383" t="n">
+        <v>201.1499938964844</v>
+      </c>
+      <c r="H383" t="n">
+        <v>240.3600006103516</v>
+      </c>
+      <c r="I383" t="n">
+        <v>200.6000061035156</v>
+      </c>
+      <c r="J383" t="n">
+        <v>239.9600067138672</v>
+      </c>
+      <c r="K383" t="n">
+        <v>20195810</v>
+      </c>
+      <c r="L383" t="n">
+        <v>19.82</v>
+      </c>
+      <c r="M383" t="inlineStr">
+        <is>
+          <t>Don't Race Out To Buy Hikal Limited (NSE:HIKAL) Just Because It's Going Ex-Dividend - simplywall.st</t>
+        </is>
+      </c>
+      <c r="N383" t="inlineStr">
+        <is>
+          <t>Hikal files FY26 sustainability report with ESG metrics - scanx.trade</t>
+        </is>
+      </c>
+      <c r="O383" t="inlineStr">
+        <is>
+          <t>Hikal FY26 net loss of ₹49 crore on exceptional items - scanx.trade</t>
+        </is>
+      </c>
+      <c r="P383" t="inlineStr">
+        <is>
+          <t>Hikal Q1 Consolidated Net Loss Narrows to ₹7.4 Crore; Revenue At ₹403 Crore - Sahi</t>
+        </is>
+      </c>
+      <c r="Q383" t="inlineStr">
+        <is>
+          <t>Hikal Share Price Gains After Sameer Hiremath Named CMD - Univest</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>2026-09-04 06:39:20 IST</t>
+        </is>
+      </c>
+      <c r="B384" t="n">
+        <v>3</v>
+      </c>
+      <c r="C384" t="inlineStr">
+        <is>
+          <t>JINDWORLD.NS</t>
+        </is>
+      </c>
+      <c r="D384" t="inlineStr">
+        <is>
+          <t>Jindal Worldwide Limited</t>
+        </is>
+      </c>
+      <c r="E384" t="n">
+        <v>40.52000045776367</v>
+      </c>
+      <c r="F384" t="n">
+        <v>48.22000122070312</v>
+      </c>
+      <c r="G384" t="n">
+        <v>40.52000045776367</v>
+      </c>
+      <c r="H384" t="n">
+        <v>48.15000152587891</v>
+      </c>
+      <c r="I384" t="n">
+        <v>40.18999862670898</v>
+      </c>
+      <c r="J384" t="n">
+        <v>48.15000152587891</v>
+      </c>
+      <c r="K384" t="n">
+        <v>110819795</v>
+      </c>
+      <c r="L384" t="n">
+        <v>19.81</v>
+      </c>
+      <c r="M384" t="inlineStr">
+        <is>
+          <t>Most Active Equities on September 3, 2026 at 4:00 PM - hdfcsky.com</t>
+        </is>
+      </c>
+      <c r="N384" t="inlineStr">
+        <is>
+          <t>Most Active Equities on September 3, 2026 at 4:00 PM - hdfcsky.com</t>
+        </is>
+      </c>
+      <c r="O384" t="inlineStr">
+        <is>
+          <t>Jindal Worldwide seeks approval for ₹650 Cr rights issue at AGM - scanx.trade</t>
+        </is>
+      </c>
+      <c r="P384" t="inlineStr"/>
+      <c r="Q384" t="inlineStr"/>
+    </row>
+    <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>2026-09-04 06:39:20 IST</t>
+        </is>
+      </c>
+      <c r="B385" t="n">
+        <v>4</v>
+      </c>
+      <c r="C385" t="inlineStr">
+        <is>
+          <t>RAYMOND.NS</t>
+        </is>
+      </c>
+      <c r="D385" t="inlineStr">
+        <is>
+          <t>Raymond Limited</t>
+        </is>
+      </c>
+      <c r="E385" t="n">
+        <v>672.2000122070312</v>
+      </c>
+      <c r="F385" t="n">
+        <v>765</v>
+      </c>
+      <c r="G385" t="n">
+        <v>672.2000122070312</v>
+      </c>
+      <c r="H385" t="n">
+        <v>757.9000244140625</v>
+      </c>
+      <c r="I385" t="n">
+        <v>667.25</v>
+      </c>
+      <c r="J385" t="n">
+        <v>757.9000244140625</v>
+      </c>
+      <c r="K385" t="n">
+        <v>16593917</v>
+      </c>
+      <c r="L385" t="n">
+        <v>13.59</v>
+      </c>
+      <c r="M385" t="inlineStr">
+        <is>
+          <t>Why Raymond, Raymond Realty shares are surging today - Business Today</t>
+        </is>
+      </c>
+      <c r="N385" t="inlineStr">
+        <is>
+          <t>The technical leader behind a 2012 uranium discovery takes over F3's exploration - Stock Titan</t>
+        </is>
+      </c>
+      <c r="O385" t="inlineStr">
+        <is>
+          <t>Raymond James raises Ciena stock price target on supply visibility By Investing.com - Investing.com India</t>
+        </is>
+      </c>
+      <c r="P385" t="inlineStr">
+        <is>
+          <t>Buzzing stock: Raymond zooms 14% on huge volume, up 137% from 52-week low - Business Standard</t>
+        </is>
+      </c>
+      <c r="Q385" t="inlineStr">
+        <is>
+          <t>Defence re-rating buzz | Raymond share price hits 52-week high, logging over 14% intraday rise - Livemint</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>2026-09-04 06:39:20 IST</t>
+        </is>
+      </c>
+      <c r="B386" t="n">
+        <v>5</v>
+      </c>
+      <c r="C386" t="inlineStr">
+        <is>
+          <t>ALPINETEX.NS</t>
+        </is>
+      </c>
+      <c r="D386" t="inlineStr">
+        <is>
+          <t>Alpine Texworld Limited</t>
+        </is>
+      </c>
+      <c r="E386" t="n">
+        <v>51.11999893188477</v>
+      </c>
+      <c r="F386" t="n">
+        <v>59.34000015258789</v>
+      </c>
+      <c r="G386" t="n">
+        <v>51.11999893188477</v>
+      </c>
+      <c r="H386" t="n">
+        <v>57.16999816894531</v>
+      </c>
+      <c r="I386" t="n">
+        <v>51.09000015258789</v>
+      </c>
+      <c r="J386" t="n">
+        <v>57.16999816894531</v>
+      </c>
+      <c r="K386" t="n">
+        <v>1147753</v>
+      </c>
+      <c r="L386" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="M386" t="inlineStr">
+        <is>
+          <t>Alpine Texworld Share Price news and valuation - Univest</t>
+        </is>
+      </c>
+      <c r="N386" t="inlineStr">
+        <is>
+          <t>Alpine Texworld Share Price news and valuation - Univest</t>
+        </is>
+      </c>
+      <c r="O386" t="inlineStr"/>
+      <c r="P386" t="inlineStr"/>
+      <c r="Q386" t="inlineStr"/>
+    </row>
+    <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>2026-09-04 06:39:20 IST</t>
+        </is>
+      </c>
+      <c r="B387" t="n">
+        <v>6</v>
+      </c>
+      <c r="C387" t="inlineStr">
+        <is>
+          <t>BRIGADE.NS</t>
+        </is>
+      </c>
+      <c r="D387" t="inlineStr">
+        <is>
+          <t>Brigade Enterprises Limited</t>
+        </is>
+      </c>
+      <c r="E387" t="n">
+        <v>646.4500122070312</v>
+      </c>
+      <c r="F387" t="n">
+        <v>733</v>
+      </c>
+      <c r="G387" t="n">
+        <v>642.7000122070312</v>
+      </c>
+      <c r="H387" t="n">
+        <v>712.2999877929688</v>
+      </c>
+      <c r="I387" t="n">
+        <v>640</v>
+      </c>
+      <c r="J387" t="n">
+        <v>712.2999877929688</v>
+      </c>
+      <c r="K387" t="n">
+        <v>5390980</v>
+      </c>
+      <c r="L387" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="M387" t="inlineStr">
+        <is>
+          <t>Anant Raj shares jump 8% today: What’s driving the rally? - BusinessLine</t>
+        </is>
+      </c>
+      <c r="N387" t="inlineStr">
+        <is>
+          <t>Brigade Hotel Ventures seeks approval for ESOP and ₹64.22 crore RPT - scanx.trade</t>
+        </is>
+      </c>
+      <c r="O387" t="inlineStr">
+        <is>
+          <t>Brigade Enterprises Share Price update on Realty sector move - Univest</t>
+        </is>
+      </c>
+      <c r="P387" t="inlineStr">
+        <is>
+          <t>Brigade Hotel Ventures seeks approval for ESOP and ₹64.22 crore RPT - scanx.trade</t>
+        </is>
+      </c>
+      <c r="Q387" t="inlineStr">
+        <is>
+          <t>Brigade Enterprises shares: Analyst on when to exit the real estate counter - Business Today</t>
+        </is>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>2026-09-04 06:39:20 IST</t>
+        </is>
+      </c>
+      <c r="B388" t="n">
+        <v>7</v>
+      </c>
+      <c r="C388" t="inlineStr">
+        <is>
+          <t>SHUKRAPHAR.NS</t>
+        </is>
+      </c>
+      <c r="D388" t="inlineStr">
+        <is>
+          <t>Shukra Pharmaceuticals Limited</t>
+        </is>
+      </c>
+      <c r="E388" t="n">
+        <v>47.36999893188477</v>
+      </c>
+      <c r="F388" t="n">
+        <v>54.90000152587891</v>
+      </c>
+      <c r="G388" t="n">
+        <v>47.09999847412109</v>
+      </c>
+      <c r="H388" t="n">
+        <v>51.93000030517578</v>
+      </c>
+      <c r="I388" t="n">
+        <v>46.79000091552734</v>
+      </c>
+      <c r="J388" t="n">
+        <v>51.93000030517578</v>
+      </c>
+      <c r="K388" t="n">
+        <v>8949935</v>
+      </c>
+      <c r="L388" t="n">
+        <v>10.99</v>
+      </c>
+      <c r="M388" t="inlineStr">
+        <is>
+          <t>SHUKRAPHAR Stock Price and Chart — NSE:SHUKRAPHAR - TradingView</t>
+        </is>
+      </c>
+      <c r="N388" t="inlineStr">
+        <is>
+          <t>Shukra Pharmaceuticals Reschedules 33rd AGM and Revises Book Closure - TipRanks</t>
+        </is>
+      </c>
+      <c r="O388" t="inlineStr">
+        <is>
+          <t>Diluted shares outstanding of Shukra Pharmaceuticals Ltd. – NSE:SHUKRAPHAR - TradingView</t>
+        </is>
+      </c>
+      <c r="P388" t="inlineStr">
+        <is>
+          <t>Shukra Pharmaceuticals equity shares listed on NSE; trading begins August 14 - scanx.trade</t>
+        </is>
+      </c>
+      <c r="Q388" t="inlineStr">
+        <is>
+          <t>SHUKRA PHARMA Stock/Share price , NSE/BSE Forecast News and Live Quotes - Equitymaster</t>
+        </is>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>2026-09-04 06:39:20 IST</t>
+        </is>
+      </c>
+      <c r="B389" t="n">
+        <v>8</v>
+      </c>
+      <c r="C389" t="inlineStr">
+        <is>
+          <t>KIRIINDUS.NS</t>
+        </is>
+      </c>
+      <c r="D389" t="inlineStr">
+        <is>
+          <t>Kiri Industries Limited</t>
+        </is>
+      </c>
+      <c r="E389" t="n">
+        <v>527</v>
+      </c>
+      <c r="F389" t="n">
+        <v>591.2000122070312</v>
+      </c>
+      <c r="G389" t="n">
+        <v>527</v>
+      </c>
+      <c r="H389" t="n">
+        <v>578.9500122070312</v>
+      </c>
+      <c r="I389" t="n">
+        <v>523.6500244140625</v>
+      </c>
+      <c r="J389" t="n">
+        <v>578.9500122070312</v>
+      </c>
+      <c r="K389" t="n">
+        <v>7182969</v>
+      </c>
+      <c r="L389" t="n">
+        <v>10.56</v>
+      </c>
+      <c r="M389" t="inlineStr">
+        <is>
+          <t>Kiri Industries Share Price today: valuation and sector view - Univest</t>
+        </is>
+      </c>
+      <c r="N389" t="inlineStr">
+        <is>
+          <t>Kiri Industries Share Price today: valuation and sector view - Univest</t>
+        </is>
+      </c>
+      <c r="O389" t="inlineStr">
+        <is>
+          <t>Kiri Industries Share Price Today: Price Rise and Valuation - Univest</t>
+        </is>
+      </c>
+      <c r="P389" t="inlineStr"/>
+      <c r="Q389" t="inlineStr"/>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>2026-09-04 06:39:20 IST</t>
+        </is>
+      </c>
+      <c r="B390" t="n">
+        <v>9</v>
+      </c>
+      <c r="C390" t="inlineStr">
+        <is>
+          <t>MAKERSL.NS</t>
+        </is>
+      </c>
+      <c r="D390" t="inlineStr">
+        <is>
+          <t>Makers Laboratories Limited</t>
+        </is>
+      </c>
+      <c r="E390" t="n">
+        <v>188</v>
+      </c>
+      <c r="F390" t="n">
+        <v>200.9700012207031</v>
+      </c>
+      <c r="G390" t="n">
+        <v>182.0599975585938</v>
+      </c>
+      <c r="H390" t="n">
+        <v>200.7700042724609</v>
+      </c>
+      <c r="I390" t="n">
+        <v>182.6999969482422</v>
+      </c>
+      <c r="J390" t="n">
+        <v>200.7700042724609</v>
+      </c>
+      <c r="K390" t="n">
+        <v>9968</v>
+      </c>
+      <c r="L390" t="n">
+        <v>9.890000000000001</v>
+      </c>
+      <c r="M390" t="inlineStr">
+        <is>
+          <t>Makers Laboratories Ltd. (MAKERSL) Fundamental and Financial Data - Stocktwits</t>
+        </is>
+      </c>
+      <c r="N390" t="inlineStr">
+        <is>
+          <t>Makers Laboratories Ltd. (MAKERSL) Fundamental and Financial Data - Stocktwits</t>
+        </is>
+      </c>
+      <c r="O390" t="inlineStr">
+        <is>
+          <t>Makers Laboratories Q1 Results: Consolidated Net Profit Surges 244% YoY to ₹150.43 lacs - scanx.trade</t>
+        </is>
+      </c>
+      <c r="P390" t="inlineStr"/>
+      <c r="Q390" t="inlineStr"/>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>2026-09-04 06:39:20 IST</t>
+        </is>
+      </c>
+      <c r="B391" t="n">
+        <v>10</v>
+      </c>
+      <c r="C391" t="inlineStr">
+        <is>
+          <t>OAL.NS</t>
+        </is>
+      </c>
+      <c r="D391" t="inlineStr">
+        <is>
+          <t>Oriental Aromatics Limited</t>
+        </is>
+      </c>
+      <c r="E391" t="n">
+        <v>463.8999938964844</v>
+      </c>
+      <c r="F391" t="n">
+        <v>503.7000122070312</v>
+      </c>
+      <c r="G391" t="n">
+        <v>460</v>
+      </c>
+      <c r="H391" t="n">
+        <v>502.2999877929688</v>
+      </c>
+      <c r="I391" t="n">
+        <v>457.9500122070312</v>
+      </c>
+      <c r="J391" t="n">
+        <v>502.2999877929688</v>
+      </c>
+      <c r="K391" t="n">
+        <v>162215</v>
+      </c>
+      <c r="L391" t="n">
+        <v>9.68</v>
+      </c>
+      <c r="M391" t="inlineStr">
+        <is>
+          <t>Oriental Aromatics Share Price rises 8.72%; valuation view - Univest</t>
+        </is>
+      </c>
+      <c r="N391" t="inlineStr">
+        <is>
+          <t>Oriental Aromatics Share Price rises 8.72%; valuation view - Univest</t>
+        </is>
+      </c>
+      <c r="O391" t="inlineStr">
+        <is>
+          <t>Oriental Aromatics Share Price update: OAL gains 12.35% - Univest</t>
+        </is>
+      </c>
+      <c r="P391" t="inlineStr">
+        <is>
+          <t>Oriental Aromatics Share Price rises 9.72% on key metrics - Univest</t>
+        </is>
+      </c>
+      <c r="Q391" t="inlineStr">
+        <is>
+          <t>Ruger American (.17hmr) - For Sale, Used - Excellent Condition - Guns.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>2026-09-04 06:39:20 IST</t>
+        </is>
+      </c>
+      <c r="B392" t="n">
+        <v>11</v>
+      </c>
+      <c r="C392" t="inlineStr">
+        <is>
+          <t>ALEMBICLTD.NS</t>
+        </is>
+      </c>
+      <c r="D392" t="inlineStr">
+        <is>
+          <t>Alembic Limited</t>
+        </is>
+      </c>
+      <c r="E392" t="n">
+        <v>100.5199966430664</v>
+      </c>
+      <c r="F392" t="n">
+        <v>117.7200012207031</v>
+      </c>
+      <c r="G392" t="n">
+        <v>100.5199966430664</v>
+      </c>
+      <c r="H392" t="n">
+        <v>109.5100021362305</v>
+      </c>
+      <c r="I392" t="n">
+        <v>100.1399993896484</v>
+      </c>
+      <c r="J392" t="n">
+        <v>109.5100021362305</v>
+      </c>
+      <c r="K392" t="n">
+        <v>35036495</v>
+      </c>
+      <c r="L392" t="n">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="M392" t="inlineStr">
+        <is>
+          <t>Alembic Ltd. Share Price Today Up 12.67% on Price Action - Univest</t>
+        </is>
+      </c>
+      <c r="N392" t="inlineStr">
+        <is>
+          <t>Alembic Ltd. Share Price Today Up 12.67% on Price Action - Univest</t>
+        </is>
+      </c>
+      <c r="O392" t="inlineStr">
+        <is>
+          <t>ISSC Dips 0.92% to $20.51: Innovative Solutions and Support Holds Key Support Level - ATR Stop - vinanet.vn</t>
+        </is>
+      </c>
+      <c r="P392" t="inlineStr"/>
+      <c r="Q392" t="inlineStr"/>
+    </row>
+    <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>2026-09-04 06:39:20 IST</t>
+        </is>
+      </c>
+      <c r="B393" t="n">
+        <v>12</v>
+      </c>
+      <c r="C393" t="inlineStr">
+        <is>
+          <t>BFUTILITIE.NS</t>
+        </is>
+      </c>
+      <c r="D393" t="inlineStr">
+        <is>
+          <t>BF Utilities Limited</t>
+        </is>
+      </c>
+      <c r="E393" t="n">
+        <v>500.0499877929688</v>
+      </c>
+      <c r="F393" t="n">
+        <v>585.7999877929688</v>
+      </c>
+      <c r="G393" t="n">
+        <v>500.0499877929688</v>
+      </c>
+      <c r="H393" t="n">
+        <v>544</v>
+      </c>
+      <c r="I393" t="n">
+        <v>500.6499938964844</v>
+      </c>
+      <c r="J393" t="n">
+        <v>544</v>
+      </c>
+      <c r="K393" t="n">
+        <v>4460017</v>
+      </c>
+      <c r="L393" t="n">
+        <v>8.66</v>
+      </c>
+      <c r="M393" t="inlineStr">
+        <is>
+          <t>BF Utilities Ltd. Share Price Rises 11.72% on Valuation - Univest</t>
+        </is>
+      </c>
+      <c r="N393" t="inlineStr">
+        <is>
+          <t>BF Utilities Ltd. Share Price Rises 11.72% on Valuation - Univest</t>
+        </is>
+      </c>
+      <c r="O393" t="inlineStr">
+        <is>
+          <t>BF Utilities board notes BSE fine, promoter freeze for FY26 delay - scanx.trade</t>
+        </is>
+      </c>
+      <c r="P393" t="inlineStr">
+        <is>
+          <t>BF Utilities gets 3-month extension for 26th AGM from ROC Pune - scanx.trade</t>
+        </is>
+      </c>
+      <c r="Q393" t="inlineStr"/>
+    </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>2026-09-04 06:39:20 IST</t>
+        </is>
+      </c>
+      <c r="B394" t="n">
+        <v>13</v>
+      </c>
+      <c r="C394" t="inlineStr">
+        <is>
+          <t>MANALIPETC.NS</t>
+        </is>
+      </c>
+      <c r="D394" t="inlineStr">
+        <is>
+          <t>Manali Petrochemicals Limited</t>
+        </is>
+      </c>
+      <c r="E394" t="n">
+        <v>83</v>
+      </c>
+      <c r="F394" t="n">
+        <v>90.88999938964844</v>
+      </c>
+      <c r="G394" t="n">
+        <v>82</v>
+      </c>
+      <c r="H394" t="n">
+        <v>89.73000335693359</v>
+      </c>
+      <c r="I394" t="n">
+        <v>82.76000213623047</v>
+      </c>
+      <c r="J394" t="n">
+        <v>89.73000335693359</v>
+      </c>
+      <c r="K394" t="n">
+        <v>39146179</v>
+      </c>
+      <c r="L394" t="n">
+        <v>8.42</v>
+      </c>
+      <c r="M394" t="inlineStr">
+        <is>
+          <t>Manali Petrochemicals Share Price update: Rs 89.95, up 8.64% - Univest</t>
+        </is>
+      </c>
+      <c r="N394" t="inlineStr">
+        <is>
+          <t>Manali Petrochemicals Share Price update: Rs 89.95, up 8.64% - Univest</t>
+        </is>
+      </c>
+      <c r="O394" t="inlineStr"/>
+      <c r="P394" t="inlineStr"/>
+      <c r="Q394" t="inlineStr"/>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>2026-09-04 06:39:20 IST</t>
+        </is>
+      </c>
+      <c r="B395" t="n">
+        <v>14</v>
+      </c>
+      <c r="C395" t="inlineStr">
+        <is>
+          <t>BESTAGRO.NS</t>
+        </is>
+      </c>
+      <c r="D395" t="inlineStr">
+        <is>
+          <t>Best Agrolife Limited</t>
+        </is>
+      </c>
+      <c r="E395" t="n">
+        <v>20</v>
+      </c>
+      <c r="F395" t="n">
+        <v>20.70000076293945</v>
+      </c>
+      <c r="G395" t="n">
+        <v>19.86000061035156</v>
+      </c>
+      <c r="H395" t="n">
+        <v>20.34000015258789</v>
+      </c>
+      <c r="I395" t="n">
+        <v>18.81999969482422</v>
+      </c>
+      <c r="J395" t="n">
+        <v>20.34000015258789</v>
+      </c>
+      <c r="K395" t="n">
+        <v>4461640</v>
+      </c>
+      <c r="L395" t="n">
+        <v>8.08</v>
+      </c>
+      <c r="M395" t="inlineStr">
+        <is>
+          <t>Best Agrolife schedules No Deal Roadshow for Mumbai investors on August 10 - scanx.trade</t>
+        </is>
+      </c>
+      <c r="N395" t="inlineStr">
+        <is>
+          <t>Best Agrolife Publishes Newspaper Notice on Special Window - TipRanks</t>
+        </is>
+      </c>
+      <c r="O395" t="inlineStr">
+        <is>
+          <t>Best Agrolife Ltd. Share Price Declines: An 8.33% Drop Today - Univest</t>
+        </is>
+      </c>
+      <c r="P395" t="inlineStr">
+        <is>
+          <t>Best Agrolife schedules board meeting to approve FY26 annual report - scanx.trade</t>
+        </is>
+      </c>
+      <c r="Q395" t="inlineStr">
+        <is>
+          <t>Best Agrolife Publishes Newspaper Notice on Special Window - TipRanks</t>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>2026-09-04 06:39:20 IST</t>
+        </is>
+      </c>
+      <c r="B396" t="n">
+        <v>15</v>
+      </c>
+      <c r="C396" t="inlineStr">
+        <is>
+          <t>GOCLCORP.NS</t>
+        </is>
+      </c>
+      <c r="D396" t="inlineStr">
+        <is>
+          <t>GOCL Corporation Limited</t>
+        </is>
+      </c>
+      <c r="E396" t="n">
+        <v>417</v>
+      </c>
+      <c r="F396" t="n">
+        <v>448</v>
+      </c>
+      <c r="G396" t="n">
+        <v>412.8999938964844</v>
+      </c>
+      <c r="H396" t="n">
+        <v>422.9500122070312</v>
+      </c>
+      <c r="I396" t="n">
+        <v>391.7000122070312</v>
+      </c>
+      <c r="J396" t="n">
+        <v>422.9500122070312</v>
+      </c>
+      <c r="K396" t="n">
+        <v>6030677</v>
+      </c>
+      <c r="L396" t="n">
+        <v>7.98</v>
+      </c>
+      <c r="M396" t="inlineStr">
+        <is>
+          <t>1500% dividend stock alert! Check amount per share, record date, payment timeline and performance - TradingView</t>
+        </is>
+      </c>
+      <c r="N396" t="inlineStr">
+        <is>
+          <t>1500% dividend stock alert! Check amount per share, record date, payment timeline and performance - TradingView</t>
+        </is>
+      </c>
+      <c r="O396" t="inlineStr">
+        <is>
+          <t>GOCL Corporation Share Price Today: 8.63% Gain Analysis - Univest</t>
+        </is>
+      </c>
+      <c r="P396" t="inlineStr">
+        <is>
+          <t>EFX Q2 2026 Earnings: EPS Beat Drives 3.85% Stock Uptick - Earnings Volatility Report - vinanet.vn</t>
+        </is>
+      </c>
+      <c r="Q396" t="inlineStr"/>
+    </row>
+    <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>2026-09-04 06:39:20 IST</t>
+        </is>
+      </c>
+      <c r="B397" t="n">
+        <v>16</v>
+      </c>
+      <c r="C397" t="inlineStr">
+        <is>
+          <t>SMLMAH.NS</t>
+        </is>
+      </c>
+      <c r="D397" t="inlineStr">
+        <is>
+          <t>SML Mahindra Limited</t>
+        </is>
+      </c>
+      <c r="E397" t="n">
+        <v>5370</v>
+      </c>
+      <c r="F397" t="n">
+        <v>5790</v>
+      </c>
+      <c r="G397" t="n">
+        <v>5291</v>
+      </c>
+      <c r="H397" t="n">
+        <v>5726</v>
+      </c>
+      <c r="I397" t="n">
+        <v>5318.5</v>
+      </c>
+      <c r="J397" t="n">
+        <v>5726</v>
+      </c>
+      <c r="K397" t="n">
+        <v>246795</v>
+      </c>
+      <c r="L397" t="n">
+        <v>7.66</v>
+      </c>
+      <c r="M397" t="inlineStr">
+        <is>
+          <t>SML Mahindra February CV Production Increases To 1,679 Units From 1,442 Units YoY - scanx.trade</t>
+        </is>
+      </c>
+      <c r="N397" t="inlineStr">
+        <is>
+          <t>SML Mahindra Posts 40% Surge in August Vehicle Sales - TipRanks</t>
+        </is>
+      </c>
+      <c r="O397" t="inlineStr">
+        <is>
+          <t>SML Mahindra Posts 40% Surge in August Vehicle Sales - TipRanks</t>
+        </is>
+      </c>
+      <c r="P397" t="inlineStr"/>
+      <c r="Q397" t="inlineStr"/>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>2026-09-04 06:39:20 IST</t>
+        </is>
+      </c>
+      <c r="B398" t="n">
+        <v>17</v>
+      </c>
+      <c r="C398" t="inlineStr">
+        <is>
+          <t>CMPDI.NS</t>
+        </is>
+      </c>
+      <c r="D398" t="inlineStr">
+        <is>
+          <t>Central Mine Planning &amp; Design Institute Limited</t>
+        </is>
+      </c>
+      <c r="E398" t="n">
+        <v>223</v>
+      </c>
+      <c r="F398" t="n">
+        <v>241.8999938964844</v>
+      </c>
+      <c r="G398" t="n">
+        <v>223</v>
+      </c>
+      <c r="H398" t="n">
+        <v>239.6600036621094</v>
+      </c>
+      <c r="I398" t="n">
+        <v>222.9700012207031</v>
+      </c>
+      <c r="J398" t="n">
+        <v>239.6600036621094</v>
+      </c>
+      <c r="K398" t="n">
+        <v>6449983</v>
+      </c>
+      <c r="L398" t="n">
+        <v>7.49</v>
+      </c>
+      <c r="M398" t="inlineStr">
+        <is>
+          <t>CMPDI Dividend Alert: Coal India Subsidiary To Announce Q4 Result, Final Dividend On THIS Date - Goodreturns</t>
+        </is>
+      </c>
+      <c r="N398" t="inlineStr">
+        <is>
+          <t>Mahanadi Coalfields IPO: After Bharat Coking &amp; CMPDI, Coal India to offload 10% stake in third subsidiary - financialexpress.com</t>
+        </is>
+      </c>
+      <c r="O398" t="inlineStr">
+        <is>
+          <t>CMPDI IPO Lists at 7% Discount on NSE, BSE; Weak Demand Keeps Stock Under Pressure Despite Mild Recovery - Goodreturns</t>
+        </is>
+      </c>
+      <c r="P398" t="inlineStr">
+        <is>
+          <t>Mahanadi Coalfields IPO: After Bharat Coking &amp; CMPDI, Coal India to offload 10% stake in third subsidiary - financialexpress.com</t>
+        </is>
+      </c>
+      <c r="Q398" t="inlineStr"/>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>2026-09-04 06:39:20 IST</t>
+        </is>
+      </c>
+      <c r="B399" t="n">
+        <v>18</v>
+      </c>
+      <c r="C399" t="inlineStr">
+        <is>
+          <t>JYOTICNC.NS</t>
+        </is>
+      </c>
+      <c r="D399" t="inlineStr">
+        <is>
+          <t>Jyoti CNC Automation Limited</t>
+        </is>
+      </c>
+      <c r="E399" t="n">
+        <v>964.7000122070312</v>
+      </c>
+      <c r="F399" t="n">
+        <v>1039</v>
+      </c>
+      <c r="G399" t="n">
+        <v>964.2000122070312</v>
+      </c>
+      <c r="H399" t="n">
+        <v>1026.849975585938</v>
+      </c>
+      <c r="I399" t="n">
+        <v>955.6500244140625</v>
+      </c>
+      <c r="J399" t="n">
+        <v>1026.849975585938</v>
+      </c>
+      <c r="K399" t="n">
+        <v>3413377</v>
+      </c>
+      <c r="L399" t="n">
+        <v>7.45</v>
+      </c>
+      <c r="M399" t="inlineStr">
+        <is>
+          <t>Jyoti CNC Automation Limited Just Missed EPS By 10%: Here's What Analysts Think Will Happen Next - simplywall.st</t>
+        </is>
+      </c>
+      <c r="N399" t="inlineStr">
+        <is>
+          <t>Jyoti CNC Automation: Promoter Pledges 8.07% Stake - InvestyWise</t>
+        </is>
+      </c>
+      <c r="O399" t="inlineStr">
+        <is>
+          <t>Jyoti CNC Automation Ltd. Share Price: Price Action View - Univest</t>
+        </is>
+      </c>
+      <c r="P399" t="inlineStr">
+        <is>
+          <t>Jyoti CNC Automation: Promoter Pledges 8.07% Stake - InvestyWise</t>
+        </is>
+      </c>
+      <c r="Q399" t="inlineStr"/>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>2026-09-04 06:39:20 IST</t>
+        </is>
+      </c>
+      <c r="B400" t="n">
+        <v>19</v>
+      </c>
+      <c r="C400" t="inlineStr">
+        <is>
+          <t>DEEPINDS.NS</t>
+        </is>
+      </c>
+      <c r="D400" t="inlineStr">
+        <is>
+          <t>Deep Industries Limited</t>
+        </is>
+      </c>
+      <c r="E400" t="n">
+        <v>712</v>
+      </c>
+      <c r="F400" t="n">
+        <v>749</v>
+      </c>
+      <c r="G400" t="n">
+        <v>704.0999755859375</v>
+      </c>
+      <c r="H400" t="n">
+        <v>744.8499755859375</v>
+      </c>
+      <c r="I400" t="n">
+        <v>693.6500244140625</v>
+      </c>
+      <c r="J400" t="n">
+        <v>744.8499755859375</v>
+      </c>
+      <c r="K400" t="n">
+        <v>1577916</v>
+      </c>
+      <c r="L400" t="n">
+        <v>7.38</v>
+      </c>
+      <c r="M400" t="inlineStr">
+        <is>
+          <t>Deep Industries (DEEPINDS.NS) Gains Marginally as Stock Holds Above Key Support - ETF NAV Deviation - vinanet.vn</t>
+        </is>
+      </c>
+      <c r="N400" t="inlineStr">
+        <is>
+          <t>DEEPINDS Q2 2026 Earnings: Revenue Surges 54.6% YoY, EPS At ₹28.12 - Earnings Manipulation Risk - vinanet.vn</t>
+        </is>
+      </c>
+      <c r="O400" t="inlineStr">
+        <is>
+          <t>Why Investors Shouldn't Be Surprised By Deep Industries Limited's (NSE:DEEPINDS) P/S - simplywall.st</t>
+        </is>
+      </c>
+      <c r="P400" t="inlineStr">
+        <is>
+          <t>Deep Industries (DEEPINDS.NS) Faces Selling Pressure, Holds Near ₹508 Support Zone - Quality Factor - vinanet.vn</t>
+        </is>
+      </c>
+      <c r="Q400" t="inlineStr">
+        <is>
+          <t>Deep Industries Limited Receives NCLT Approval for Amalgamation with Wholly-Owned Subsidiary KECL - scanx.trade</t>
+        </is>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>2026-09-04 06:39:20 IST</t>
+        </is>
+      </c>
+      <c r="B401" t="n">
+        <v>20</v>
+      </c>
+      <c r="C401" t="inlineStr">
+        <is>
+          <t>MUKKA.NS</t>
+        </is>
+      </c>
+      <c r="D401" t="inlineStr">
+        <is>
+          <t>Mukka Proteins Limited</t>
+        </is>
+      </c>
+      <c r="E401" t="n">
+        <v>26.98999977111816</v>
+      </c>
+      <c r="F401" t="n">
+        <v>28.92000007629395</v>
+      </c>
+      <c r="G401" t="n">
+        <v>26.89999961853027</v>
+      </c>
+      <c r="H401" t="n">
+        <v>28.71999931335449</v>
+      </c>
+      <c r="I401" t="n">
+        <v>26.85000038146973</v>
+      </c>
+      <c r="J401" t="n">
+        <v>28.71999931335449</v>
+      </c>
+      <c r="K401" t="n">
+        <v>3369622</v>
+      </c>
+      <c r="L401" t="n">
+        <v>6.96</v>
+      </c>
+      <c r="M401" t="inlineStr">
+        <is>
+          <t>Mukka Proteins approves ₹13.19 crore stake in Shipwaves Online - scanx.trade</t>
+        </is>
+      </c>
+      <c r="N401" t="inlineStr">
+        <is>
+          <t>Mukka Proteins approves ₹13.19 crore stake in Shipwaves Online - scanx.trade</t>
+        </is>
+      </c>
+      <c r="O401" t="inlineStr"/>
+      <c r="P401" t="inlineStr"/>
+      <c r="Q401" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:Q361"/>
@@ -25557,7 +26819,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q681"/>
+  <dimension ref="A1:Q701"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -67236,9 +68498,6 @@
           <t>Here's Why Cords Cable Industries (NSE:CORDSCABLE) Has Caught The Eye Of Investors - simplywall.st</t>
         </is>
       </c>
-      <c r="O666" t="inlineStr"/>
-      <c r="P666" t="inlineStr"/>
-      <c r="Q666" t="inlineStr"/>
     </row>
     <row r="667">
       <c r="A667" t="inlineStr">
@@ -67298,8 +68557,6 @@
           <t>QPOWER Share Price rise with Rs 10,145.95 Cr market cap - Univest</t>
         </is>
       </c>
-      <c r="P667" t="inlineStr"/>
-      <c r="Q667" t="inlineStr"/>
     </row>
     <row r="668">
       <c r="A668" t="inlineStr">
@@ -67635,8 +68892,6 @@
           <t>Aarnav Fashions Ltd. Key Financial Ratios – Valuation, Profitability &amp; More - Value Research</t>
         </is>
       </c>
-      <c r="P672" t="inlineStr"/>
-      <c r="Q672" t="inlineStr"/>
     </row>
     <row r="673">
       <c r="A673" t="inlineStr">
@@ -67908,7 +69163,6 @@
           <t>Vedanta Iron And Steel,VEDL,visl Share Analysis,Vedanta Power,Buy ? Vedanta Iron &amp; Steel Target 2030 Fa Cup Final (Z7HpU44d6K) - Mshale</t>
         </is>
       </c>
-      <c r="Q676" t="inlineStr"/>
     </row>
     <row r="677">
       <c r="A677" t="inlineStr">
@@ -67973,7 +69227,6 @@
           <t>APL Apollo Tubes Completes Dispatch of 41st AGM Notice and FY26 Report - TipRanks</t>
         </is>
       </c>
-      <c r="Q677" t="inlineStr"/>
     </row>
     <row r="678">
       <c r="A678" t="inlineStr">
@@ -68097,9 +69350,6 @@
           <t>Oil Country Tubular shareholders approve FY26 accounts, director reappointments - scanx.trade</t>
         </is>
       </c>
-      <c r="O679" t="inlineStr"/>
-      <c r="P679" t="inlineStr"/>
-      <c r="Q679" t="inlineStr"/>
     </row>
     <row r="680">
       <c r="A680" t="inlineStr">
@@ -68236,6 +69486,1322 @@
       <c r="Q681" t="inlineStr">
         <is>
           <t>DJ Mediaprint &amp; Logistics Raises ₹11.97 Crore Through Warrant Conversion - scanx.trade</t>
+        </is>
+      </c>
+    </row>
+    <row r="682">
+      <c r="A682" t="inlineStr">
+        <is>
+          <t>2026-09-04 06:39:20 IST</t>
+        </is>
+      </c>
+      <c r="B682" t="n">
+        <v>1</v>
+      </c>
+      <c r="C682" t="inlineStr">
+        <is>
+          <t>SALASAR.NS</t>
+        </is>
+      </c>
+      <c r="D682" t="inlineStr">
+        <is>
+          <t>Salasar Techno Engineering Limited</t>
+        </is>
+      </c>
+      <c r="E682" t="n">
+        <v>5.639999866485596</v>
+      </c>
+      <c r="F682" t="n">
+        <v>5.690000057220459</v>
+      </c>
+      <c r="G682" t="n">
+        <v>4.730000019073486</v>
+      </c>
+      <c r="H682" t="n">
+        <v>5.079999923706055</v>
+      </c>
+      <c r="I682" t="n">
+        <v>5.650000095367432</v>
+      </c>
+      <c r="J682" t="n">
+        <v>5.079999923706055</v>
+      </c>
+      <c r="K682" t="n">
+        <v>40156990</v>
+      </c>
+      <c r="L682" t="n">
+        <v>-10.09</v>
+      </c>
+      <c r="M682" t="inlineStr">
+        <is>
+          <t>Salasar Techno Engineering Ltd. Stock News - valueresearchonline.com</t>
+        </is>
+      </c>
+      <c r="N682" t="inlineStr">
+        <is>
+          <t>Salasar Techno Engineering Ltd. Stock News - valueresearchonline.com</t>
+        </is>
+      </c>
+      <c r="O682" t="inlineStr"/>
+      <c r="P682" t="inlineStr"/>
+      <c r="Q682" t="inlineStr"/>
+    </row>
+    <row r="683">
+      <c r="A683" t="inlineStr">
+        <is>
+          <t>2026-09-04 06:39:20 IST</t>
+        </is>
+      </c>
+      <c r="B683" t="n">
+        <v>2</v>
+      </c>
+      <c r="C683" t="inlineStr">
+        <is>
+          <t>INDBANK.NS</t>
+        </is>
+      </c>
+      <c r="D683" t="inlineStr">
+        <is>
+          <t>Indbank Merchant Banking Services Limited</t>
+        </is>
+      </c>
+      <c r="E683" t="n">
+        <v>30.79999923706055</v>
+      </c>
+      <c r="F683" t="n">
+        <v>31.10000038146973</v>
+      </c>
+      <c r="G683" t="n">
+        <v>28.10000038146973</v>
+      </c>
+      <c r="H683" t="n">
+        <v>28.70999908447266</v>
+      </c>
+      <c r="I683" t="n">
+        <v>31.10000038146973</v>
+      </c>
+      <c r="J683" t="n">
+        <v>28.70999908447266</v>
+      </c>
+      <c r="K683" t="n">
+        <v>719248</v>
+      </c>
+      <c r="L683" t="n">
+        <v>-7.68</v>
+      </c>
+      <c r="M683" t="inlineStr">
+        <is>
+          <t>Indbank Merchant Banking sets Sep 17 as AGM record date - scanx.trade</t>
+        </is>
+      </c>
+      <c r="N683" t="inlineStr">
+        <is>
+          <t>Indbank Merchant Banking sets Sep 17 as AGM record date - scanx.trade</t>
+        </is>
+      </c>
+      <c r="O683" t="inlineStr">
+        <is>
+          <t>Indbank Merchant Banking Services Share Price Rises 14.75% - Univest</t>
+        </is>
+      </c>
+      <c r="P683" t="inlineStr">
+        <is>
+          <t>Kestrel Group Ltd. (KG) Slips 0.82% to $7.45 as Shares Test Key Support Zone - Hull Moving Average - vinanet.vn</t>
+        </is>
+      </c>
+      <c r="Q683" t="inlineStr">
+        <is>
+          <t>Indbank Merchant Banking: ਮੁਨਾਫੇ ਵਿੱਚ ਆਈ ਗਿਰਾਵਟ, ਕੰਪਨੀ ਨੇ ਡਿਵੀਡੈਂਡ ਦੇਣ ਤੋਂ ਕੀਤਾ ਇਨਕਾਰ - Whalesbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="684">
+      <c r="A684" t="inlineStr">
+        <is>
+          <t>2026-09-04 06:39:20 IST</t>
+        </is>
+      </c>
+      <c r="B684" t="n">
+        <v>3</v>
+      </c>
+      <c r="C684" t="inlineStr">
+        <is>
+          <t>RTNINDIA.NS</t>
+        </is>
+      </c>
+      <c r="D684" t="inlineStr">
+        <is>
+          <t>RattanIndia Enterprises Limited</t>
+        </is>
+      </c>
+      <c r="E684" t="n">
+        <v>29.65999984741211</v>
+      </c>
+      <c r="F684" t="n">
+        <v>29.89999961853027</v>
+      </c>
+      <c r="G684" t="n">
+        <v>27.20999908447266</v>
+      </c>
+      <c r="H684" t="n">
+        <v>27.43000030517578</v>
+      </c>
+      <c r="I684" t="n">
+        <v>29.59000015258789</v>
+      </c>
+      <c r="J684" t="n">
+        <v>27.43000030517578</v>
+      </c>
+      <c r="K684" t="n">
+        <v>7638164</v>
+      </c>
+      <c r="L684" t="n">
+        <v>-7.3</v>
+      </c>
+      <c r="M684" t="inlineStr">
+        <is>
+          <t>RattanIndia Enterprises Reprices 54 Lakh Stock Options Under ESOP 2022 - scanx.trade</t>
+        </is>
+      </c>
+      <c r="N684" t="inlineStr">
+        <is>
+          <t>RattanIndia Enterprises Sees Positive Momentum: RTNINDIA Rises 2.53%, Eyes Key Resistance - PCR Extreme - vinanet.vn</t>
+        </is>
+      </c>
+      <c r="O684" t="inlineStr">
+        <is>
+          <t>CMPDI Stock Price and Chart — NSE:CMPDI - TradingView</t>
+        </is>
+      </c>
+      <c r="P684" t="inlineStr">
+        <is>
+          <t>RTNINDIA.NS Q2 2026 Earnings: Revenue Growth Continues Despite Narrowing Losses - Earnings Risk Report - vinanet.vn</t>
+        </is>
+      </c>
+      <c r="Q684" t="inlineStr">
+        <is>
+          <t>RattanIndia Enterprises Reports Q3FY26 Loss of ₹1,620M Amid Investment Valuation Impact - scanx.trade</t>
+        </is>
+      </c>
+    </row>
+    <row r="685">
+      <c r="A685" t="inlineStr">
+        <is>
+          <t>2026-09-04 06:39:20 IST</t>
+        </is>
+      </c>
+      <c r="B685" t="n">
+        <v>4</v>
+      </c>
+      <c r="C685" t="inlineStr">
+        <is>
+          <t>SURAJEST.NS</t>
+        </is>
+      </c>
+      <c r="D685" t="inlineStr">
+        <is>
+          <t>Suraj Estate Developers Limited</t>
+        </is>
+      </c>
+      <c r="E685" t="n">
+        <v>187.4400024414062</v>
+      </c>
+      <c r="F685" t="n">
+        <v>187.4400024414062</v>
+      </c>
+      <c r="G685" t="n">
+        <v>175.2100067138672</v>
+      </c>
+      <c r="H685" t="n">
+        <v>177.8000030517578</v>
+      </c>
+      <c r="I685" t="n">
+        <v>189.9400024414062</v>
+      </c>
+      <c r="J685" t="n">
+        <v>177.8000030517578</v>
+      </c>
+      <c r="K685" t="n">
+        <v>336506</v>
+      </c>
+      <c r="L685" t="n">
+        <v>-6.39</v>
+      </c>
+      <c r="M685" t="inlineStr">
+        <is>
+          <t>Suraj Estate promoters hold 3.33 crore shares, no encumbrance in FY26 - scanx.trade</t>
+        </is>
+      </c>
+      <c r="N685" t="inlineStr">
+        <is>
+          <t>Suraj Estate promoters hold 3.33 crore shares, no encumbrance in FY26 - scanx.trade</t>
+        </is>
+      </c>
+      <c r="O685" t="inlineStr">
+        <is>
+          <t>Suraj Estate Developers Limited Begins FY27 on Strong Footing, Driven by Robust Sales Momentum - Business Standard</t>
+        </is>
+      </c>
+      <c r="P685" t="inlineStr"/>
+      <c r="Q685" t="inlineStr"/>
+    </row>
+    <row r="686">
+      <c r="A686" t="inlineStr">
+        <is>
+          <t>2026-09-04 06:39:20 IST</t>
+        </is>
+      </c>
+      <c r="B686" t="n">
+        <v>5</v>
+      </c>
+      <c r="C686" t="inlineStr">
+        <is>
+          <t>GSS.NS</t>
+        </is>
+      </c>
+      <c r="D686" t="inlineStr">
+        <is>
+          <t>GSS Infotech Limited</t>
+        </is>
+      </c>
+      <c r="E686" t="n">
+        <v>12.28999996185303</v>
+      </c>
+      <c r="F686" t="n">
+        <v>12.4399995803833</v>
+      </c>
+      <c r="G686" t="n">
+        <v>10.76000022888184</v>
+      </c>
+      <c r="H686" t="n">
+        <v>11.15999984741211</v>
+      </c>
+      <c r="I686" t="n">
+        <v>11.82999992370605</v>
+      </c>
+      <c r="J686" t="n">
+        <v>11.15999984741211</v>
+      </c>
+      <c r="K686" t="n">
+        <v>192431</v>
+      </c>
+      <c r="L686" t="n">
+        <v>-5.66</v>
+      </c>
+      <c r="M686" t="inlineStr">
+        <is>
+          <t>GSS Infotech sets Sep 18 record date for AGM e-voting - scanx.trade</t>
+        </is>
+      </c>
+      <c r="N686" t="inlineStr">
+        <is>
+          <t>BCAL Diagnostics Issues Section 249D Notice to Genetic Signatures for Board Restructuring - Kalkine Media</t>
+        </is>
+      </c>
+      <c r="O686" t="inlineStr">
+        <is>
+          <t>Genetic Signatures (ASX:GSS): Board Challenge Emerges Amid Shareholding Queries - Kalkine</t>
+        </is>
+      </c>
+      <c r="P686" t="inlineStr">
+        <is>
+          <t>GSS Infotech Submits Q4FY26 Depositories Compliance Certificate to Exchanges - scanx.trade</t>
+        </is>
+      </c>
+      <c r="Q686" t="inlineStr">
+        <is>
+          <t>BCAL Diagnostics Issues Section 249D Notice to Genetic Signatures for Board Restructuring - Kalkine Media</t>
+        </is>
+      </c>
+    </row>
+    <row r="687">
+      <c r="A687" t="inlineStr">
+        <is>
+          <t>2026-09-04 06:39:20 IST</t>
+        </is>
+      </c>
+      <c r="B687" t="n">
+        <v>6</v>
+      </c>
+      <c r="C687" t="inlineStr">
+        <is>
+          <t>ANNU.NS</t>
+        </is>
+      </c>
+      <c r="D687" t="inlineStr">
+        <is>
+          <t>Annu Projects Limited</t>
+        </is>
+      </c>
+      <c r="E687" t="n">
+        <v>74.80000305175781</v>
+      </c>
+      <c r="F687" t="n">
+        <v>74.80000305175781</v>
+      </c>
+      <c r="G687" t="n">
+        <v>71.81999969482422</v>
+      </c>
+      <c r="H687" t="n">
+        <v>71.81999969482422</v>
+      </c>
+      <c r="I687" t="n">
+        <v>75.59999847412109</v>
+      </c>
+      <c r="J687" t="n">
+        <v>71.81999969482422</v>
+      </c>
+      <c r="K687" t="n">
+        <v>2067647</v>
+      </c>
+      <c r="L687" t="n">
+        <v>-5</v>
+      </c>
+      <c r="M687" t="inlineStr">
+        <is>
+          <t>Weak Start! Annu Projects shares list at 27% discount to IPO price - The Economic Times</t>
+        </is>
+      </c>
+      <c r="N687" t="inlineStr">
+        <is>
+          <t>Share Price Today - Annu Projects Ltd. Stock Price Live NSE/BSE - hdfcsky.com</t>
+        </is>
+      </c>
+      <c r="O687" t="inlineStr">
+        <is>
+          <t>Weak market debut: Annu Projects shares list at over 27% discount to its IPO price - Moneycontrol.com</t>
+        </is>
+      </c>
+      <c r="P687" t="inlineStr">
+        <is>
+          <t>Annu Projects Limited Stock (ANNU) - Quote NSE India S.E. - marketscreener.com</t>
+        </is>
+      </c>
+      <c r="Q687" t="inlineStr">
+        <is>
+          <t>Share Price Today - Annu Projects Ltd. Stock Price Live NSE/BSE - hdfcsky.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="688">
+      <c r="A688" t="inlineStr">
+        <is>
+          <t>2026-09-04 06:39:20 IST</t>
+        </is>
+      </c>
+      <c r="B688" t="n">
+        <v>7</v>
+      </c>
+      <c r="C688" t="inlineStr">
+        <is>
+          <t>GAUDIUMIVF.NS</t>
+        </is>
+      </c>
+      <c r="D688" t="inlineStr">
+        <is>
+          <t>Gaudium IVF and Women Health Limited</t>
+        </is>
+      </c>
+      <c r="E688" t="n">
+        <v>123.4000015258789</v>
+      </c>
+      <c r="F688" t="n">
+        <v>124.8399963378906</v>
+      </c>
+      <c r="G688" t="n">
+        <v>117.2300033569336</v>
+      </c>
+      <c r="H688" t="n">
+        <v>117.2399978637695</v>
+      </c>
+      <c r="I688" t="n">
+        <v>123.4000015258789</v>
+      </c>
+      <c r="J688" t="n">
+        <v>117.2399978637695</v>
+      </c>
+      <c r="K688" t="n">
+        <v>217233</v>
+      </c>
+      <c r="L688" t="n">
+        <v>-4.99</v>
+      </c>
+      <c r="M688" t="inlineStr">
+        <is>
+          <t>Gaudium IVF and Women Health Limited’s Initial Public Offer of Equity Shares to open on February 20, 2026 - english.metrovaartha.com</t>
+        </is>
+      </c>
+      <c r="N688" t="inlineStr">
+        <is>
+          <t>GAUDIUMIVF.NS Mar 2026 Earnings: Strong Revenue Base Amid Weak Comparative Benchmarks - Earnings Preview - vinanet.vn</t>
+        </is>
+      </c>
+      <c r="O688" t="inlineStr">
+        <is>
+          <t>GAUDIUMIVF.NS Mar 2026 Earnings: Revenue at ₹22.17 Crore, EPS of ₹1.06; Stock Declines 2% - Profit Recovery Report - vinanet.vn</t>
+        </is>
+      </c>
+      <c r="P688" t="inlineStr">
+        <is>
+          <t>GAUDIUMIVF Mar 2026 Earnings: Solid EPS of ₹1.06 on Revenue of ₹22.17 Cr; Stock Down 2.66% - Earnings Weakness Phase - vinanet.vn</t>
+        </is>
+      </c>
+      <c r="Q688" t="inlineStr">
+        <is>
+          <t>Gaudium IVF Gains 2%: Navigating Support and Resistance Levels at ₹108.72 - Trading Ideas - vinanet.vn</t>
+        </is>
+      </c>
+    </row>
+    <row r="689">
+      <c r="A689" t="inlineStr">
+        <is>
+          <t>2026-09-04 06:39:20 IST</t>
+        </is>
+      </c>
+      <c r="B689" t="n">
+        <v>8</v>
+      </c>
+      <c r="C689" t="inlineStr">
+        <is>
+          <t>MODISONLTD.NS</t>
+        </is>
+      </c>
+      <c r="D689" t="inlineStr">
+        <is>
+          <t>MODISON LIMITED</t>
+        </is>
+      </c>
+      <c r="E689" t="n">
+        <v>520.6500244140625</v>
+      </c>
+      <c r="F689" t="n">
+        <v>544.9000244140625</v>
+      </c>
+      <c r="G689" t="n">
+        <v>494.6499938964844</v>
+      </c>
+      <c r="H689" t="n">
+        <v>494.6499938964844</v>
+      </c>
+      <c r="I689" t="n">
+        <v>520.6500244140625</v>
+      </c>
+      <c r="J689" t="n">
+        <v>494.6499938964844</v>
+      </c>
+      <c r="K689" t="n">
+        <v>583790</v>
+      </c>
+      <c r="L689" t="n">
+        <v>-4.99</v>
+      </c>
+      <c r="M689" t="inlineStr">
+        <is>
+          <t>Modison's (NSE:MODISONLTD) Promising Earnings May Rest On Soft Foundations - simplywall.st</t>
+        </is>
+      </c>
+      <c r="N689" t="inlineStr">
+        <is>
+          <t>Modison Limited (MODISONLTD.NS) Slips 4% as Shares Approach Key Support Level - Zero Gamma Level - vinanet.vn</t>
+        </is>
+      </c>
+      <c r="O689" t="inlineStr">
+        <is>
+          <t>Here's Why Modison (NSE:MODISONLTD) Has Caught The Eye Of Investors - simplywall.st</t>
+        </is>
+      </c>
+      <c r="P689" t="inlineStr">
+        <is>
+          <t>Modison Limited Schedules Board Meeting on May 22, 2026 to Consider Q4FY26 Audited Results and Dividend - scanx.trade</t>
+        </is>
+      </c>
+      <c r="Q689" t="inlineStr">
+        <is>
+          <t>Modison Limited (MODISONLTD.NS) Slips 4% as Shares Approach Key Support Level - Zero Gamma Level - vinanet.vn</t>
+        </is>
+      </c>
+    </row>
+    <row r="690">
+      <c r="A690" t="inlineStr">
+        <is>
+          <t>2026-09-04 06:39:20 IST</t>
+        </is>
+      </c>
+      <c r="B690" t="n">
+        <v>9</v>
+      </c>
+      <c r="C690" t="inlineStr">
+        <is>
+          <t>RNBDENIMS.NS</t>
+        </is>
+      </c>
+      <c r="D690" t="inlineStr">
+        <is>
+          <t>R&amp;B Denims Limited</t>
+        </is>
+      </c>
+      <c r="E690" t="n">
+        <v>11.93000030517578</v>
+      </c>
+      <c r="F690" t="n">
+        <v>11.93000030517578</v>
+      </c>
+      <c r="G690" t="n">
+        <v>10.8100004196167</v>
+      </c>
+      <c r="H690" t="n">
+        <v>10.8100004196167</v>
+      </c>
+      <c r="I690" t="n">
+        <v>11.36999988555908</v>
+      </c>
+      <c r="J690" t="n">
+        <v>10.8100004196167</v>
+      </c>
+      <c r="K690" t="n">
+        <v>3089346</v>
+      </c>
+      <c r="L690" t="n">
+        <v>-4.93</v>
+      </c>
+      <c r="M690" t="inlineStr">
+        <is>
+          <t>RNBDENIMS Stock Price and Chart — NSE:RNBDENIMS - TradingView</t>
+        </is>
+      </c>
+      <c r="N690" t="inlineStr">
+        <is>
+          <t>R&amp;B Denims (RNBDENIMS.NS) Slips 1.5%: Testing Key Support Near ₹9.89 - Defined Outcome ETF - vinanet.vn</t>
+        </is>
+      </c>
+      <c r="O690" t="inlineStr">
+        <is>
+          <t>R&amp;B Denims Schedules EGM for March 13 to Approve Stock Split and Corporate Actions - scanx.trade</t>
+        </is>
+      </c>
+      <c r="P690" t="inlineStr">
+        <is>
+          <t>R&amp;B Denims (RNBDENIMS.NS) Slips 1.5%: Testing Key Support Near ₹9.89 - Defined Outcome ETF - vinanet.vn</t>
+        </is>
+      </c>
+      <c r="Q690" t="inlineStr">
+        <is>
+          <t>R&amp;B Denims Limited (RNBDENIMS.NS) Faces Selling Pressure, Holds Above Key Support - Institutional Sentiment - vinanet.vn</t>
+        </is>
+      </c>
+    </row>
+    <row r="691">
+      <c r="A691" t="inlineStr">
+        <is>
+          <t>2026-09-04 06:39:20 IST</t>
+        </is>
+      </c>
+      <c r="B691" t="n">
+        <v>10</v>
+      </c>
+      <c r="C691" t="inlineStr">
+        <is>
+          <t>RAJTV.NS</t>
+        </is>
+      </c>
+      <c r="D691" t="inlineStr">
+        <is>
+          <t>Raj Television Network Limited</t>
+        </is>
+      </c>
+      <c r="E691" t="n">
+        <v>8.489999771118164</v>
+      </c>
+      <c r="F691" t="n">
+        <v>9.25</v>
+      </c>
+      <c r="G691" t="n">
+        <v>8.489999771118164</v>
+      </c>
+      <c r="H691" t="n">
+        <v>8.489999771118164</v>
+      </c>
+      <c r="I691" t="n">
+        <v>8.930000305175781</v>
+      </c>
+      <c r="J691" t="n">
+        <v>8.489999771118164</v>
+      </c>
+      <c r="K691" t="n">
+        <v>96443</v>
+      </c>
+      <c r="L691" t="n">
+        <v>-4.93</v>
+      </c>
+      <c r="M691" t="inlineStr">
+        <is>
+          <t>Raj Television Network schedules 32nd AGM for September 30 - scanx.trade</t>
+        </is>
+      </c>
+      <c r="N691" t="inlineStr">
+        <is>
+          <t>Raj Television Network schedules 32nd AGM for September 30 - scanx.trade</t>
+        </is>
+      </c>
+      <c r="O691" t="inlineStr">
+        <is>
+          <t>Raj TV Network Q1 Results: Unaudited financials for June quarter filed - scanx.trade</t>
+        </is>
+      </c>
+      <c r="P691" t="inlineStr">
+        <is>
+          <t>Raj TV Network Q1 Results: Net Loss Widens To ₹10.08 Million - scanx.trade</t>
+        </is>
+      </c>
+      <c r="Q691" t="inlineStr">
+        <is>
+          <t>Kiran Kumar Jain M sells 5.87 lakh Raj TV Network shares via open market - scanx.trade</t>
+        </is>
+      </c>
+    </row>
+    <row r="692">
+      <c r="A692" t="inlineStr">
+        <is>
+          <t>2026-09-04 06:39:20 IST</t>
+        </is>
+      </c>
+      <c r="B692" t="n">
+        <v>11</v>
+      </c>
+      <c r="C692" t="inlineStr">
+        <is>
+          <t>GANGAFORGE.NS</t>
+        </is>
+      </c>
+      <c r="D692" t="inlineStr">
+        <is>
+          <t>Ganga Forging Limited</t>
+        </is>
+      </c>
+      <c r="E692" t="n">
+        <v>1.820000052452087</v>
+      </c>
+      <c r="F692" t="n">
+        <v>1.850000023841858</v>
+      </c>
+      <c r="G692" t="n">
+        <v>1.759999990463257</v>
+      </c>
+      <c r="H692" t="n">
+        <v>1.759999990463257</v>
+      </c>
+      <c r="I692" t="n">
+        <v>1.850000023841858</v>
+      </c>
+      <c r="J692" t="n">
+        <v>1.759999990463257</v>
+      </c>
+      <c r="K692" t="n">
+        <v>7489255</v>
+      </c>
+      <c r="L692" t="n">
+        <v>-4.86</v>
+      </c>
+      <c r="M692" t="inlineStr">
+        <is>
+          <t>Adamas (ADAM) Q2 2026 Results: EPS Exceeds Its Estimate on the Day; Trading Response: Shares Finish 0.80% Down at the Close - Product Revenue Analysis - vinanet.vn</t>
+        </is>
+      </c>
+      <c r="N692" t="inlineStr">
+        <is>
+          <t>Adamas (ADAM) Q2 2026 Results: EPS Exceeds Its Estimate on the Day; Trading Response: Shares Finish 0.80% Down at the Close - Product Revenue Analysis - vinanet.vn</t>
+        </is>
+      </c>
+      <c r="O692" t="inlineStr"/>
+      <c r="P692" t="inlineStr"/>
+      <c r="Q692" t="inlineStr"/>
+    </row>
+    <row r="693">
+      <c r="A693" t="inlineStr">
+        <is>
+          <t>2026-09-04 06:39:20 IST</t>
+        </is>
+      </c>
+      <c r="B693" t="n">
+        <v>12</v>
+      </c>
+      <c r="C693" t="inlineStr">
+        <is>
+          <t>HTEL.NS</t>
+        </is>
+      </c>
+      <c r="D693" t="inlineStr">
+        <is>
+          <t>Hy-Tech Engineers Limited</t>
+        </is>
+      </c>
+      <c r="E693" t="n">
+        <v>77</v>
+      </c>
+      <c r="F693" t="n">
+        <v>77.90000152587891</v>
+      </c>
+      <c r="G693" t="n">
+        <v>74.62999725341797</v>
+      </c>
+      <c r="H693" t="n">
+        <v>74.73000335693359</v>
+      </c>
+      <c r="I693" t="n">
+        <v>78.55000305175781</v>
+      </c>
+      <c r="J693" t="n">
+        <v>74.73000335693359</v>
+      </c>
+      <c r="K693" t="n">
+        <v>2290257</v>
+      </c>
+      <c r="L693" t="n">
+        <v>-4.86</v>
+      </c>
+      <c r="M693" t="inlineStr">
+        <is>
+          <t>Share Price Today - Hy-Tech Engineers Ltd. Stock Price Live NSE/BSE - hdfcsky.com</t>
+        </is>
+      </c>
+      <c r="N693" t="inlineStr">
+        <is>
+          <t>Share Price Today - Hy-Tech Engineers Ltd. Stock Price Live NSE/BSE - hdfcsky.com</t>
+        </is>
+      </c>
+      <c r="O693" t="inlineStr">
+        <is>
+          <t>Hy-Tech Engineers Limited Financial Statements – NSE:HTEL - TradingView</t>
+        </is>
+      </c>
+      <c r="P693" t="inlineStr">
+        <is>
+          <t>Hy-Tech Engineers Ltd Share Price Today,, HTEL Share Price NSE, BSE - Business Today</t>
+        </is>
+      </c>
+      <c r="Q693" t="inlineStr">
+        <is>
+          <t>HTEL: Static price chart | Hy-Tech Engineers Limited | INE0LEG01024 - marketscreener.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="694">
+      <c r="A694" t="inlineStr">
+        <is>
+          <t>2026-09-04 06:39:20 IST</t>
+        </is>
+      </c>
+      <c r="B694" t="n">
+        <v>13</v>
+      </c>
+      <c r="C694" t="inlineStr">
+        <is>
+          <t>EMPOWER.NS</t>
+        </is>
+      </c>
+      <c r="D694" t="inlineStr">
+        <is>
+          <t>Empower India Limited</t>
+        </is>
+      </c>
+      <c r="E694" t="n">
+        <v>1.820000052452087</v>
+      </c>
+      <c r="F694" t="n">
+        <v>1.820000052452087</v>
+      </c>
+      <c r="G694" t="n">
+        <v>1.820000052452087</v>
+      </c>
+      <c r="H694" t="n">
+        <v>1.820000052452087</v>
+      </c>
+      <c r="I694" t="n">
+        <v>1.909999966621399</v>
+      </c>
+      <c r="J694" t="n">
+        <v>1.820000052452087</v>
+      </c>
+      <c r="K694" t="n">
+        <v>4402278</v>
+      </c>
+      <c r="L694" t="n">
+        <v>-4.71</v>
+      </c>
+      <c r="M694" t="inlineStr">
+        <is>
+          <t>NET Power Closes Acquisition of 123 MW Power Generation Rights From EMPower; Shares Rise - marketscreener.com</t>
+        </is>
+      </c>
+      <c r="N694" t="inlineStr">
+        <is>
+          <t>NET Power Closes Acquisition of 123 MW Power Generation Rights From EMPower; Shares Rise - marketscreener.com</t>
+        </is>
+      </c>
+      <c r="O694" t="inlineStr">
+        <is>
+          <t>A West Texas project plans 10 gas engines totaling 123 megawatts - Stock Titan</t>
+        </is>
+      </c>
+      <c r="P694" t="inlineStr"/>
+      <c r="Q694" t="inlineStr"/>
+    </row>
+    <row r="695">
+      <c r="A695" t="inlineStr">
+        <is>
+          <t>2026-09-04 06:39:20 IST</t>
+        </is>
+      </c>
+      <c r="B695" t="n">
+        <v>14</v>
+      </c>
+      <c r="C695" t="inlineStr">
+        <is>
+          <t>ARIHANTSUP.NS</t>
+        </is>
+      </c>
+      <c r="D695" t="inlineStr">
+        <is>
+          <t>Arihant Superstructures Limited</t>
+        </is>
+      </c>
+      <c r="E695" t="n">
+        <v>249</v>
+      </c>
+      <c r="F695" t="n">
+        <v>249</v>
+      </c>
+      <c r="G695" t="n">
+        <v>231.3500061035156</v>
+      </c>
+      <c r="H695" t="n">
+        <v>236.1499938964844</v>
+      </c>
+      <c r="I695" t="n">
+        <v>247.75</v>
+      </c>
+      <c r="J695" t="n">
+        <v>236.1499938964844</v>
+      </c>
+      <c r="K695" t="n">
+        <v>30352</v>
+      </c>
+      <c r="L695" t="n">
+        <v>-4.68</v>
+      </c>
+      <c r="M695" t="inlineStr">
+        <is>
+          <t>Arihant Superstructures Ltd (ARIHANTSUP.NS) Q2 2026 Earnings: Robust Revenue Growth Amid Strong Affordable Housing Demand - Guidance Revision Trend - vinanet.vn</t>
+        </is>
+      </c>
+      <c r="N695" t="inlineStr">
+        <is>
+          <t>Arihant Superstructures Q2 2026 Earnings: Revenue Growth of 10.45% Amid Modest Market Reaction - Analyst Earnings Estimate - vinanet.vn</t>
+        </is>
+      </c>
+      <c r="O695" t="inlineStr">
+        <is>
+          <t>The Compensation For Arihant Superstructures Limited's (NSE:ARIHANTSUP) CEO Looks Deserved And Here's Why - simplywall.st</t>
+        </is>
+      </c>
+      <c r="P695" t="inlineStr">
+        <is>
+          <t>ARIHANTSUP Q2 2026 Earnings: Revenue Growth of 10.45% and Strong EPS of ₹10.65 Highlight Steady Performance - Capex Guidance - vinanet.vn</t>
+        </is>
+      </c>
+      <c r="Q695" t="inlineStr">
+        <is>
+          <t>Arihant Superstructures Shows Mild Upside as Price Hovers Near Support, Resistance in Focus - Call Resistance - vinanet.vn</t>
+        </is>
+      </c>
+    </row>
+    <row r="696">
+      <c r="A696" t="inlineStr">
+        <is>
+          <t>2026-09-04 06:39:20 IST</t>
+        </is>
+      </c>
+      <c r="B696" t="n">
+        <v>15</v>
+      </c>
+      <c r="C696" t="inlineStr">
+        <is>
+          <t>OMNI.NS</t>
+        </is>
+      </c>
+      <c r="D696" t="inlineStr">
+        <is>
+          <t>Omnitech Engineering Limited</t>
+        </is>
+      </c>
+      <c r="E696" t="n">
+        <v>546.7000122070312</v>
+      </c>
+      <c r="F696" t="n">
+        <v>546.7000122070312</v>
+      </c>
+      <c r="G696" t="n">
+        <v>514.0999755859375</v>
+      </c>
+      <c r="H696" t="n">
+        <v>519.25</v>
+      </c>
+      <c r="I696" t="n">
+        <v>543.1500244140625</v>
+      </c>
+      <c r="J696" t="n">
+        <v>519.25</v>
+      </c>
+      <c r="K696" t="n">
+        <v>648674</v>
+      </c>
+      <c r="L696" t="n">
+        <v>-4.4</v>
+      </c>
+      <c r="M696" t="inlineStr">
+        <is>
+          <t>7,329,803 Equity Shares of Omnitech Engineering Limited are subject to a Lock-Up Agreement Ending on 2-SEP-2026. - marketscreener.com</t>
+        </is>
+      </c>
+      <c r="N696" t="inlineStr">
+        <is>
+          <t>7,329,803 Equity Shares of Omnitech Engineering Limited are subject to a Lock-Up Agreement Ending on 2-SEP-2026. - marketscreener.com</t>
+        </is>
+      </c>
+      <c r="O696" t="inlineStr">
+        <is>
+          <t>Omni Bridgeway (ASX:OBL) Shares Reflect Valuation Strain Despite Profitable FY 2026 - webull.com</t>
+        </is>
+      </c>
+      <c r="P696" t="inlineStr">
+        <is>
+          <t>Omni-Lite Industries Stock Falls 2.18%: Aerospace Demand Risks and Growth Uncertainty Pressure TSXV:OML Sentiment - kalkine.ca</t>
+        </is>
+      </c>
+      <c r="Q696" t="inlineStr">
+        <is>
+          <t>Kotak Diversified Equity All Cap Omni FoF Regular-Growth (₹ 10.02) - NAV, Reviews &amp; asset allocation - The Economic Times</t>
+        </is>
+      </c>
+    </row>
+    <row r="697">
+      <c r="A697" t="inlineStr">
+        <is>
+          <t>2026-09-04 06:39:20 IST</t>
+        </is>
+      </c>
+      <c r="B697" t="n">
+        <v>16</v>
+      </c>
+      <c r="C697" t="inlineStr">
+        <is>
+          <t>DEEPAKFERT.NS</t>
+        </is>
+      </c>
+      <c r="D697" t="inlineStr">
+        <is>
+          <t>Deepak Fertilizers and Petrochemicals Corporation Limited</t>
+        </is>
+      </c>
+      <c r="E697" t="n">
+        <v>1385</v>
+      </c>
+      <c r="F697" t="n">
+        <v>1411</v>
+      </c>
+      <c r="G697" t="n">
+        <v>1351.099975585938</v>
+      </c>
+      <c r="H697" t="n">
+        <v>1355.900024414062</v>
+      </c>
+      <c r="I697" t="n">
+        <v>1416.699951171875</v>
+      </c>
+      <c r="J697" t="n">
+        <v>1355.900024414062</v>
+      </c>
+      <c r="K697" t="n">
+        <v>816334</v>
+      </c>
+      <c r="L697" t="n">
+        <v>-4.29</v>
+      </c>
+      <c r="M697" t="inlineStr">
+        <is>
+          <t>News by CNBC TV18 on TradingView, 2026-08-23 — cnbctv:8653cb759094b:0 - TradingView</t>
+        </is>
+      </c>
+      <c r="N697" t="inlineStr">
+        <is>
+          <t>News by CNBC TV18 on TradingView, 2026-08-23 — cnbctv:8653cb759094b:0 - TradingView</t>
+        </is>
+      </c>
+      <c r="O697" t="inlineStr"/>
+      <c r="P697" t="inlineStr"/>
+      <c r="Q697" t="inlineStr"/>
+    </row>
+    <row r="698">
+      <c r="A698" t="inlineStr">
+        <is>
+          <t>2026-09-04 06:39:20 IST</t>
+        </is>
+      </c>
+      <c r="B698" t="n">
+        <v>17</v>
+      </c>
+      <c r="C698" t="inlineStr">
+        <is>
+          <t>OMAXE.NS</t>
+        </is>
+      </c>
+      <c r="D698" t="inlineStr">
+        <is>
+          <t>Omaxe Limited</t>
+        </is>
+      </c>
+      <c r="E698" t="n">
+        <v>133.5800018310547</v>
+      </c>
+      <c r="F698" t="n">
+        <v>135.8000030517578</v>
+      </c>
+      <c r="G698" t="n">
+        <v>125.5100021362305</v>
+      </c>
+      <c r="H698" t="n">
+        <v>127.2900009155273</v>
+      </c>
+      <c r="I698" t="n">
+        <v>132.6699981689453</v>
+      </c>
+      <c r="J698" t="n">
+        <v>127.2900009155273</v>
+      </c>
+      <c r="K698" t="n">
+        <v>5734642</v>
+      </c>
+      <c r="L698" t="n">
+        <v>-4.06</v>
+      </c>
+      <c r="M698" t="inlineStr">
+        <is>
+          <t>SAT dismisses Omaxe appeal against SEBI order over financial statement irregularities - Moneycontrol.com</t>
+        </is>
+      </c>
+      <c r="N698" t="inlineStr">
+        <is>
+          <t>Omaxe files FY26 BRSR report highlighting zero safety incidents - scanx.trade</t>
+        </is>
+      </c>
+      <c r="O698" t="inlineStr">
+        <is>
+          <t>Omaxe files FY26 BRSR report highlighting zero safety incidents - scanx.trade</t>
+        </is>
+      </c>
+      <c r="P698" t="inlineStr">
+        <is>
+          <t>Omaxe Ltd. Share Price Rise: Price Action and Fundamentals - Univest</t>
+        </is>
+      </c>
+      <c r="Q698" t="inlineStr">
+        <is>
+          <t>Omaxe clarifies on share price movement - Business Upturn</t>
+        </is>
+      </c>
+    </row>
+    <row r="699">
+      <c r="A699" t="inlineStr">
+        <is>
+          <t>2026-09-04 06:39:20 IST</t>
+        </is>
+      </c>
+      <c r="B699" t="n">
+        <v>18</v>
+      </c>
+      <c r="C699" t="inlineStr">
+        <is>
+          <t>ROSSARI.NS</t>
+        </is>
+      </c>
+      <c r="D699" t="inlineStr">
+        <is>
+          <t>Rossari Biotech Limited</t>
+        </is>
+      </c>
+      <c r="E699" t="n">
+        <v>479.5</v>
+      </c>
+      <c r="F699" t="n">
+        <v>482.3500061035156</v>
+      </c>
+      <c r="G699" t="n">
+        <v>451.3999938964844</v>
+      </c>
+      <c r="H699" t="n">
+        <v>457</v>
+      </c>
+      <c r="I699" t="n">
+        <v>476.2000122070312</v>
+      </c>
+      <c r="J699" t="n">
+        <v>457</v>
+      </c>
+      <c r="K699" t="n">
+        <v>342764</v>
+      </c>
+      <c r="L699" t="n">
+        <v>-4.03</v>
+      </c>
+      <c r="M699" t="inlineStr">
+        <is>
+          <t>Sudarshan Chemical Industries vs Rossari Biotech: Which Specialty Stock - Univest</t>
+        </is>
+      </c>
+      <c r="N699" t="inlineStr">
+        <is>
+          <t>Specialty Chemicals Stocks To Buy: Navin Fluorine, Rossari Among Nirmal Bang's Eight Picks With Up To 37% Upside — Full List Inside - NDTV Profit</t>
+        </is>
+      </c>
+      <c r="O699" t="inlineStr">
+        <is>
+          <t>Specialty Chemicals Stocks To Buy: Navin Fluorine, Rossari Among Nirmal Bang's Eight Picks With Up To 37% Upside — Full List Inside - NDTV Profit</t>
+        </is>
+      </c>
+      <c r="P699" t="inlineStr"/>
+      <c r="Q699" t="inlineStr"/>
+    </row>
+    <row r="700">
+      <c r="A700" t="inlineStr">
+        <is>
+          <t>2026-09-04 06:39:20 IST</t>
+        </is>
+      </c>
+      <c r="B700" t="n">
+        <v>19</v>
+      </c>
+      <c r="C700" t="inlineStr">
+        <is>
+          <t>CORDSCABLE.NS</t>
+        </is>
+      </c>
+      <c r="D700" t="inlineStr">
+        <is>
+          <t>Cords Cable Industries Limited</t>
+        </is>
+      </c>
+      <c r="E700" t="n">
+        <v>323.8999938964844</v>
+      </c>
+      <c r="F700" t="n">
+        <v>323.8999938964844</v>
+      </c>
+      <c r="G700" t="n">
+        <v>287.2000122070312</v>
+      </c>
+      <c r="H700" t="n">
+        <v>302.8999938964844</v>
+      </c>
+      <c r="I700" t="n">
+        <v>315.5</v>
+      </c>
+      <c r="J700" t="n">
+        <v>302.8999938964844</v>
+      </c>
+      <c r="K700" t="n">
+        <v>259816</v>
+      </c>
+      <c r="L700" t="n">
+        <v>-3.99</v>
+      </c>
+      <c r="M700" t="inlineStr">
+        <is>
+          <t>Cords Cable Industries Share Price Gain With Valuation View - Univest</t>
+        </is>
+      </c>
+      <c r="N700" t="inlineStr">
+        <is>
+          <t>Cords Cable Industries Share Price Gain With Valuation View - Univest</t>
+        </is>
+      </c>
+      <c r="O700" t="inlineStr">
+        <is>
+          <t>Here's Why Cords Cable Industries (NSE:CORDSCABLE) Has Caught The Eye Of Investors - simplywall.st</t>
+        </is>
+      </c>
+      <c r="P700" t="inlineStr">
+        <is>
+          <t>Cords Cable Flags Routine Newspaper Disclosure to Exchange - TipRanks</t>
+        </is>
+      </c>
+      <c r="Q700" t="inlineStr"/>
+    </row>
+    <row r="701">
+      <c r="A701" t="inlineStr">
+        <is>
+          <t>2026-09-04 06:39:20 IST</t>
+        </is>
+      </c>
+      <c r="B701" t="n">
+        <v>20</v>
+      </c>
+      <c r="C701" t="inlineStr">
+        <is>
+          <t>OLAELEC.NS</t>
+        </is>
+      </c>
+      <c r="D701" t="inlineStr">
+        <is>
+          <t>Ola Electric Mobility Limited</t>
+        </is>
+      </c>
+      <c r="E701" t="n">
+        <v>39.34999847412109</v>
+      </c>
+      <c r="F701" t="n">
+        <v>39.70000076293945</v>
+      </c>
+      <c r="G701" t="n">
+        <v>37.11000061035156</v>
+      </c>
+      <c r="H701" t="n">
+        <v>37.47000122070312</v>
+      </c>
+      <c r="I701" t="n">
+        <v>38.97999954223633</v>
+      </c>
+      <c r="J701" t="n">
+        <v>37.47000122070312</v>
+      </c>
+      <c r="K701" t="n">
+        <v>66732839</v>
+      </c>
+      <c r="L701" t="n">
+        <v>-3.87</v>
+      </c>
+      <c r="M701" t="inlineStr">
+        <is>
+          <t>Ola Electric Share Price - Live NSE: OLAELEC Stock Price &amp; Chart - Upstox</t>
+        </is>
+      </c>
+      <c r="N701" t="inlineStr">
+        <is>
+          <t>Ola Electric Share Price - Live NSE: OLAELEC Stock Price &amp; Chart - Upstox</t>
+        </is>
+      </c>
+      <c r="O701" t="inlineStr">
+        <is>
+          <t>Ola Electric Heralds New ‘LFP Era’ as Gigafactory Ramp-Up Powers Thousands of EVs - theglobeandmail.com</t>
+        </is>
+      </c>
+      <c r="P701" t="inlineStr">
+        <is>
+          <t>Ola Electric Launches New Battery Energy Storage Portfolio in India - theglobeandmail.com</t>
+        </is>
+      </c>
+      <c r="Q701" t="inlineStr">
+        <is>
+          <t>Ola Electric Files Q1 FY27 Monitoring Reports on IPO and QIP Proceeds - theglobeandmail.com</t>
         </is>
       </c>
     </row>

--- a/NEWS_Daily_Report/output/history/NEWS_Daily_Report_History.xlsx
+++ b/NEWS_Daily_Report/output/history/NEWS_Daily_Report_History.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q401"/>
+  <dimension ref="A1:Q421"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21.42578125" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -25584,9 +25584,6 @@
           <t>Birla Precision Technologies Ltd. (BIRLAPREC) Share Price Rises 10.68% Today - Univest</t>
         </is>
       </c>
-      <c r="O382" t="inlineStr"/>
-      <c r="P382" t="inlineStr"/>
-      <c r="Q382" t="inlineStr"/>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
@@ -25715,8 +25712,6 @@
           <t>Jindal Worldwide seeks approval for ₹650 Cr rights issue at AGM - scanx.trade</t>
         </is>
       </c>
-      <c r="P384" t="inlineStr"/>
-      <c r="Q384" t="inlineStr"/>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
@@ -25840,9 +25835,6 @@
           <t>Alpine Texworld Share Price news and valuation - Univest</t>
         </is>
       </c>
-      <c r="O386" t="inlineStr"/>
-      <c r="P386" t="inlineStr"/>
-      <c r="Q386" t="inlineStr"/>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
@@ -26040,8 +26032,6 @@
           <t>Kiri Industries Share Price Today: Price Rise and Valuation - Univest</t>
         </is>
       </c>
-      <c r="P389" t="inlineStr"/>
-      <c r="Q389" t="inlineStr"/>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
@@ -26101,8 +26091,6 @@
           <t>Makers Laboratories Q1 Results: Consolidated Net Profit Surges 244% YoY to ₹150.43 lacs - scanx.trade</t>
         </is>
       </c>
-      <c r="P390" t="inlineStr"/>
-      <c r="Q390" t="inlineStr"/>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
@@ -26231,8 +26219,6 @@
           <t>ISSC Dips 0.92% to $20.51: Innovative Solutions and Support Holds Key Support Level - ATR Stop - vinanet.vn</t>
         </is>
       </c>
-      <c r="P392" t="inlineStr"/>
-      <c r="Q392" t="inlineStr"/>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
@@ -26297,7 +26283,6 @@
           <t>BF Utilities gets 3-month extension for 26th AGM from ROC Pune - scanx.trade</t>
         </is>
       </c>
-      <c r="Q393" t="inlineStr"/>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
@@ -26352,9 +26337,6 @@
           <t>Manali Petrochemicals Share Price update: Rs 89.95, up 8.64% - Univest</t>
         </is>
       </c>
-      <c r="O394" t="inlineStr"/>
-      <c r="P394" t="inlineStr"/>
-      <c r="Q394" t="inlineStr"/>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
@@ -26488,7 +26470,6 @@
           <t>EFX Q2 2026 Earnings: EPS Beat Drives 3.85% Stock Uptick - Earnings Volatility Report - vinanet.vn</t>
         </is>
       </c>
-      <c r="Q396" t="inlineStr"/>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
@@ -26548,8 +26529,6 @@
           <t>SML Mahindra Posts 40% Surge in August Vehicle Sales - TipRanks</t>
         </is>
       </c>
-      <c r="P397" t="inlineStr"/>
-      <c r="Q397" t="inlineStr"/>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
@@ -26614,7 +26593,6 @@
           <t>Mahanadi Coalfields IPO: After Bharat Coking &amp; CMPDI, Coal India to offload 10% stake in third subsidiary - financialexpress.com</t>
         </is>
       </c>
-      <c r="Q398" t="inlineStr"/>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
@@ -26679,7 +26657,6 @@
           <t>Jyoti CNC Automation: Promoter Pledges 8.07% Stake - InvestyWise</t>
         </is>
       </c>
-      <c r="Q399" t="inlineStr"/>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
@@ -26803,9 +26780,1294 @@
           <t>Mukka Proteins approves ₹13.19 crore stake in Shipwaves Online - scanx.trade</t>
         </is>
       </c>
-      <c r="O401" t="inlineStr"/>
-      <c r="P401" t="inlineStr"/>
-      <c r="Q401" t="inlineStr"/>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>2026-09-04 12:50:03 IST</t>
+        </is>
+      </c>
+      <c r="B402" t="n">
+        <v>1</v>
+      </c>
+      <c r="C402" t="inlineStr">
+        <is>
+          <t>JINDWORLD.NS</t>
+        </is>
+      </c>
+      <c r="D402" t="inlineStr">
+        <is>
+          <t>Jindal Worldwide Limited</t>
+        </is>
+      </c>
+      <c r="E402" t="n">
+        <v>49.66999816894531</v>
+      </c>
+      <c r="F402" t="n">
+        <v>57.75</v>
+      </c>
+      <c r="G402" t="n">
+        <v>49.02000045776367</v>
+      </c>
+      <c r="H402" t="n">
+        <v>57.29000091552734</v>
+      </c>
+      <c r="I402" t="n">
+        <v>48.15000152587891</v>
+      </c>
+      <c r="J402" t="n">
+        <v>57.29000091552734</v>
+      </c>
+      <c r="K402" t="n">
+        <v>165843995</v>
+      </c>
+      <c r="L402" t="n">
+        <v>18.98</v>
+      </c>
+      <c r="M402" t="inlineStr">
+        <is>
+          <t>Most Active Equities on September 3, 2026 at 4:00 PM - hdfcsky.com</t>
+        </is>
+      </c>
+      <c r="N402" t="inlineStr">
+        <is>
+          <t>Most Active Equities on September 4, 2026 at 12:00 PM - hdfcsky.com</t>
+        </is>
+      </c>
+      <c r="O402" t="inlineStr">
+        <is>
+          <t>Jindal Worldwide seeks approval for ₹650 Cr rights issue at AGM - scanx.trade</t>
+        </is>
+      </c>
+      <c r="P402" t="inlineStr">
+        <is>
+          <t>Most Active Equities on September 4, 2026 at 12:00 PM - hdfcsky.com</t>
+        </is>
+      </c>
+      <c r="Q402" t="inlineStr">
+        <is>
+          <t>Jindal Worldwide shares surge again, up about 30% in two sessions on EV showroom expansion plan - Business Upturn</t>
+        </is>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>2026-09-04 12:50:03 IST</t>
+        </is>
+      </c>
+      <c r="B403" t="n">
+        <v>2</v>
+      </c>
+      <c r="C403" t="inlineStr">
+        <is>
+          <t>NIACL.NS</t>
+        </is>
+      </c>
+      <c r="D403" t="inlineStr">
+        <is>
+          <t>The New India Assurance Company Limited</t>
+        </is>
+      </c>
+      <c r="E403" t="n">
+        <v>196.4900054931641</v>
+      </c>
+      <c r="F403" t="n">
+        <v>229.2200012207031</v>
+      </c>
+      <c r="G403" t="n">
+        <v>196.4900054931641</v>
+      </c>
+      <c r="H403" t="n">
+        <v>227.0700073242188</v>
+      </c>
+      <c r="I403" t="n">
+        <v>195.3300018310547</v>
+      </c>
+      <c r="J403" t="n">
+        <v>227.0700073242188</v>
+      </c>
+      <c r="K403" t="n">
+        <v>41018366</v>
+      </c>
+      <c r="L403" t="n">
+        <v>16.25</v>
+      </c>
+      <c r="M403" t="inlineStr">
+        <is>
+          <t>NSE targets listing on Sep 25, reports CNBC-TV18; IFCI, NIACL shares rise up to 11% - TradingView</t>
+        </is>
+      </c>
+      <c r="N403" t="inlineStr">
+        <is>
+          <t>NSE targets listing on Sep 25, reports CNBC-TV18; IFCI, NIACL shares rise up to 11% - TradingView</t>
+        </is>
+      </c>
+      <c r="O403" t="inlineStr">
+        <is>
+          <t>NSE IPO Speculation Lifts IFCI, NIACL; Profit Booking Cuts Gains - hdfcsky.com</t>
+        </is>
+      </c>
+      <c r="P403" t="inlineStr">
+        <is>
+          <t>IFCI, NIACL stocks jump up to 14%; NSE IPO buzz lifts focus: Analysts share outlook - Business Today</t>
+        </is>
+      </c>
+      <c r="Q403" t="inlineStr">
+        <is>
+          <t>NSE IPO soon? NIACL, IFCI shares jump up to 11% on buzz over issue launch - TradingView</t>
+        </is>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>2026-09-04 12:50:03 IST</t>
+        </is>
+      </c>
+      <c r="B404" t="n">
+        <v>3</v>
+      </c>
+      <c r="C404" t="inlineStr">
+        <is>
+          <t>RESPONIND.NS</t>
+        </is>
+      </c>
+      <c r="D404" t="inlineStr">
+        <is>
+          <t>Responsive Industries Limited</t>
+        </is>
+      </c>
+      <c r="E404" t="n">
+        <v>151.25</v>
+      </c>
+      <c r="F404" t="n">
+        <v>176.1399993896484</v>
+      </c>
+      <c r="G404" t="n">
+        <v>151.25</v>
+      </c>
+      <c r="H404" t="n">
+        <v>173.0299987792969</v>
+      </c>
+      <c r="I404" t="n">
+        <v>151.8699951171875</v>
+      </c>
+      <c r="J404" t="n">
+        <v>173.0299987792969</v>
+      </c>
+      <c r="K404" t="n">
+        <v>22911336</v>
+      </c>
+      <c r="L404" t="n">
+        <v>13.93</v>
+      </c>
+      <c r="M404" t="inlineStr">
+        <is>
+          <t>Responsive Industries board to consider equity share buyback on Aug 14 - scanx.trade</t>
+        </is>
+      </c>
+      <c r="N404" t="inlineStr">
+        <is>
+          <t>Responsive Industries board to consider equity share buyback on Aug 14 - scanx.trade</t>
+        </is>
+      </c>
+      <c r="O404" t="inlineStr"/>
+      <c r="P404" t="inlineStr"/>
+      <c r="Q404" t="inlineStr"/>
+    </row>
+    <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>2026-09-04 12:50:03 IST</t>
+        </is>
+      </c>
+      <c r="B405" t="n">
+        <v>4</v>
+      </c>
+      <c r="C405" t="inlineStr">
+        <is>
+          <t>LANCORHOL.NS</t>
+        </is>
+      </c>
+      <c r="D405" t="inlineStr">
+        <is>
+          <t>Lancor Holdings Limited</t>
+        </is>
+      </c>
+      <c r="E405" t="n">
+        <v>35.13000106811523</v>
+      </c>
+      <c r="F405" t="n">
+        <v>40</v>
+      </c>
+      <c r="G405" t="n">
+        <v>34.20999908447266</v>
+      </c>
+      <c r="H405" t="n">
+        <v>39.5099983215332</v>
+      </c>
+      <c r="I405" t="n">
+        <v>34.75</v>
+      </c>
+      <c r="J405" t="n">
+        <v>39.5099983215332</v>
+      </c>
+      <c r="K405" t="n">
+        <v>1244384</v>
+      </c>
+      <c r="L405" t="n">
+        <v>13.7</v>
+      </c>
+      <c r="M405" t="inlineStr">
+        <is>
+          <t>Lancor Holdings Ltd. Share Price News and Stock Analysis - Univest</t>
+        </is>
+      </c>
+      <c r="N405" t="inlineStr">
+        <is>
+          <t>Lancor Holdings Ltd. Share Price News and Stock Analysis - Univest</t>
+        </is>
+      </c>
+      <c r="O405" t="inlineStr"/>
+      <c r="P405" t="inlineStr"/>
+      <c r="Q405" t="inlineStr"/>
+    </row>
+    <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>2026-09-04 12:50:03 IST</t>
+        </is>
+      </c>
+      <c r="B406" t="n">
+        <v>5</v>
+      </c>
+      <c r="C406" t="inlineStr">
+        <is>
+          <t>MARSONS.NS</t>
+        </is>
+      </c>
+      <c r="D406" t="inlineStr">
+        <is>
+          <t>Marsons Limited</t>
+        </is>
+      </c>
+      <c r="E406" t="n">
+        <v>125.8899993896484</v>
+      </c>
+      <c r="F406" t="n">
+        <v>140.7299957275391</v>
+      </c>
+      <c r="G406" t="n">
+        <v>125.3000030517578</v>
+      </c>
+      <c r="H406" t="n">
+        <v>139.4400024414062</v>
+      </c>
+      <c r="I406" t="n">
+        <v>125.5299987792969</v>
+      </c>
+      <c r="J406" t="n">
+        <v>139.4400024414062</v>
+      </c>
+      <c r="K406" t="n">
+        <v>10070759</v>
+      </c>
+      <c r="L406" t="n">
+        <v>11.08</v>
+      </c>
+      <c r="M406" t="inlineStr">
+        <is>
+          <t>Marsons Limited Receives PGCIL Vendor Approval for Supply of Power Transformers - scanx.trade</t>
+        </is>
+      </c>
+      <c r="N406" t="inlineStr">
+        <is>
+          <t>Marsons Limited Receives PGCIL Vendor Approval for Supply of Power Transformers - scanx.trade</t>
+        </is>
+      </c>
+      <c r="O406" t="inlineStr"/>
+      <c r="P406" t="inlineStr"/>
+      <c r="Q406" t="inlineStr"/>
+    </row>
+    <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>2026-09-04 12:50:03 IST</t>
+        </is>
+      </c>
+      <c r="B407" t="n">
+        <v>6</v>
+      </c>
+      <c r="C407" t="inlineStr">
+        <is>
+          <t>BIRLAPREC.NS</t>
+        </is>
+      </c>
+      <c r="D407" t="inlineStr">
+        <is>
+          <t>Birla Precision Technologies Limited</t>
+        </is>
+      </c>
+      <c r="E407" t="n">
+        <v>53.25</v>
+      </c>
+      <c r="F407" t="n">
+        <v>59.79000091552734</v>
+      </c>
+      <c r="G407" t="n">
+        <v>52.72999954223633</v>
+      </c>
+      <c r="H407" t="n">
+        <v>57.15000152587891</v>
+      </c>
+      <c r="I407" t="n">
+        <v>51.66999816894531</v>
+      </c>
+      <c r="J407" t="n">
+        <v>57.15000152587891</v>
+      </c>
+      <c r="K407" t="n">
+        <v>2011222</v>
+      </c>
+      <c r="L407" t="n">
+        <v>10.61</v>
+      </c>
+      <c r="M407" t="inlineStr">
+        <is>
+          <t>Birla Precision Technologies Ltd. (BIRLAPREC) Share Price Rises 10.68% Today - Univest</t>
+        </is>
+      </c>
+      <c r="N407" t="inlineStr">
+        <is>
+          <t>Birla Precision Technologies Ltd. (BIRLAPREC) Share Price Rises 10.68% Today - Univest</t>
+        </is>
+      </c>
+      <c r="O407" t="inlineStr"/>
+      <c r="P407" t="inlineStr"/>
+      <c r="Q407" t="inlineStr"/>
+    </row>
+    <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>2026-09-04 12:50:03 IST</t>
+        </is>
+      </c>
+      <c r="B408" t="n">
+        <v>7</v>
+      </c>
+      <c r="C408" t="inlineStr">
+        <is>
+          <t>TBZ.NS</t>
+        </is>
+      </c>
+      <c r="D408" t="inlineStr">
+        <is>
+          <t>Tribhovandas Bhimji Zaveri Limited</t>
+        </is>
+      </c>
+      <c r="E408" t="n">
+        <v>456</v>
+      </c>
+      <c r="F408" t="n">
+        <v>480.8500061035156</v>
+      </c>
+      <c r="G408" t="n">
+        <v>456</v>
+      </c>
+      <c r="H408" t="n">
+        <v>480.8500061035156</v>
+      </c>
+      <c r="I408" t="n">
+        <v>437.1499938964844</v>
+      </c>
+      <c r="J408" t="n">
+        <v>480.8500061035156</v>
+      </c>
+      <c r="K408" t="n">
+        <v>3433517</v>
+      </c>
+      <c r="L408" t="n">
+        <v>10</v>
+      </c>
+      <c r="M408" t="inlineStr">
+        <is>
+          <t>Tribhovandas Bhimji Zaveri is now GRT's jewel - Finshots</t>
+        </is>
+      </c>
+      <c r="N408" t="inlineStr">
+        <is>
+          <t>Tribhovandas Bhimji Zaveri soars 58% in 4 days; zooms 107% from Aug low - Business Standard</t>
+        </is>
+      </c>
+      <c r="O408" t="inlineStr">
+        <is>
+          <t>Tribhovandas Bhimji Zaveri soars 58% in 4 days; zooms 107% from Aug low - Business Standard</t>
+        </is>
+      </c>
+      <c r="P408" t="inlineStr">
+        <is>
+          <t>56% Jump In 5 Sessions: Why Is Tribhovandas Bhimji Zaveri Stock Locked In 10% Upper Circuit Today? - NDTV Profit</t>
+        </is>
+      </c>
+      <c r="Q408" t="inlineStr">
+        <is>
+          <t>TBZ shares zoom 20%, hit upper circuit after GRT Jewellers open offer - economictimes.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>2026-09-04 12:50:03 IST</t>
+        </is>
+      </c>
+      <c r="B409" t="n">
+        <v>8</v>
+      </c>
+      <c r="C409" t="inlineStr">
+        <is>
+          <t>RAMBHAJO.NS</t>
+        </is>
+      </c>
+      <c r="D409" t="inlineStr">
+        <is>
+          <t>Advit Jewels Limited</t>
+        </is>
+      </c>
+      <c r="E409" t="n">
+        <v>249.8999938964844</v>
+      </c>
+      <c r="F409" t="n">
+        <v>267.5</v>
+      </c>
+      <c r="G409" t="n">
+        <v>247.0599975585938</v>
+      </c>
+      <c r="H409" t="n">
+        <v>264.6400146484375</v>
+      </c>
+      <c r="I409" t="n">
+        <v>244.2599945068359</v>
+      </c>
+      <c r="J409" t="n">
+        <v>264.6400146484375</v>
+      </c>
+      <c r="K409" t="n">
+        <v>1505092</v>
+      </c>
+      <c r="L409" t="n">
+        <v>8.34</v>
+      </c>
+      <c r="M409" t="inlineStr">
+        <is>
+          <t>Advit Jewels Q1 Results: Earnings call audio now available online - scanx.trade</t>
+        </is>
+      </c>
+      <c r="N409" t="inlineStr">
+        <is>
+          <t>Advit Jewels Q1 Results: Earnings call audio now available online - scanx.trade</t>
+        </is>
+      </c>
+      <c r="O409" t="inlineStr"/>
+      <c r="P409" t="inlineStr"/>
+      <c r="Q409" t="inlineStr"/>
+    </row>
+    <row r="410">
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>2026-09-04 12:50:03 IST</t>
+        </is>
+      </c>
+      <c r="B410" t="n">
+        <v>9</v>
+      </c>
+      <c r="C410" t="inlineStr">
+        <is>
+          <t>MOTISONS.NS</t>
+        </is>
+      </c>
+      <c r="D410" t="inlineStr">
+        <is>
+          <t>Motisons Jewellers Limited</t>
+        </is>
+      </c>
+      <c r="E410" t="n">
+        <v>15.21000003814697</v>
+      </c>
+      <c r="F410" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="G410" t="n">
+        <v>15.21000003814697</v>
+      </c>
+      <c r="H410" t="n">
+        <v>16.39999961853027</v>
+      </c>
+      <c r="I410" t="n">
+        <v>15.36999988555908</v>
+      </c>
+      <c r="J410" t="n">
+        <v>16.39999961853027</v>
+      </c>
+      <c r="K410" t="n">
+        <v>103761387</v>
+      </c>
+      <c r="L410" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="M410" t="inlineStr">
+        <is>
+          <t>Motisons Jewellers Q1FY27 net profit rises 38% to ₹110.5 crore - scanx.trade</t>
+        </is>
+      </c>
+      <c r="N410" t="inlineStr">
+        <is>
+          <t>Vodafone Idea, Motisons, LEAP India Among Top NSE Movers - hdfcsky.com</t>
+        </is>
+      </c>
+      <c r="O410" t="inlineStr">
+        <is>
+          <t>Vodafone Idea, Motisons, LEAP India Among Top NSE Movers - hdfcsky.com</t>
+        </is>
+      </c>
+      <c r="P410" t="inlineStr">
+        <is>
+          <t>Motisons Jewellers standalone net profit rises 37.61% in the June 2026 quarter - Business Standard</t>
+        </is>
+      </c>
+      <c r="Q410" t="inlineStr">
+        <is>
+          <t>Motisons Jewellers shares jump 5% on heavy volumes after Q1 results: Here's what the numbers showed - Business Upturn</t>
+        </is>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>2026-09-04 12:50:03 IST</t>
+        </is>
+      </c>
+      <c r="B411" t="n">
+        <v>10</v>
+      </c>
+      <c r="C411" t="inlineStr">
+        <is>
+          <t>PURVA.NS</t>
+        </is>
+      </c>
+      <c r="D411" t="inlineStr">
+        <is>
+          <t>Puravankara Limited</t>
+        </is>
+      </c>
+      <c r="E411" t="n">
+        <v>215</v>
+      </c>
+      <c r="F411" t="n">
+        <v>236</v>
+      </c>
+      <c r="G411" t="n">
+        <v>215</v>
+      </c>
+      <c r="H411" t="n">
+        <v>224.7299957275391</v>
+      </c>
+      <c r="I411" t="n">
+        <v>211.0899963378906</v>
+      </c>
+      <c r="J411" t="n">
+        <v>224.7299957275391</v>
+      </c>
+      <c r="K411" t="n">
+        <v>13276061</v>
+      </c>
+      <c r="L411" t="n">
+        <v>6.46</v>
+      </c>
+      <c r="M411" t="inlineStr">
+        <is>
+          <t>TTI Enterprise appoints Purva Sharegistry as new RTA - scanx.trade</t>
+        </is>
+      </c>
+      <c r="N411" t="inlineStr">
+        <is>
+          <t>Puravankara Ltd. Share Price Rise: Valuation and Sector - Univest</t>
+        </is>
+      </c>
+      <c r="O411" t="inlineStr">
+        <is>
+          <t>Puravankara Ltd. Share Price Rise: Valuation and Sector - Univest</t>
+        </is>
+      </c>
+      <c r="P411" t="inlineStr">
+        <is>
+          <t>What Drove Puravankara’s Q1 FY27 Profit Turnaround? Key Factors Explained - Trade Brains</t>
+        </is>
+      </c>
+      <c r="Q411" t="inlineStr">
+        <is>
+          <t>Puravankara Moves AGM Online, Directs Offline Shareholders to Digital Annual Report - TipRanks</t>
+        </is>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>2026-09-04 12:50:03 IST</t>
+        </is>
+      </c>
+      <c r="B412" t="n">
+        <v>11</v>
+      </c>
+      <c r="C412" t="inlineStr">
+        <is>
+          <t>AFFLE.NS</t>
+        </is>
+      </c>
+      <c r="D412" t="inlineStr">
+        <is>
+          <t>Affle 3i Limited</t>
+        </is>
+      </c>
+      <c r="E412" t="n">
+        <v>1529</v>
+      </c>
+      <c r="F412" t="n">
+        <v>1620.699951171875</v>
+      </c>
+      <c r="G412" t="n">
+        <v>1521</v>
+      </c>
+      <c r="H412" t="n">
+        <v>1611.300048828125</v>
+      </c>
+      <c r="I412" t="n">
+        <v>1519.199951171875</v>
+      </c>
+      <c r="J412" t="n">
+        <v>1611.300048828125</v>
+      </c>
+      <c r="K412" t="n">
+        <v>650727</v>
+      </c>
+      <c r="L412" t="n">
+        <v>6.06</v>
+      </c>
+      <c r="M412" t="inlineStr">
+        <is>
+          <t>Affle 3i Share Price: Buy, Hold or Sell Guide - Univest</t>
+        </is>
+      </c>
+      <c r="N412" t="inlineStr">
+        <is>
+          <t>Affle 3i Share Price: Is It a Good Buy After Q1 FY27 Results? - Univest</t>
+        </is>
+      </c>
+      <c r="O412" t="inlineStr">
+        <is>
+          <t>Affle 3i Share Price: Is It a Good Buy After Q1 FY27 Results? - Univest</t>
+        </is>
+      </c>
+      <c r="P412" t="inlineStr">
+        <is>
+          <t>Affle 3i to participate in Elara Capital investor conference - scanx.trade</t>
+        </is>
+      </c>
+      <c r="Q412" t="inlineStr">
+        <is>
+          <t>Affle 3i holds investor meet with Stallion Asset Management - scanx.trade</t>
+        </is>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>2026-09-04 12:50:03 IST</t>
+        </is>
+      </c>
+      <c r="B413" t="n">
+        <v>12</v>
+      </c>
+      <c r="C413" t="inlineStr">
+        <is>
+          <t>WELSPLSOL.NS</t>
+        </is>
+      </c>
+      <c r="D413" t="inlineStr">
+        <is>
+          <t>Welspun Specialty Solutions Limited</t>
+        </is>
+      </c>
+      <c r="E413" t="n">
+        <v>56.95000076293945</v>
+      </c>
+      <c r="F413" t="n">
+        <v>59.43999862670898</v>
+      </c>
+      <c r="G413" t="n">
+        <v>56.0099983215332</v>
+      </c>
+      <c r="H413" t="n">
+        <v>59.38000106811523</v>
+      </c>
+      <c r="I413" t="n">
+        <v>56.02000045776367</v>
+      </c>
+      <c r="J413" t="n">
+        <v>59.38000106811523</v>
+      </c>
+      <c r="K413" t="n">
+        <v>1434273</v>
+      </c>
+      <c r="L413" t="n">
+        <v>6</v>
+      </c>
+      <c r="M413" t="inlineStr">
+        <is>
+          <t>WELSPLSOL Stock Price and Chart — NSE:WELSPLSOL - TradingView</t>
+        </is>
+      </c>
+      <c r="N413" t="inlineStr">
+        <is>
+          <t>Welspun Specialty Solutions (WELSPLSOL) Mar 2026 Earnings: Modest Profitability Amid Revenue Stability - Capex Guidance - vinanet.vn</t>
+        </is>
+      </c>
+      <c r="O413" t="inlineStr">
+        <is>
+          <t>Shareholders Will Be Pleased With The Quality of Welspun Specialty Solutions' (NSE:WELSPLSOL) Earnings - simplywall.st</t>
+        </is>
+      </c>
+      <c r="P413" t="inlineStr">
+        <is>
+          <t>Welspun Specialty Solutions Limited (WELSPLSOL.NS) Mar 2026 Earnings: Marginal Profitability Maintained on Steady Revenue - Revenue Growth Outlook - vinanet.vn</t>
+        </is>
+      </c>
+      <c r="Q413" t="inlineStr">
+        <is>
+          <t>WELSPLSOL Mar 2026 Earnings: Modest Profitability Amidst Stable Revenue Run-Rate - Revenue Estimate Trend - vinanet.vn</t>
+        </is>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>2026-09-04 12:50:03 IST</t>
+        </is>
+      </c>
+      <c r="B414" t="n">
+        <v>13</v>
+      </c>
+      <c r="C414" t="inlineStr">
+        <is>
+          <t>WELENT.NS</t>
+        </is>
+      </c>
+      <c r="D414" t="inlineStr">
+        <is>
+          <t>Welspun Enterprises Limited</t>
+        </is>
+      </c>
+      <c r="E414" t="n">
+        <v>761.7999877929688</v>
+      </c>
+      <c r="F414" t="n">
+        <v>825</v>
+      </c>
+      <c r="G414" t="n">
+        <v>757.4000244140625</v>
+      </c>
+      <c r="H414" t="n">
+        <v>810.5</v>
+      </c>
+      <c r="I414" t="n">
+        <v>764.75</v>
+      </c>
+      <c r="J414" t="n">
+        <v>810.5</v>
+      </c>
+      <c r="K414" t="n">
+        <v>1719692</v>
+      </c>
+      <c r="L414" t="n">
+        <v>5.98</v>
+      </c>
+      <c r="M414" t="inlineStr">
+        <is>
+          <t>Welspun Enterprises Share Price News: Fresh 52-Week Peak - Univest</t>
+        </is>
+      </c>
+      <c r="N414" t="inlineStr">
+        <is>
+          <t>Welspun Enterprises Share Price: fresh 52-week high update - Univest</t>
+        </is>
+      </c>
+      <c r="O414" t="inlineStr">
+        <is>
+          <t>Welspun Enterprises Share Price: fresh 52-week high update - Univest</t>
+        </is>
+      </c>
+      <c r="P414" t="inlineStr">
+        <is>
+          <t>Welspun Enterprises Ltd. Share Price at Fresh 52-Week High - Univest</t>
+        </is>
+      </c>
+      <c r="Q414" t="inlineStr"/>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>2026-09-04 12:50:03 IST</t>
+        </is>
+      </c>
+      <c r="B415" t="n">
+        <v>14</v>
+      </c>
+      <c r="C415" t="inlineStr">
+        <is>
+          <t>SKIPPER.NS</t>
+        </is>
+      </c>
+      <c r="D415" t="inlineStr">
+        <is>
+          <t>Skipper Limited</t>
+        </is>
+      </c>
+      <c r="E415" t="n">
+        <v>538.1500244140625</v>
+      </c>
+      <c r="F415" t="n">
+        <v>578.7999877929688</v>
+      </c>
+      <c r="G415" t="n">
+        <v>533.75</v>
+      </c>
+      <c r="H415" t="n">
+        <v>578.7999877929688</v>
+      </c>
+      <c r="I415" t="n">
+        <v>546.9000244140625</v>
+      </c>
+      <c r="J415" t="n">
+        <v>578.7999877929688</v>
+      </c>
+      <c r="K415" t="n">
+        <v>1388238</v>
+      </c>
+      <c r="L415" t="n">
+        <v>5.83</v>
+      </c>
+      <c r="M415" t="inlineStr">
+        <is>
+          <t>Skipper Q1FY27 net profit rises 26.5% to ₹565M on infra surge - scanx.trade</t>
+        </is>
+      </c>
+      <c r="N415" t="inlineStr">
+        <is>
+          <t>Skipper Q1FY27 net profit rises 26.5% to ₹565M on infra surge - scanx.trade</t>
+        </is>
+      </c>
+      <c r="O415" t="inlineStr">
+        <is>
+          <t>Skipper Shares Rise 3% on Rs 1,305 Cr T&amp;D Order Wins - Equitypandit</t>
+        </is>
+      </c>
+      <c r="P415" t="inlineStr">
+        <is>
+          <t>News by CNBC TV18 on TradingView, 2026-08-27 — cnbctv:6bc1348a7094b:0 - TradingView</t>
+        </is>
+      </c>
+      <c r="Q415" t="inlineStr">
+        <is>
+          <t>50% Return in Six Months: This Stock Jumped 3% After Getting Rs 1,305 Crore New Project Order - NDTV Profit</t>
+        </is>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>2026-09-04 12:50:03 IST</t>
+        </is>
+      </c>
+      <c r="B416" t="n">
+        <v>15</v>
+      </c>
+      <c r="C416" t="inlineStr">
+        <is>
+          <t>ANGELONE.NS</t>
+        </is>
+      </c>
+      <c r="D416" t="inlineStr">
+        <is>
+          <t>Angel One Limited</t>
+        </is>
+      </c>
+      <c r="E416" t="n">
+        <v>295.1000061035156</v>
+      </c>
+      <c r="F416" t="n">
+        <v>308.3500061035156</v>
+      </c>
+      <c r="G416" t="n">
+        <v>294.75</v>
+      </c>
+      <c r="H416" t="n">
+        <v>302.1499938964844</v>
+      </c>
+      <c r="I416" t="n">
+        <v>286</v>
+      </c>
+      <c r="J416" t="n">
+        <v>302.1499938964844</v>
+      </c>
+      <c r="K416" t="n">
+        <v>25159255</v>
+      </c>
+      <c r="L416" t="n">
+        <v>5.65</v>
+      </c>
+      <c r="M416" t="inlineStr">
+        <is>
+          <t>Angel One Stock And Indian Trading Platforms Facing A Volatile Market Test - simplywall.st</t>
+        </is>
+      </c>
+      <c r="N416" t="inlineStr">
+        <is>
+          <t>Angel One Stock And Indian Trading Platforms Facing A Volatile Market Test - simplywall.st</t>
+        </is>
+      </c>
+      <c r="O416" t="inlineStr">
+        <is>
+          <t>Should You Buy Angel One Shares On Monday To Be Eligible For 2nd Interim Dividend By Record Date? - Goodreturns</t>
+        </is>
+      </c>
+      <c r="P416" t="inlineStr">
+        <is>
+          <t>Angel One Allots 3.49 Lakh Shares Under Employee Incentive Plan - TipRanks</t>
+        </is>
+      </c>
+      <c r="Q416" t="inlineStr"/>
+    </row>
+    <row r="417">
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>2026-09-04 12:50:03 IST</t>
+        </is>
+      </c>
+      <c r="B417" t="n">
+        <v>16</v>
+      </c>
+      <c r="C417" t="inlineStr">
+        <is>
+          <t>SMLMAH.NS</t>
+        </is>
+      </c>
+      <c r="D417" t="inlineStr">
+        <is>
+          <t>SML Mahindra Limited</t>
+        </is>
+      </c>
+      <c r="E417" t="n">
+        <v>5725</v>
+      </c>
+      <c r="F417" t="n">
+        <v>6094</v>
+      </c>
+      <c r="G417" t="n">
+        <v>5719.5</v>
+      </c>
+      <c r="H417" t="n">
+        <v>6049.5</v>
+      </c>
+      <c r="I417" t="n">
+        <v>5726</v>
+      </c>
+      <c r="J417" t="n">
+        <v>6049.5</v>
+      </c>
+      <c r="K417" t="n">
+        <v>226226</v>
+      </c>
+      <c r="L417" t="n">
+        <v>5.65</v>
+      </c>
+      <c r="M417" t="inlineStr">
+        <is>
+          <t>SML Mahindra February CV Production Increases To 1,679 Units From 1,442 Units YoY - scanx.trade</t>
+        </is>
+      </c>
+      <c r="N417" t="inlineStr">
+        <is>
+          <t>SML Mahindra Posts 40% Surge in August Vehicle Sales - TipRanks</t>
+        </is>
+      </c>
+      <c r="O417" t="inlineStr">
+        <is>
+          <t>SML Mahindra Posts 40% Surge in August Vehicle Sales - TipRanks</t>
+        </is>
+      </c>
+      <c r="P417" t="inlineStr"/>
+      <c r="Q417" t="inlineStr"/>
+    </row>
+    <row r="418">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>2026-09-04 12:50:03 IST</t>
+        </is>
+      </c>
+      <c r="B418" t="n">
+        <v>17</v>
+      </c>
+      <c r="C418" t="inlineStr">
+        <is>
+          <t>INDORAMA.NS</t>
+        </is>
+      </c>
+      <c r="D418" t="inlineStr">
+        <is>
+          <t>Indo Rama Synthetics (India) Limited</t>
+        </is>
+      </c>
+      <c r="E418" t="n">
+        <v>69.79000091552734</v>
+      </c>
+      <c r="F418" t="n">
+        <v>74.25</v>
+      </c>
+      <c r="G418" t="n">
+        <v>69.55000305175781</v>
+      </c>
+      <c r="H418" t="n">
+        <v>72.56999969482422</v>
+      </c>
+      <c r="I418" t="n">
+        <v>68.87000274658203</v>
+      </c>
+      <c r="J418" t="n">
+        <v>72.56999969482422</v>
+      </c>
+      <c r="K418" t="n">
+        <v>1298184</v>
+      </c>
+      <c r="L418" t="n">
+        <v>5.37</v>
+      </c>
+      <c r="M418" t="inlineStr">
+        <is>
+          <t>Indo Rama Synthetics (India) Ltd. (INDORAMA) Share Price Rises 10.14% Today - Univest</t>
+        </is>
+      </c>
+      <c r="N418" t="inlineStr">
+        <is>
+          <t>Indo Rama Synthetics (India) Ltd. (INDORAMA) Share Price Rises 10.14% Today - Univest</t>
+        </is>
+      </c>
+      <c r="O418" t="inlineStr">
+        <is>
+          <t>Indorama Ventures posts strong 1H26 recovery as EBITDA jumps 61% - Thai Enquirer</t>
+        </is>
+      </c>
+      <c r="P418" t="inlineStr">
+        <is>
+          <t>Indorama Ventures Public Company Limited 2026 Q2 - Results - Earnings Call Presentation - Seeking Alpha</t>
+        </is>
+      </c>
+      <c r="Q418" t="inlineStr"/>
+    </row>
+    <row r="419">
+      <c r="A419" t="inlineStr">
+        <is>
+          <t>2026-09-04 12:50:03 IST</t>
+        </is>
+      </c>
+      <c r="B419" t="n">
+        <v>18</v>
+      </c>
+      <c r="C419" t="inlineStr">
+        <is>
+          <t>PAISALO.NS</t>
+        </is>
+      </c>
+      <c r="D419" t="inlineStr">
+        <is>
+          <t>Paisalo Digital Limited</t>
+        </is>
+      </c>
+      <c r="E419" t="n">
+        <v>71.65000152587891</v>
+      </c>
+      <c r="F419" t="n">
+        <v>74.05999755859375</v>
+      </c>
+      <c r="G419" t="n">
+        <v>70.05000305175781</v>
+      </c>
+      <c r="H419" t="n">
+        <v>74</v>
+      </c>
+      <c r="I419" t="n">
+        <v>70.27999877929688</v>
+      </c>
+      <c r="J419" t="n">
+        <v>74</v>
+      </c>
+      <c r="K419" t="n">
+        <v>19527382</v>
+      </c>
+      <c r="L419" t="n">
+        <v>5.29</v>
+      </c>
+      <c r="M419" t="inlineStr">
+        <is>
+          <t>Paisalo Digital Share Price rises 5.78%: valuation view - Univest</t>
+        </is>
+      </c>
+      <c r="N419" t="inlineStr">
+        <is>
+          <t>Paisalo Digital Share Price rises 5.78%: valuation view - Univest</t>
+        </is>
+      </c>
+      <c r="O419" t="inlineStr">
+        <is>
+          <t>Paisalo Digital Operations and Finance Committee to review NCD issuance on September 5 - scanx.trade</t>
+        </is>
+      </c>
+      <c r="P419" t="inlineStr">
+        <is>
+          <t>Paisalo Digital Ltd. Stock News - Value Research</t>
+        </is>
+      </c>
+      <c r="Q419" t="inlineStr">
+        <is>
+          <t>Paisalo Digital Ltd. Share Price Today - Paisalo Digital Ltd. Stock Price Live NSE/BSE - CNBC TV18</t>
+        </is>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="inlineStr">
+        <is>
+          <t>2026-09-04 12:50:03 IST</t>
+        </is>
+      </c>
+      <c r="B420" t="n">
+        <v>19</v>
+      </c>
+      <c r="C420" t="inlineStr">
+        <is>
+          <t>CARBORUNIV.NS</t>
+        </is>
+      </c>
+      <c r="D420" t="inlineStr">
+        <is>
+          <t>Carborundum Universal Limited</t>
+        </is>
+      </c>
+      <c r="E420" t="n">
+        <v>1078.699951171875</v>
+      </c>
+      <c r="F420" t="n">
+        <v>1140.900024414062</v>
+      </c>
+      <c r="G420" t="n">
+        <v>1069.900024414062</v>
+      </c>
+      <c r="H420" t="n">
+        <v>1135</v>
+      </c>
+      <c r="I420" t="n">
+        <v>1078</v>
+      </c>
+      <c r="J420" t="n">
+        <v>1135</v>
+      </c>
+      <c r="K420" t="n">
+        <v>218121</v>
+      </c>
+      <c r="L420" t="n">
+        <v>5.29</v>
+      </c>
+      <c r="M420" t="inlineStr">
+        <is>
+          <t>Carborundum Universal Ltd. Share Price Rise: Price Action - Univest</t>
+        </is>
+      </c>
+      <c r="N420" t="inlineStr">
+        <is>
+          <t>Carborundum Universal Share Price Rises 3.69%: Analysis - Univest</t>
+        </is>
+      </c>
+      <c r="O420" t="inlineStr">
+        <is>
+          <t>Carborundum Universal Share Price: 4.87% Price Rise Analysis - Univest</t>
+        </is>
+      </c>
+      <c r="P420" t="inlineStr">
+        <is>
+          <t>Carborundum Universal Share Price Rises 3.69%: Analysis - Univest</t>
+        </is>
+      </c>
+      <c r="Q420" t="inlineStr">
+        <is>
+          <t>Carborundum Universal Ltd. Share Price Price Action View - Univest</t>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>2026-09-04 12:50:03 IST</t>
+        </is>
+      </c>
+      <c r="B421" t="n">
+        <v>20</v>
+      </c>
+      <c r="C421" t="inlineStr">
+        <is>
+          <t>PWL.NS</t>
+        </is>
+      </c>
+      <c r="D421" t="inlineStr">
+        <is>
+          <t>Physicswallah Limited</t>
+        </is>
+      </c>
+      <c r="E421" t="n">
+        <v>123.370002746582</v>
+      </c>
+      <c r="F421" t="n">
+        <v>129.6999969482422</v>
+      </c>
+      <c r="G421" t="n">
+        <v>123.0299987792969</v>
+      </c>
+      <c r="H421" t="n">
+        <v>126.9000015258789</v>
+      </c>
+      <c r="I421" t="n">
+        <v>120.5999984741211</v>
+      </c>
+      <c r="J421" t="n">
+        <v>126.9000015258789</v>
+      </c>
+      <c r="K421" t="n">
+        <v>35587662</v>
+      </c>
+      <c r="L421" t="n">
+        <v>5.22</v>
+      </c>
+      <c r="M421" t="inlineStr">
+        <is>
+          <t>PW Gyaan-E Finance | 33+ Courses, Guides &amp; 200+ Skill Courses - PW</t>
+        </is>
+      </c>
+      <c r="N421" t="inlineStr">
+        <is>
+          <t>PW Gyaan-E Finance | 33+ Courses, Guides &amp; 200+ Skill Courses - PW</t>
+        </is>
+      </c>
+      <c r="O421" t="inlineStr"/>
+      <c r="P421" t="inlineStr"/>
+      <c r="Q421" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:Q361"/>
@@ -26819,7 +28081,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q701"/>
+  <dimension ref="A1:Q721"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -69542,9 +70804,6 @@
           <t>Salasar Techno Engineering Ltd. Stock News - valueresearchonline.com</t>
         </is>
       </c>
-      <c r="O682" t="inlineStr"/>
-      <c r="P682" t="inlineStr"/>
-      <c r="Q682" t="inlineStr"/>
     </row>
     <row r="683">
       <c r="A683" t="inlineStr">
@@ -69742,8 +71001,6 @@
           <t>Suraj Estate Developers Limited Begins FY27 on Strong Footing, Driven by Robust Sales Momentum - Business Standard</t>
         </is>
       </c>
-      <c r="P685" t="inlineStr"/>
-      <c r="Q685" t="inlineStr"/>
     </row>
     <row r="686">
       <c r="A686" t="inlineStr">
@@ -70212,9 +71469,6 @@
           <t>Adamas (ADAM) Q2 2026 Results: EPS Exceeds Its Estimate on the Day; Trading Response: Shares Finish 0.80% Down at the Close - Product Revenue Analysis - vinanet.vn</t>
         </is>
       </c>
-      <c r="O692" t="inlineStr"/>
-      <c r="P692" t="inlineStr"/>
-      <c r="Q692" t="inlineStr"/>
     </row>
     <row r="693">
       <c r="A693" t="inlineStr">
@@ -70343,8 +71597,6 @@
           <t>A West Texas project plans 10 gas engines totaling 123 megawatts - Stock Titan</t>
         </is>
       </c>
-      <c r="P694" t="inlineStr"/>
-      <c r="Q694" t="inlineStr"/>
     </row>
     <row r="695">
       <c r="A695" t="inlineStr">
@@ -70537,9 +71789,6 @@
           <t>News by CNBC TV18 on TradingView, 2026-08-23 — cnbctv:8653cb759094b:0 - TradingView</t>
         </is>
       </c>
-      <c r="O697" t="inlineStr"/>
-      <c r="P697" t="inlineStr"/>
-      <c r="Q697" t="inlineStr"/>
     </row>
     <row r="698">
       <c r="A698" t="inlineStr">
@@ -70668,8 +71917,6 @@
           <t>Specialty Chemicals Stocks To Buy: Navin Fluorine, Rossari Among Nirmal Bang's Eight Picks With Up To 37% Upside — Full List Inside - NDTV Profit</t>
         </is>
       </c>
-      <c r="P699" t="inlineStr"/>
-      <c r="Q699" t="inlineStr"/>
     </row>
     <row r="700">
       <c r="A700" t="inlineStr">
@@ -70734,7 +71981,6 @@
           <t>Cords Cable Flags Routine Newspaper Disclosure to Exchange - TipRanks</t>
         </is>
       </c>
-      <c r="Q700" t="inlineStr"/>
     </row>
     <row r="701">
       <c r="A701" t="inlineStr">
@@ -70804,6 +72050,1330 @@
           <t>Ola Electric Files Q1 FY27 Monitoring Reports on IPO and QIP Proceeds - theglobeandmail.com</t>
         </is>
       </c>
+    </row>
+    <row r="702">
+      <c r="A702" t="inlineStr">
+        <is>
+          <t>2026-09-04 12:50:03 IST</t>
+        </is>
+      </c>
+      <c r="B702" t="n">
+        <v>1</v>
+      </c>
+      <c r="C702" t="inlineStr">
+        <is>
+          <t>JAYNECOIND.NS</t>
+        </is>
+      </c>
+      <c r="D702" t="inlineStr">
+        <is>
+          <t>Jayaswal Neco Industries Limited</t>
+        </is>
+      </c>
+      <c r="E702" t="n">
+        <v>92</v>
+      </c>
+      <c r="F702" t="n">
+        <v>94.37000274658203</v>
+      </c>
+      <c r="G702" t="n">
+        <v>85.22000122070312</v>
+      </c>
+      <c r="H702" t="n">
+        <v>86.76000213623047</v>
+      </c>
+      <c r="I702" t="n">
+        <v>98.68000030517578</v>
+      </c>
+      <c r="J702" t="n">
+        <v>86.76000213623047</v>
+      </c>
+      <c r="K702" t="n">
+        <v>39076238</v>
+      </c>
+      <c r="L702" t="n">
+        <v>-12.08</v>
+      </c>
+      <c r="M702" t="inlineStr">
+        <is>
+          <t>With EPS Growth And More, Jayaswal Neco Industries (NSE:JAYNECOIND) Makes An Interesting Case - simplywall.st</t>
+        </is>
+      </c>
+      <c r="N702" t="inlineStr">
+        <is>
+          <t>With EPS Growth And More, Jayaswal Neco Industries (NSE:JAYNECOIND) Makes An Interesting Case - simplywall.st</t>
+        </is>
+      </c>
+      <c r="O702" t="inlineStr"/>
+      <c r="P702" t="inlineStr"/>
+      <c r="Q702" t="inlineStr"/>
+    </row>
+    <row r="703">
+      <c r="A703" t="inlineStr">
+        <is>
+          <t>2026-09-04 12:50:03 IST</t>
+        </is>
+      </c>
+      <c r="B703" t="n">
+        <v>2</v>
+      </c>
+      <c r="C703" t="inlineStr">
+        <is>
+          <t>UGARSUGAR.NS</t>
+        </is>
+      </c>
+      <c r="D703" t="inlineStr">
+        <is>
+          <t>The Ugar Sugar Works Limited</t>
+        </is>
+      </c>
+      <c r="E703" t="n">
+        <v>58.40000152587891</v>
+      </c>
+      <c r="F703" t="n">
+        <v>58.5</v>
+      </c>
+      <c r="G703" t="n">
+        <v>53.43000030517578</v>
+      </c>
+      <c r="H703" t="n">
+        <v>53.84000015258789</v>
+      </c>
+      <c r="I703" t="n">
+        <v>58.56000137329102</v>
+      </c>
+      <c r="J703" t="n">
+        <v>53.84000015258789</v>
+      </c>
+      <c r="K703" t="n">
+        <v>1106436</v>
+      </c>
+      <c r="L703" t="n">
+        <v>-8.06</v>
+      </c>
+      <c r="M703" t="inlineStr">
+        <is>
+          <t>Ugar Sugar Works director Hari Athawale retires, Prafulla Shirgaokar resigns from board - ChiniMandi</t>
+        </is>
+      </c>
+      <c r="N703" t="inlineStr">
+        <is>
+          <t>Ugar Sugar Works director Hari Athawale retires, Prafulla Shirgaokar resigns from board - ChiniMandi</t>
+        </is>
+      </c>
+      <c r="O703" t="inlineStr"/>
+      <c r="P703" t="inlineStr"/>
+      <c r="Q703" t="inlineStr"/>
+    </row>
+    <row r="704">
+      <c r="A704" t="inlineStr">
+        <is>
+          <t>2026-09-04 12:50:03 IST</t>
+        </is>
+      </c>
+      <c r="B704" t="n">
+        <v>3</v>
+      </c>
+      <c r="C704" t="inlineStr">
+        <is>
+          <t>DYCL.NS</t>
+        </is>
+      </c>
+      <c r="D704" t="inlineStr">
+        <is>
+          <t>Dynamic Cables Limited</t>
+        </is>
+      </c>
+      <c r="E704" t="n">
+        <v>541.9000244140625</v>
+      </c>
+      <c r="F704" t="n">
+        <v>546.7999877929688</v>
+      </c>
+      <c r="G704" t="n">
+        <v>500</v>
+      </c>
+      <c r="H704" t="n">
+        <v>505.25</v>
+      </c>
+      <c r="I704" t="n">
+        <v>544.2999877929688</v>
+      </c>
+      <c r="J704" t="n">
+        <v>505.25</v>
+      </c>
+      <c r="K704" t="n">
+        <v>994101</v>
+      </c>
+      <c r="L704" t="n">
+        <v>-7.17</v>
+      </c>
+      <c r="M704" t="inlineStr">
+        <is>
+          <t>We Ran A Stock Scan For Earnings Growth And Dynamic Cables (NSE:DYCL) Passed With Ease - simplywall.st</t>
+        </is>
+      </c>
+      <c r="N704" t="inlineStr">
+        <is>
+          <t>Dynamic Cables (DYCL.NS): Modest Uptick Mirrors Cautious Sector Optimism - Reversal Setup Alerts - vinanet.vn</t>
+        </is>
+      </c>
+      <c r="O704" t="inlineStr">
+        <is>
+          <t>Dynamic Cables Limited Confirms No Share Encumbrance by Promoters for FY26 - scanx.trade</t>
+        </is>
+      </c>
+      <c r="P704" t="inlineStr">
+        <is>
+          <t>Dynamic Cables Limited (DYCL.NS) Q2 2026 Earnings: Revenue Growth Drivers and Operational Resilience - ROA Comparison - vinanet.vn</t>
+        </is>
+      </c>
+      <c r="Q704" t="inlineStr">
+        <is>
+          <t>Dynamic Cables Limited Receives CRISIL Credit Rating Reaffirmation for Rs. 350 Crore Banking Facilities - scanx.trade</t>
+        </is>
+      </c>
+    </row>
+    <row r="705">
+      <c r="A705" t="inlineStr">
+        <is>
+          <t>2026-09-04 12:50:03 IST</t>
+        </is>
+      </c>
+      <c r="B705" t="n">
+        <v>4</v>
+      </c>
+      <c r="C705" t="inlineStr">
+        <is>
+          <t>POLYCAB.NS</t>
+        </is>
+      </c>
+      <c r="D705" t="inlineStr">
+        <is>
+          <t>Polycab India Limited</t>
+        </is>
+      </c>
+      <c r="E705" t="n">
+        <v>8500</v>
+      </c>
+      <c r="F705" t="n">
+        <v>8500</v>
+      </c>
+      <c r="G705" t="n">
+        <v>8287.5</v>
+      </c>
+      <c r="H705" t="n">
+        <v>8308.5</v>
+      </c>
+      <c r="I705" t="n">
+        <v>8807.5</v>
+      </c>
+      <c r="J705" t="n">
+        <v>8308.5</v>
+      </c>
+      <c r="K705" t="n">
+        <v>1026763</v>
+      </c>
+      <c r="L705" t="n">
+        <v>-5.67</v>
+      </c>
+      <c r="M705" t="inlineStr">
+        <is>
+          <t>Polycab, KEI Industries shares crash up to 9% after UltraTech Cement enters wires &amp; cables business. What - economictimes.com</t>
+        </is>
+      </c>
+      <c r="N705" t="inlineStr">
+        <is>
+          <t>RR Kabel, KEI Industries, Polycab shares sink up to 8%; Nuvama lists preferred picks - Business Today</t>
+        </is>
+      </c>
+      <c r="O705" t="inlineStr">
+        <is>
+          <t>Polycab, KEI Industries Shares up to 8% as Ultratech Enters Wires &amp; Cables Business with Ultravolt - India Infoline</t>
+        </is>
+      </c>
+      <c r="P705" t="inlineStr">
+        <is>
+          <t>Cable stocks crash up to 6% as UltraTech launches Ultravolt; Polycab, KEI, RR Kabel among top losers - Moneycontrol.com</t>
+        </is>
+      </c>
+      <c r="Q705" t="inlineStr">
+        <is>
+          <t>Copper Shock Hits Cables Stocks: Polycab, Finolex, RR Kabel Slide Up To 6% After Price Hikes - NDTV Profit</t>
+        </is>
+      </c>
+    </row>
+    <row r="706">
+      <c r="A706" t="inlineStr">
+        <is>
+          <t>2026-09-04 12:50:03 IST</t>
+        </is>
+      </c>
+      <c r="B706" t="n">
+        <v>5</v>
+      </c>
+      <c r="C706" t="inlineStr">
+        <is>
+          <t>UTTAMSUGAR.NS</t>
+        </is>
+      </c>
+      <c r="D706" t="inlineStr">
+        <is>
+          <t>Uttam Sugar Mills Limited</t>
+        </is>
+      </c>
+      <c r="E706" t="n">
+        <v>300.8999938964844</v>
+      </c>
+      <c r="F706" t="n">
+        <v>302</v>
+      </c>
+      <c r="G706" t="n">
+        <v>281.0499877929688</v>
+      </c>
+      <c r="H706" t="n">
+        <v>283.2000122070312</v>
+      </c>
+      <c r="I706" t="n">
+        <v>299</v>
+      </c>
+      <c r="J706" t="n">
+        <v>283.2000122070312</v>
+      </c>
+      <c r="K706" t="n">
+        <v>231891</v>
+      </c>
+      <c r="L706" t="n">
+        <v>-5.28</v>
+      </c>
+      <c r="M706" t="inlineStr">
+        <is>
+          <t>Uttam Sugar Mills Share Price Today: 8.75% rise - Univest</t>
+        </is>
+      </c>
+      <c r="N706" t="inlineStr">
+        <is>
+          <t>Uttam Sugar Mills Share Price Today: 8.75% rise - Univest</t>
+        </is>
+      </c>
+      <c r="O706" t="inlineStr">
+        <is>
+          <t>Uttam Sugar Mills Share Price: Technical, Fundamental View - Univest</t>
+        </is>
+      </c>
+      <c r="P706" t="inlineStr">
+        <is>
+          <t>Uttam Sugar Mills Ltd. Share Price Today Near 52-Week High - Univest</t>
+        </is>
+      </c>
+      <c r="Q706" t="inlineStr">
+        <is>
+          <t>Uttam Sugar Mills Q1 Net Profit Plummets 94.69% YoY to ₹85 lakh - Sahi</t>
+        </is>
+      </c>
+    </row>
+    <row r="707">
+      <c r="A707" t="inlineStr">
+        <is>
+          <t>2026-09-04 12:50:03 IST</t>
+        </is>
+      </c>
+      <c r="B707" t="n">
+        <v>6</v>
+      </c>
+      <c r="C707" t="inlineStr">
+        <is>
+          <t>RNBDENIMS.NS</t>
+        </is>
+      </c>
+      <c r="D707" t="inlineStr">
+        <is>
+          <t>R&amp;B Denims Limited</t>
+        </is>
+      </c>
+      <c r="E707" t="n">
+        <v>10.8100004196167</v>
+      </c>
+      <c r="F707" t="n">
+        <v>10.8100004196167</v>
+      </c>
+      <c r="G707" t="n">
+        <v>10.27000045776367</v>
+      </c>
+      <c r="H707" t="n">
+        <v>10.27000045776367</v>
+      </c>
+      <c r="I707" t="n">
+        <v>10.8100004196167</v>
+      </c>
+      <c r="J707" t="n">
+        <v>10.27000045776367</v>
+      </c>
+      <c r="K707" t="n">
+        <v>406522</v>
+      </c>
+      <c r="L707" t="n">
+        <v>-5</v>
+      </c>
+      <c r="M707" t="inlineStr">
+        <is>
+          <t>RNBDENIMS Stock Price and Chart — NSE:RNBDENIMS - TradingView</t>
+        </is>
+      </c>
+      <c r="N707" t="inlineStr">
+        <is>
+          <t>R&amp;B Denims (RNBDENIMS.NS) Slips 1.5%: Testing Key Support Near ₹9.89 - Defined Outcome ETF - vinanet.vn</t>
+        </is>
+      </c>
+      <c r="O707" t="inlineStr">
+        <is>
+          <t>R&amp;B Denims Limited Allots Bonus Shares in 1:2 Ratio with Record Date April 03, 2026 - scanx.trade</t>
+        </is>
+      </c>
+      <c r="P707" t="inlineStr">
+        <is>
+          <t>R&amp;B Denims (RNBDENIMS.NS) Slips 1.5%: Testing Key Support Near ₹9.89 - Defined Outcome ETF - vinanet.vn</t>
+        </is>
+      </c>
+      <c r="Q707" t="inlineStr">
+        <is>
+          <t>R&amp;B Denims Limited Sets Record Date April 3, 2026 for 1:2 Bonus Equity Shares - scanx.trade</t>
+        </is>
+      </c>
+    </row>
+    <row r="708">
+      <c r="A708" t="inlineStr">
+        <is>
+          <t>2026-09-04 12:50:03 IST</t>
+        </is>
+      </c>
+      <c r="B708" t="n">
+        <v>7</v>
+      </c>
+      <c r="C708" t="inlineStr">
+        <is>
+          <t>PAR.NS</t>
+        </is>
+      </c>
+      <c r="D708" t="inlineStr">
+        <is>
+          <t>Par Drugs And Chemicals Limited</t>
+        </is>
+      </c>
+      <c r="E708" t="n">
+        <v>168</v>
+      </c>
+      <c r="F708" t="n">
+        <v>168</v>
+      </c>
+      <c r="G708" t="n">
+        <v>156.7100067138672</v>
+      </c>
+      <c r="H708" t="n">
+        <v>156.7100067138672</v>
+      </c>
+      <c r="I708" t="n">
+        <v>164.9499969482422</v>
+      </c>
+      <c r="J708" t="n">
+        <v>156.7100067138672</v>
+      </c>
+      <c r="K708" t="n">
+        <v>9717</v>
+      </c>
+      <c r="L708" t="n">
+        <v>-5</v>
+      </c>
+      <c r="M708" t="inlineStr">
+        <is>
+          <t>Alliance Select Foods International Announces Equity Restructuring For Common Shares Par Value Reduction To 0.10 Pesos Per Share - TradingView</t>
+        </is>
+      </c>
+      <c r="N708" t="inlineStr">
+        <is>
+          <t>Par Pacific (NYSE: PARR) officer lines up new stock sale - Stock Titan</t>
+        </is>
+      </c>
+      <c r="O708" t="inlineStr">
+        <is>
+          <t>Symbiotec Pharmalab makes tepid market debut, lists at par with IPO price - Business Standard</t>
+        </is>
+      </c>
+      <c r="P708" t="inlineStr">
+        <is>
+          <t>Strategy’s (MSTR) STRC remains below par as Strive’s SATA attracts investors - coindesk.com</t>
+        </is>
+      </c>
+      <c r="Q708" t="inlineStr">
+        <is>
+          <t>GFL Environmental Inc. Subordinate voting shares no par value - ADR Shareholding Pattern – Promoters, FIIs &amp; DIIs - Value Research</t>
+        </is>
+      </c>
+    </row>
+    <row r="709">
+      <c r="A709" t="inlineStr">
+        <is>
+          <t>2026-09-04 12:50:03 IST</t>
+        </is>
+      </c>
+      <c r="B709" t="n">
+        <v>8</v>
+      </c>
+      <c r="C709" t="inlineStr">
+        <is>
+          <t>HIKAL.NS</t>
+        </is>
+      </c>
+      <c r="D709" t="inlineStr">
+        <is>
+          <t>Hikal Limited</t>
+        </is>
+      </c>
+      <c r="E709" t="n">
+        <v>234</v>
+      </c>
+      <c r="F709" t="n">
+        <v>236.7400054931641</v>
+      </c>
+      <c r="G709" t="n">
+        <v>226.1999969482422</v>
+      </c>
+      <c r="H709" t="n">
+        <v>230.0200042724609</v>
+      </c>
+      <c r="I709" t="n">
+        <v>240.3600006103516</v>
+      </c>
+      <c r="J709" t="n">
+        <v>230.0200042724609</v>
+      </c>
+      <c r="K709" t="n">
+        <v>3668424</v>
+      </c>
+      <c r="L709" t="n">
+        <v>-4.3</v>
+      </c>
+      <c r="M709" t="inlineStr">
+        <is>
+          <t>Hikal Ltd. Share Price Rise: Price Action and Fundamentals - Univest</t>
+        </is>
+      </c>
+      <c r="N709" t="inlineStr">
+        <is>
+          <t>Hikal Ltd. Share Price Rise: Price Action and Fundamentals - Univest</t>
+        </is>
+      </c>
+      <c r="O709" t="inlineStr">
+        <is>
+          <t>Don't Race Out To Buy Hikal Limited (NSE:HIKAL) Just Because It's Going Ex-Dividend - simplywall.st</t>
+        </is>
+      </c>
+      <c r="P709" t="inlineStr">
+        <is>
+          <t>Hikal files FY26 sustainability report with ESG metrics - scanx.trade</t>
+        </is>
+      </c>
+      <c r="Q709" t="inlineStr">
+        <is>
+          <t>Hikal Q1 Consolidated Net Loss Narrows to ₹7.4 Crore; Revenue At ₹403 Crore - Sahi</t>
+        </is>
+      </c>
+    </row>
+    <row r="710">
+      <c r="A710" t="inlineStr">
+        <is>
+          <t>2026-09-04 12:50:03 IST</t>
+        </is>
+      </c>
+      <c r="B710" t="n">
+        <v>9</v>
+      </c>
+      <c r="C710" t="inlineStr">
+        <is>
+          <t>DWARKESH.NS</t>
+        </is>
+      </c>
+      <c r="D710" t="inlineStr">
+        <is>
+          <t>Dwarikesh Sugar Industries Limited</t>
+        </is>
+      </c>
+      <c r="E710" t="n">
+        <v>49.40999984741211</v>
+      </c>
+      <c r="F710" t="n">
+        <v>49.40999984741211</v>
+      </c>
+      <c r="G710" t="n">
+        <v>47.13999938964844</v>
+      </c>
+      <c r="H710" t="n">
+        <v>47.25</v>
+      </c>
+      <c r="I710" t="n">
+        <v>49.31999969482422</v>
+      </c>
+      <c r="J710" t="n">
+        <v>47.25</v>
+      </c>
+      <c r="K710" t="n">
+        <v>1456612</v>
+      </c>
+      <c r="L710" t="n">
+        <v>-4.2</v>
+      </c>
+      <c r="M710" t="inlineStr">
+        <is>
+          <t>Dwarikesh Sugar Industries: Promoter Gautam Morarka Increases Stake to 15.22% - scanx.trade</t>
+        </is>
+      </c>
+      <c r="N710" t="inlineStr">
+        <is>
+          <t>AI: The Tech ‘Go-Direct’ Ethos Meets Grassroots AI Revolt. AI-RTZ #1198 - AI: Reset to Zero</t>
+        </is>
+      </c>
+      <c r="O710" t="inlineStr">
+        <is>
+          <t>Dwarikesh Sugar Industries Share Price Rises 8.3% Today - Univest</t>
+        </is>
+      </c>
+      <c r="P710" t="inlineStr">
+        <is>
+          <t>Dwarkesh Patels’s wildly popular but dangerously misleading account of the OpenAI Hugging Face incident - Marcus on AI | Substack</t>
+        </is>
+      </c>
+      <c r="Q710" t="inlineStr">
+        <is>
+          <t>OpenAI-Hugging Face controversy deepens as experts debate Dwarkesh Patel's 'AI civilisation' claims - Moneycontrol.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="711">
+      <c r="A711" t="inlineStr">
+        <is>
+          <t>2026-09-04 12:50:03 IST</t>
+        </is>
+      </c>
+      <c r="B711" t="n">
+        <v>10</v>
+      </c>
+      <c r="C711" t="inlineStr">
+        <is>
+          <t>SYNCOMF.NS</t>
+        </is>
+      </c>
+      <c r="D711" t="inlineStr">
+        <is>
+          <t>Syncom Formulations (India) Limited</t>
+        </is>
+      </c>
+      <c r="E711" t="n">
+        <v>20.93000030517578</v>
+      </c>
+      <c r="F711" t="n">
+        <v>21.8799991607666</v>
+      </c>
+      <c r="G711" t="n">
+        <v>20.04999923706055</v>
+      </c>
+      <c r="H711" t="n">
+        <v>20.54000091552734</v>
+      </c>
+      <c r="I711" t="n">
+        <v>21.36000061035156</v>
+      </c>
+      <c r="J711" t="n">
+        <v>20.54000091552734</v>
+      </c>
+      <c r="K711" t="n">
+        <v>11553212</v>
+      </c>
+      <c r="L711" t="n">
+        <v>-3.84</v>
+      </c>
+      <c r="M711" t="inlineStr">
+        <is>
+          <t>Here's Why Syncom Formulations (India) (NSE:SYNCOMF) Has Caught The Eye Of Investors - simplywall.st</t>
+        </is>
+      </c>
+      <c r="N711" t="inlineStr">
+        <is>
+          <t>Syncom Formulations Sees Minor Pullback, Holds Above Key Support at ₹13.27 - Last Point Support - vinanet.vn</t>
+        </is>
+      </c>
+      <c r="O711" t="inlineStr">
+        <is>
+          <t>Syncom Formulations (India) Limited Acquires Commercial Property from HDFC Bank Ltd for ₹57,26,00,000 - scanx.trade</t>
+        </is>
+      </c>
+      <c r="P711" t="inlineStr">
+        <is>
+          <t>SYNCOMF.NS Q2 2025 Earnings: Robust Revenue Growth of 76% YoY Despite Marginal Stock Dip - Tax Rate Impact - vinanet.vn</t>
+        </is>
+      </c>
+      <c r="Q711" t="inlineStr">
+        <is>
+          <t>SYNCOMF Stock Price and Chart — NSE:SYNCOMF - TradingView</t>
+        </is>
+      </c>
+    </row>
+    <row r="712">
+      <c r="A712" t="inlineStr">
+        <is>
+          <t>2026-09-04 12:50:03 IST</t>
+        </is>
+      </c>
+      <c r="B712" t="n">
+        <v>11</v>
+      </c>
+      <c r="C712" t="inlineStr">
+        <is>
+          <t>DBOL.NS</t>
+        </is>
+      </c>
+      <c r="D712" t="inlineStr">
+        <is>
+          <t>Dhampur Bio Organics Limited</t>
+        </is>
+      </c>
+      <c r="E712" t="n">
+        <v>128.9600067138672</v>
+      </c>
+      <c r="F712" t="n">
+        <v>128.9600067138672</v>
+      </c>
+      <c r="G712" t="n">
+        <v>124</v>
+      </c>
+      <c r="H712" t="n">
+        <v>124.6900024414062</v>
+      </c>
+      <c r="I712" t="n">
+        <v>129.6399993896484</v>
+      </c>
+      <c r="J712" t="n">
+        <v>124.6900024414062</v>
+      </c>
+      <c r="K712" t="n">
+        <v>181551</v>
+      </c>
+      <c r="L712" t="n">
+        <v>-3.82</v>
+      </c>
+      <c r="M712" t="inlineStr">
+        <is>
+          <t>Dhampur Bio Organics promoters confirm no share encumbrance in FY26 - scanx.trade</t>
+        </is>
+      </c>
+      <c r="N712" t="inlineStr">
+        <is>
+          <t>Dhampur Bio Organics promoters confirm no share encumbrance in FY26 - scanx.trade</t>
+        </is>
+      </c>
+      <c r="O712" t="inlineStr">
+        <is>
+          <t>Dhampur Bio Organics Share Price, Valuation, Sector View - Univest</t>
+        </is>
+      </c>
+      <c r="P712" t="inlineStr">
+        <is>
+          <t>Sonitron acquires 40,000 Dhampur Bio Organics shares in open market - scanx.trade</t>
+        </is>
+      </c>
+      <c r="Q712" t="inlineStr">
+        <is>
+          <t>PHAT Q2 2026 Earnings: Narrower Loss Beats Estimates, Shares Gain 4.36% - Earnings Yield Spread - vinanet.vn</t>
+        </is>
+      </c>
+    </row>
+    <row r="713">
+      <c r="A713" t="inlineStr">
+        <is>
+          <t>2026-09-04 12:50:03 IST</t>
+        </is>
+      </c>
+      <c r="B713" t="n">
+        <v>12</v>
+      </c>
+      <c r="C713" t="inlineStr">
+        <is>
+          <t>ATHERENERG.NS</t>
+        </is>
+      </c>
+      <c r="D713" t="inlineStr">
+        <is>
+          <t>Ather Energy Limited</t>
+        </is>
+      </c>
+      <c r="E713" t="n">
+        <v>1644</v>
+      </c>
+      <c r="F713" t="n">
+        <v>1644.5</v>
+      </c>
+      <c r="G713" t="n">
+        <v>1573.5</v>
+      </c>
+      <c r="H713" t="n">
+        <v>1576.5</v>
+      </c>
+      <c r="I713" t="n">
+        <v>1638.900024414062</v>
+      </c>
+      <c r="J713" t="n">
+        <v>1576.5</v>
+      </c>
+      <c r="K713" t="n">
+        <v>3222709</v>
+      </c>
+      <c r="L713" t="n">
+        <v>-3.81</v>
+      </c>
+      <c r="M713" t="inlineStr">
+        <is>
+          <t>ATHER ENERGY LIMITED Share Price - Live NSE: ATHERENERG Stock Price &amp; Chart - Upstox</t>
+        </is>
+      </c>
+      <c r="N713" t="inlineStr">
+        <is>
+          <t>ATHER ENERGY Share Price: Today's 2.45% Decline - Univest</t>
+        </is>
+      </c>
+      <c r="O713" t="inlineStr">
+        <is>
+          <t>When Can We Expect A Profit From Ather Energy Limited (NSE:ATHERENERG)? - simplywall.st</t>
+        </is>
+      </c>
+      <c r="P713" t="inlineStr">
+        <is>
+          <t>Ather Energy shares climb to all-time high, rising 17% above Hero MotoCorp block price - TechStock²</t>
+        </is>
+      </c>
+      <c r="Q713" t="inlineStr">
+        <is>
+          <t>Ather Energy Share Price Rise: Market Cap and Valuation - Univest</t>
+        </is>
+      </c>
+    </row>
+    <row r="714">
+      <c r="A714" t="inlineStr">
+        <is>
+          <t>2026-09-04 12:50:03 IST</t>
+        </is>
+      </c>
+      <c r="B714" t="n">
+        <v>13</v>
+      </c>
+      <c r="C714" t="inlineStr">
+        <is>
+          <t>EMIL.NS</t>
+        </is>
+      </c>
+      <c r="D714" t="inlineStr">
+        <is>
+          <t>Electronics Mart India Limited</t>
+        </is>
+      </c>
+      <c r="E714" t="n">
+        <v>175.3999938964844</v>
+      </c>
+      <c r="F714" t="n">
+        <v>176.6699981689453</v>
+      </c>
+      <c r="G714" t="n">
+        <v>168.9299926757812</v>
+      </c>
+      <c r="H714" t="n">
+        <v>169.7200012207031</v>
+      </c>
+      <c r="I714" t="n">
+        <v>176.1600036621094</v>
+      </c>
+      <c r="J714" t="n">
+        <v>169.7200012207031</v>
+      </c>
+      <c r="K714" t="n">
+        <v>753170</v>
+      </c>
+      <c r="L714" t="n">
+        <v>-3.66</v>
+      </c>
+      <c r="M714" t="inlineStr">
+        <is>
+          <t>Pentagon official overseeing military AI sold millions worth of stock in AI firm - The Guardian</t>
+        </is>
+      </c>
+      <c r="N714" t="inlineStr">
+        <is>
+          <t>Top Pentagon AI Official Sold Millions in Perplexity Stock, Disclosures Show - Decrypt</t>
+        </is>
+      </c>
+      <c r="O714" t="inlineStr">
+        <is>
+          <t>Electronics Mart India Share Price Within 2% of 52W High - Univest</t>
+        </is>
+      </c>
+      <c r="P714" t="inlineStr">
+        <is>
+          <t>Most Active Equities, August 10, 2026, 3:30 PM IST - hdfcsky.com</t>
+        </is>
+      </c>
+      <c r="Q714" t="inlineStr">
+        <is>
+          <t>Earnings Update: Here's Why Analysts Just Lifted Their Electronics Mart India Limited (NSE:EMIL) Price Target To ₹186 - simplywall.st</t>
+        </is>
+      </c>
+    </row>
+    <row r="715">
+      <c r="A715" t="inlineStr">
+        <is>
+          <t>2026-09-04 12:50:03 IST</t>
+        </is>
+      </c>
+      <c r="B715" t="n">
+        <v>14</v>
+      </c>
+      <c r="C715" t="inlineStr">
+        <is>
+          <t>FIVESTAR.NS</t>
+        </is>
+      </c>
+      <c r="D715" t="inlineStr">
+        <is>
+          <t>Five-Star Business Finance Limited</t>
+        </is>
+      </c>
+      <c r="E715" t="n">
+        <v>538</v>
+      </c>
+      <c r="F715" t="n">
+        <v>538</v>
+      </c>
+      <c r="G715" t="n">
+        <v>512.5</v>
+      </c>
+      <c r="H715" t="n">
+        <v>515.25</v>
+      </c>
+      <c r="I715" t="n">
+        <v>534.5999755859375</v>
+      </c>
+      <c r="J715" t="n">
+        <v>515.25</v>
+      </c>
+      <c r="K715" t="n">
+        <v>554474</v>
+      </c>
+      <c r="L715" t="n">
+        <v>-3.62</v>
+      </c>
+      <c r="M715" t="inlineStr">
+        <is>
+          <t>Five-Star Business Finance Limited Appoints Sreeram Ranganathan Iyer as A Non­ Executive Independent Director, Effective July 25, 2026 - marketscreener.com</t>
+        </is>
+      </c>
+      <c r="N715" t="inlineStr">
+        <is>
+          <t>Five-Star Business Finance Limited Appoints Sreeram Ranganathan Iyer as A Non­ Executive Independent Director, Effective July 25, 2026 - marketscreener.com</t>
+        </is>
+      </c>
+      <c r="O715" t="inlineStr">
+        <is>
+          <t>Five Star Business Finance Submits Business Responsibility and Sustainability Report for FY 2025-26 - scanx.trade</t>
+        </is>
+      </c>
+      <c r="P715" t="inlineStr"/>
+      <c r="Q715" t="inlineStr"/>
+    </row>
+    <row r="716">
+      <c r="A716" t="inlineStr">
+        <is>
+          <t>2026-09-04 12:50:03 IST</t>
+        </is>
+      </c>
+      <c r="B716" t="n">
+        <v>15</v>
+      </c>
+      <c r="C716" t="inlineStr">
+        <is>
+          <t>EBGNG.NS</t>
+        </is>
+      </c>
+      <c r="D716" t="inlineStr">
+        <is>
+          <t>GNG Electronics Limited</t>
+        </is>
+      </c>
+      <c r="E716" t="n">
+        <v>622</v>
+      </c>
+      <c r="F716" t="n">
+        <v>633.4000244140625</v>
+      </c>
+      <c r="G716" t="n">
+        <v>598</v>
+      </c>
+      <c r="H716" t="n">
+        <v>600</v>
+      </c>
+      <c r="I716" t="n">
+        <v>622.0999755859375</v>
+      </c>
+      <c r="J716" t="n">
+        <v>600</v>
+      </c>
+      <c r="K716" t="n">
+        <v>572288</v>
+      </c>
+      <c r="L716" t="n">
+        <v>-3.55</v>
+      </c>
+      <c r="M716" t="inlineStr">
+        <is>
+          <t>Should You Be Adding GNG Electronics (NSE:EBGNG) To Your Watchlist Today? - simplywall.st</t>
+        </is>
+      </c>
+      <c r="N716" t="inlineStr">
+        <is>
+          <t>GNG Electronics Schedules 20th AGM and Releases FY 2025-26 Annual Report - TipRanks</t>
+        </is>
+      </c>
+      <c r="O716" t="inlineStr">
+        <is>
+          <t>GNG Electronics Limited (NSE: EBGNG) Stock Price, News &amp; Analysis - Kalkine</t>
+        </is>
+      </c>
+      <c r="P716" t="inlineStr">
+        <is>
+          <t>GNG Electronics reports 32% revenue surge in Q1FY27 on margin expansion - scanx.trade</t>
+        </is>
+      </c>
+      <c r="Q716" t="inlineStr">
+        <is>
+          <t>GNG Electronics Schedules 20th AGM and Releases FY 2025-26 Annual Report - TipRanks</t>
+        </is>
+      </c>
+    </row>
+    <row r="717">
+      <c r="A717" t="inlineStr">
+        <is>
+          <t>2026-09-04 12:50:03 IST</t>
+        </is>
+      </c>
+      <c r="B717" t="n">
+        <v>16</v>
+      </c>
+      <c r="C717" t="inlineStr">
+        <is>
+          <t>MACPOWER.NS</t>
+        </is>
+      </c>
+      <c r="D717" t="inlineStr">
+        <is>
+          <t>Macpower CNC Machines Limited</t>
+        </is>
+      </c>
+      <c r="E717" t="n">
+        <v>1955.800048828125</v>
+      </c>
+      <c r="F717" t="n">
+        <v>1960</v>
+      </c>
+      <c r="G717" t="n">
+        <v>1868.300048828125</v>
+      </c>
+      <c r="H717" t="n">
+        <v>1878.599975585938</v>
+      </c>
+      <c r="I717" t="n">
+        <v>1944.099975585938</v>
+      </c>
+      <c r="J717" t="n">
+        <v>1878.599975585938</v>
+      </c>
+      <c r="K717" t="n">
+        <v>23752</v>
+      </c>
+      <c r="L717" t="n">
+        <v>-3.37</v>
+      </c>
+      <c r="M717" t="inlineStr">
+        <is>
+          <t>Macpower CNC Machines Ltd is Rated Hold - MarketsMojo</t>
+        </is>
+      </c>
+      <c r="N717" t="inlineStr">
+        <is>
+          <t>Macpower CNC Machines Ltd is Rated Hold - MarketsMojo</t>
+        </is>
+      </c>
+      <c r="O717" t="inlineStr">
+        <is>
+          <t>Rs 21,932 cr opportunity: 2 stocks powering India’s next manufacturing wave - financialexpress.com</t>
+        </is>
+      </c>
+      <c r="P717" t="inlineStr"/>
+      <c r="Q717" t="inlineStr"/>
+    </row>
+    <row r="718">
+      <c r="A718" t="inlineStr">
+        <is>
+          <t>2026-09-04 12:50:03 IST</t>
+        </is>
+      </c>
+      <c r="B718" t="n">
+        <v>17</v>
+      </c>
+      <c r="C718" t="inlineStr">
+        <is>
+          <t>GRAVITA.NS</t>
+        </is>
+      </c>
+      <c r="D718" t="inlineStr">
+        <is>
+          <t>Gravita India Limited</t>
+        </is>
+      </c>
+      <c r="E718" t="n">
+        <v>1684.800048828125</v>
+      </c>
+      <c r="F718" t="n">
+        <v>1696.599975585938</v>
+      </c>
+      <c r="G718" t="n">
+        <v>1626.900024414062</v>
+      </c>
+      <c r="H718" t="n">
+        <v>1630</v>
+      </c>
+      <c r="I718" t="n">
+        <v>1684.800048828125</v>
+      </c>
+      <c r="J718" t="n">
+        <v>1630</v>
+      </c>
+      <c r="K718" t="n">
+        <v>255828</v>
+      </c>
+      <c r="L718" t="n">
+        <v>-3.25</v>
+      </c>
+      <c r="M718" t="inlineStr">
+        <is>
+          <t>Gravita India closes books for AGM from Sep 22 to Sep 28 - scanx.trade</t>
+        </is>
+      </c>
+      <c r="N718" t="inlineStr">
+        <is>
+          <t>Gravita India closes books for AGM from Sep 22 to Sep 28 - scanx.trade</t>
+        </is>
+      </c>
+      <c r="O718" t="inlineStr">
+        <is>
+          <t>Gravita India approves ₹100 Cr corporate guarantee for subsidiary RMIL - scanx.trade</t>
+        </is>
+      </c>
+      <c r="P718" t="inlineStr">
+        <is>
+          <t>Gravita India to add 59,200 MTPA copper recycling capacity at Mundra with ₹64 crore capex - CNBC TV18</t>
+        </is>
+      </c>
+      <c r="Q718" t="inlineStr">
+        <is>
+          <t>Gravita India schedules physical investor meet in Jaipur on Sep 2 - scanx.trade</t>
+        </is>
+      </c>
+    </row>
+    <row r="719">
+      <c r="A719" t="inlineStr">
+        <is>
+          <t>2026-09-04 12:50:03 IST</t>
+        </is>
+      </c>
+      <c r="B719" t="n">
+        <v>18</v>
+      </c>
+      <c r="C719" t="inlineStr">
+        <is>
+          <t>WEL.NS</t>
+        </is>
+      </c>
+      <c r="D719" t="inlineStr">
+        <is>
+          <t>Wonder Electricals Limited</t>
+        </is>
+      </c>
+      <c r="E719" t="n">
+        <v>79.25</v>
+      </c>
+      <c r="F719" t="n">
+        <v>79.25</v>
+      </c>
+      <c r="G719" t="n">
+        <v>75.41000366210938</v>
+      </c>
+      <c r="H719" t="n">
+        <v>76.83000183105469</v>
+      </c>
+      <c r="I719" t="n">
+        <v>79.37000274658203</v>
+      </c>
+      <c r="J719" t="n">
+        <v>76.83000183105469</v>
+      </c>
+      <c r="K719" t="n">
+        <v>914005</v>
+      </c>
+      <c r="L719" t="n">
+        <v>-3.2</v>
+      </c>
+      <c r="M719" t="inlineStr">
+        <is>
+          <t>Integrated Wellness Acquisition Corp (WEL) Peer Comparison – Compare with Others - Value Research</t>
+        </is>
+      </c>
+      <c r="N719" t="inlineStr">
+        <is>
+          <t>Integrated Wellness Acquisition Corp (WEL) Peer Comparison – Compare with Others - Value Research</t>
+        </is>
+      </c>
+      <c r="O719" t="inlineStr">
+        <is>
+          <t>Wonder Electricals Share Price Today After Sharp Fall - Univest</t>
+        </is>
+      </c>
+      <c r="P719" t="inlineStr">
+        <is>
+          <t>Btab uses artificial intelligence to link global manufacturers with U.S. business buyers - Stock Titan</t>
+        </is>
+      </c>
+      <c r="Q719" t="inlineStr">
+        <is>
+          <t>Wonder Electricals Share Price Today: Market Cap and P/E - Univest</t>
+        </is>
+      </c>
+    </row>
+    <row r="720">
+      <c r="A720" t="inlineStr">
+        <is>
+          <t>2026-09-04 12:50:03 IST</t>
+        </is>
+      </c>
+      <c r="B720" t="n">
+        <v>19</v>
+      </c>
+      <c r="C720" t="inlineStr">
+        <is>
+          <t>PONNIERODE.NS</t>
+        </is>
+      </c>
+      <c r="D720" t="inlineStr">
+        <is>
+          <t>Ponni Sugars (Erode) Limited</t>
+        </is>
+      </c>
+      <c r="E720" t="n">
+        <v>402.8999938964844</v>
+      </c>
+      <c r="F720" t="n">
+        <v>402.8999938964844</v>
+      </c>
+      <c r="G720" t="n">
+        <v>385</v>
+      </c>
+      <c r="H720" t="n">
+        <v>386</v>
+      </c>
+      <c r="I720" t="n">
+        <v>398.6499938964844</v>
+      </c>
+      <c r="J720" t="n">
+        <v>386</v>
+      </c>
+      <c r="K720" t="n">
+        <v>17691</v>
+      </c>
+      <c r="L720" t="n">
+        <v>-3.17</v>
+      </c>
+      <c r="M720" t="inlineStr">
+        <is>
+          <t>Ponni Sugars Share Price Today: Price Rise and Analysis - Univest</t>
+        </is>
+      </c>
+      <c r="N720" t="inlineStr">
+        <is>
+          <t>NXG Infrastructure Income Fund Holds Ground at $56.30 as Market Waits for Direction - Fear Greed Extreme - vinanet.vn</t>
+        </is>
+      </c>
+      <c r="O720" t="inlineStr">
+        <is>
+          <t>NXG Infrastructure Income Fund Holds Ground at $56.30 as Market Waits for Direction - Fear Greed Extreme - vinanet.vn</t>
+        </is>
+      </c>
+      <c r="P720" t="inlineStr"/>
+      <c r="Q720" t="inlineStr"/>
+    </row>
+    <row r="721">
+      <c r="A721" t="inlineStr">
+        <is>
+          <t>2026-09-04 12:50:03 IST</t>
+        </is>
+      </c>
+      <c r="B721" t="n">
+        <v>20</v>
+      </c>
+      <c r="C721" t="inlineStr">
+        <is>
+          <t>POWERMECH.NS</t>
+        </is>
+      </c>
+      <c r="D721" t="inlineStr">
+        <is>
+          <t>Power Mech Projects Limited</t>
+        </is>
+      </c>
+      <c r="E721" t="n">
+        <v>2399.89990234375</v>
+      </c>
+      <c r="F721" t="n">
+        <v>2416</v>
+      </c>
+      <c r="G721" t="n">
+        <v>2331</v>
+      </c>
+      <c r="H721" t="n">
+        <v>2334</v>
+      </c>
+      <c r="I721" t="n">
+        <v>2399.800048828125</v>
+      </c>
+      <c r="J721" t="n">
+        <v>2334</v>
+      </c>
+      <c r="K721" t="n">
+        <v>37175</v>
+      </c>
+      <c r="L721" t="n">
+        <v>-2.74</v>
+      </c>
+      <c r="M721" t="inlineStr">
+        <is>
+          <t>Power Mech Projects Limited announces Annual dividend, payable on October 17, 2026 - marketscreener.com</t>
+        </is>
+      </c>
+      <c r="N721" t="inlineStr">
+        <is>
+          <t>Power Mech Projects Limited announces Annual dividend, payable on October 17, 2026 - marketscreener.com</t>
+        </is>
+      </c>
+      <c r="O721" t="inlineStr">
+        <is>
+          <t>Power Mech Projects Publishes AGM Notice and E-Voting Details in Newspapers - TipRanks</t>
+        </is>
+      </c>
+      <c r="P721" t="inlineStr"/>
+      <c r="Q721" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/NEWS_Daily_Report/output/history/NEWS_Daily_Report_History.xlsx
+++ b/NEWS_Daily_Report/output/history/NEWS_Daily_Report_History.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q421"/>
+  <dimension ref="A1:Q441"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21.42578125" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -26972,9 +26972,6 @@
           <t>Responsive Industries board to consider equity share buyback on Aug 14 - scanx.trade</t>
         </is>
       </c>
-      <c r="O404" t="inlineStr"/>
-      <c r="P404" t="inlineStr"/>
-      <c r="Q404" t="inlineStr"/>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
@@ -27029,9 +27026,6 @@
           <t>Lancor Holdings Ltd. Share Price News and Stock Analysis - Univest</t>
         </is>
       </c>
-      <c r="O405" t="inlineStr"/>
-      <c r="P405" t="inlineStr"/>
-      <c r="Q405" t="inlineStr"/>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
@@ -27086,9 +27080,6 @@
           <t>Marsons Limited Receives PGCIL Vendor Approval for Supply of Power Transformers - scanx.trade</t>
         </is>
       </c>
-      <c r="O406" t="inlineStr"/>
-      <c r="P406" t="inlineStr"/>
-      <c r="Q406" t="inlineStr"/>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
@@ -27143,9 +27134,6 @@
           <t>Birla Precision Technologies Ltd. (BIRLAPREC) Share Price Rises 10.68% Today - Univest</t>
         </is>
       </c>
-      <c r="O407" t="inlineStr"/>
-      <c r="P407" t="inlineStr"/>
-      <c r="Q407" t="inlineStr"/>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
@@ -27269,9 +27257,6 @@
           <t>Advit Jewels Q1 Results: Earnings call audio now available online - scanx.trade</t>
         </is>
       </c>
-      <c r="O409" t="inlineStr"/>
-      <c r="P409" t="inlineStr"/>
-      <c r="Q409" t="inlineStr"/>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
@@ -27612,7 +27597,6 @@
           <t>Welspun Enterprises Ltd. Share Price at Fresh 52-Week High - Univest</t>
         </is>
       </c>
-      <c r="Q414" t="inlineStr"/>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
@@ -27746,7 +27730,6 @@
           <t>Angel One Allots 3.49 Lakh Shares Under Employee Incentive Plan - TipRanks</t>
         </is>
       </c>
-      <c r="Q416" t="inlineStr"/>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
@@ -27806,8 +27789,6 @@
           <t>SML Mahindra Posts 40% Surge in August Vehicle Sales - TipRanks</t>
         </is>
       </c>
-      <c r="P417" t="inlineStr"/>
-      <c r="Q417" t="inlineStr"/>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
@@ -27872,7 +27853,6 @@
           <t>Indorama Ventures Public Company Limited 2026 Q2 - Results - Earnings Call Presentation - Seeking Alpha</t>
         </is>
       </c>
-      <c r="Q418" t="inlineStr"/>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
@@ -28065,9 +28045,1294 @@
           <t>PW Gyaan-E Finance | 33+ Courses, Guides &amp; 200+ Skill Courses - PW</t>
         </is>
       </c>
-      <c r="O421" t="inlineStr"/>
-      <c r="P421" t="inlineStr"/>
-      <c r="Q421" t="inlineStr"/>
+    </row>
+    <row r="422">
+      <c r="A422" t="inlineStr">
+        <is>
+          <t>2026-09-04 20:18:15 IST</t>
+        </is>
+      </c>
+      <c r="B422" t="n">
+        <v>1</v>
+      </c>
+      <c r="C422" t="inlineStr">
+        <is>
+          <t>XTRANET.NS</t>
+        </is>
+      </c>
+      <c r="D422" t="inlineStr">
+        <is>
+          <t>Xtranet Technologies Limited</t>
+        </is>
+      </c>
+      <c r="E422" t="n">
+        <v>197.1999969482422</v>
+      </c>
+      <c r="F422" t="n">
+        <v>234.2400054931641</v>
+      </c>
+      <c r="G422" t="n">
+        <v>193.1100006103516</v>
+      </c>
+      <c r="H422" t="n">
+        <v>234.2400054931641</v>
+      </c>
+      <c r="I422" t="n">
+        <v>195.1999969482422</v>
+      </c>
+      <c r="J422" t="n">
+        <v>234.2400054931641</v>
+      </c>
+      <c r="K422" t="n">
+        <v>5584584</v>
+      </c>
+      <c r="L422" t="n">
+        <v>20</v>
+      </c>
+      <c r="M422" t="inlineStr">
+        <is>
+          <t>XTRANET TECHNOLOGIES LTD Share Price - Upstox</t>
+        </is>
+      </c>
+      <c r="N422" t="inlineStr">
+        <is>
+          <t>Xtranet Technologies Ltd (XTRANET) Share Price - businesstoday.in</t>
+        </is>
+      </c>
+      <c r="O422" t="inlineStr">
+        <is>
+          <t>Xtranet Technologies Ltd (XTRANET) Share Price - businesstoday.in</t>
+        </is>
+      </c>
+      <c r="P422" t="inlineStr">
+        <is>
+          <t>XTRANET Share Price Today - XTRANET TECHNOLOGIES LTD Stock Price Live NSE/BSE - Univest</t>
+        </is>
+      </c>
+      <c r="Q422" t="inlineStr">
+        <is>
+          <t>Stocks to Watch Today: BSE, United Spirits, Hyundai Motor, XtraNet Tech, Autoline Industries, EMS, Ramco... - Moneycontrol.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="inlineStr">
+        <is>
+          <t>2026-09-04 20:18:15 IST</t>
+        </is>
+      </c>
+      <c r="B423" t="n">
+        <v>2</v>
+      </c>
+      <c r="C423" t="inlineStr">
+        <is>
+          <t>JINDWORLD.NS</t>
+        </is>
+      </c>
+      <c r="D423" t="inlineStr">
+        <is>
+          <t>Jindal Worldwide Limited</t>
+        </is>
+      </c>
+      <c r="E423" t="n">
+        <v>49.66999816894531</v>
+      </c>
+      <c r="F423" t="n">
+        <v>57.77999877929688</v>
+      </c>
+      <c r="G423" t="n">
+        <v>49.02000045776367</v>
+      </c>
+      <c r="H423" t="n">
+        <v>57.5099983215332</v>
+      </c>
+      <c r="I423" t="n">
+        <v>48.15000152587891</v>
+      </c>
+      <c r="J423" t="n">
+        <v>57.5099983215332</v>
+      </c>
+      <c r="K423" t="n">
+        <v>187907453</v>
+      </c>
+      <c r="L423" t="n">
+        <v>19.44</v>
+      </c>
+      <c r="M423" t="inlineStr">
+        <is>
+          <t>Jindal Worldwide (JINDWORLD.NS) Edges Higher at ₹38.31; Key Support and Resistance in Focus - Dividend Growth Stocks - siam.in</t>
+        </is>
+      </c>
+      <c r="N423" t="inlineStr">
+        <is>
+          <t>Most Active Equities on September 4, 2026 at 4:00 PM - HDFC Sky</t>
+        </is>
+      </c>
+      <c r="O423" t="inlineStr">
+        <is>
+          <t>Jindal Worldwide shares hit 20% upper circuit as arm plans 100 electric scooter showrooms - TradingView</t>
+        </is>
+      </c>
+      <c r="P423" t="inlineStr">
+        <is>
+          <t>News by CNBC TV18 on TradingView, 2026-09-04 — cnbctv:657850109094b:0 - TradingView</t>
+        </is>
+      </c>
+      <c r="Q423" t="inlineStr">
+        <is>
+          <t>Jindal Worldwide stock hits upper circuit - What's behind the share price jump? - Livemint</t>
+        </is>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>2026-09-04 20:18:15 IST</t>
+        </is>
+      </c>
+      <c r="B424" t="n">
+        <v>3</v>
+      </c>
+      <c r="C424" t="inlineStr">
+        <is>
+          <t>NRAIL.NS</t>
+        </is>
+      </c>
+      <c r="D424" t="inlineStr">
+        <is>
+          <t>N R Agarwal Industries Limited</t>
+        </is>
+      </c>
+      <c r="E424" t="n">
+        <v>498.9500122070312</v>
+      </c>
+      <c r="F424" t="n">
+        <v>595.25</v>
+      </c>
+      <c r="G424" t="n">
+        <v>496.0499877929688</v>
+      </c>
+      <c r="H424" t="n">
+        <v>584</v>
+      </c>
+      <c r="I424" t="n">
+        <v>496.0499877929688</v>
+      </c>
+      <c r="J424" t="n">
+        <v>584</v>
+      </c>
+      <c r="K424" t="n">
+        <v>157425</v>
+      </c>
+      <c r="L424" t="n">
+        <v>17.73</v>
+      </c>
+      <c r="M424" t="inlineStr">
+        <is>
+          <t>NR Agarwal Industries Ltd. (NRAIL) Share Price Rises 12.36% Today - Univest</t>
+        </is>
+      </c>
+      <c r="N424" t="inlineStr">
+        <is>
+          <t>NR Agarwal Industries Ltd. (NRAIL) Share Price Rises 12.36% Today - Univest</t>
+        </is>
+      </c>
+      <c r="O424" t="inlineStr"/>
+      <c r="P424" t="inlineStr"/>
+      <c r="Q424" t="inlineStr"/>
+    </row>
+    <row r="425">
+      <c r="A425" t="inlineStr">
+        <is>
+          <t>2026-09-04 20:18:15 IST</t>
+        </is>
+      </c>
+      <c r="B425" t="n">
+        <v>4</v>
+      </c>
+      <c r="C425" t="inlineStr">
+        <is>
+          <t>LANCORHOL.NS</t>
+        </is>
+      </c>
+      <c r="D425" t="inlineStr">
+        <is>
+          <t>Lancor Holdings Limited</t>
+        </is>
+      </c>
+      <c r="E425" t="n">
+        <v>35.13000106811523</v>
+      </c>
+      <c r="F425" t="n">
+        <v>40.88000106811523</v>
+      </c>
+      <c r="G425" t="n">
+        <v>34.20999908447266</v>
+      </c>
+      <c r="H425" t="n">
+        <v>40.34999847412109</v>
+      </c>
+      <c r="I425" t="n">
+        <v>34.75</v>
+      </c>
+      <c r="J425" t="n">
+        <v>40.34999847412109</v>
+      </c>
+      <c r="K425" t="n">
+        <v>2380475</v>
+      </c>
+      <c r="L425" t="n">
+        <v>16.12</v>
+      </c>
+      <c r="M425" t="inlineStr">
+        <is>
+          <t>Lancor Holdings Limited (NSE:LANCORHOL) Shares Fly 25% But Investors Aren't Buying For Growth - simplywall.st</t>
+        </is>
+      </c>
+      <c r="N425" t="inlineStr">
+        <is>
+          <t>LANCORHOL.NS Mar 2026 Earnings: EPS of ₹5.84 on Revenue of ₹14.0 Cr; Stock Gains 8.32 Points - Analyst Drop Coverage - vinanet.vn</t>
+        </is>
+      </c>
+      <c r="O425" t="inlineStr">
+        <is>
+          <t>Lancor Holdings Limited Sees Marginal Decline: Technical Resistance and Support Levels in Focus - SuperTrend - vinanet.vn</t>
+        </is>
+      </c>
+      <c r="P425" t="inlineStr">
+        <is>
+          <t>Lancor Holdings Faces Resistance: Stock Declines 2.62% Amid Sector Volatility - Elliott Wave Entry - vinanet.vn</t>
+        </is>
+      </c>
+      <c r="Q425" t="inlineStr">
+        <is>
+          <t>LANCOR HOLDINGS LIMITED Share Price - Upstox</t>
+        </is>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="inlineStr">
+        <is>
+          <t>2026-09-04 20:18:15 IST</t>
+        </is>
+      </c>
+      <c r="B426" t="n">
+        <v>5</v>
+      </c>
+      <c r="C426" t="inlineStr">
+        <is>
+          <t>SVGLOBAL.NS</t>
+        </is>
+      </c>
+      <c r="D426" t="inlineStr">
+        <is>
+          <t>S V Global Mill Limited</t>
+        </is>
+      </c>
+      <c r="E426" t="n">
+        <v>162</v>
+      </c>
+      <c r="F426" t="n">
+        <v>172.8099975585938</v>
+      </c>
+      <c r="G426" t="n">
+        <v>157.1499938964844</v>
+      </c>
+      <c r="H426" t="n">
+        <v>163.6199951171875</v>
+      </c>
+      <c r="I426" t="n">
+        <v>144.0099945068359</v>
+      </c>
+      <c r="J426" t="n">
+        <v>163.6199951171875</v>
+      </c>
+      <c r="K426" t="n">
+        <v>286297</v>
+      </c>
+      <c r="L426" t="n">
+        <v>13.62</v>
+      </c>
+      <c r="M426" t="inlineStr">
+        <is>
+          <t>S V Global Mill Ltd (SVGLOBAL) Profile, Company FAQs &amp; Facts, Industry, Sector, Employee Strength - Stocktwits</t>
+        </is>
+      </c>
+      <c r="N426" t="inlineStr">
+        <is>
+          <t>SV Global Mill Ltd. Share Price Rise Streak: Price Action - Univest</t>
+        </is>
+      </c>
+      <c r="O426" t="inlineStr">
+        <is>
+          <t>SV Global Mill Share Price Today: Stock Drops to Rs 124.30 - Univest</t>
+        </is>
+      </c>
+      <c r="P426" t="inlineStr">
+        <is>
+          <t>SV Global Mill Share Price gains 19.99% amid market focus - Univest</t>
+        </is>
+      </c>
+      <c r="Q426" t="inlineStr">
+        <is>
+          <t>SV Global Mill Share Price today: price rise and valuation - Univest</t>
+        </is>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="inlineStr">
+        <is>
+          <t>2026-09-04 20:18:15 IST</t>
+        </is>
+      </c>
+      <c r="B427" t="n">
+        <v>6</v>
+      </c>
+      <c r="C427" t="inlineStr">
+        <is>
+          <t>NAGREEKEXP.NS</t>
+        </is>
+      </c>
+      <c r="D427" t="inlineStr">
+        <is>
+          <t>Nagreeka Exports Limited</t>
+        </is>
+      </c>
+      <c r="E427" t="n">
+        <v>21.10000038146973</v>
+      </c>
+      <c r="F427" t="n">
+        <v>25</v>
+      </c>
+      <c r="G427" t="n">
+        <v>20.80999946594238</v>
+      </c>
+      <c r="H427" t="n">
+        <v>24.10000038146973</v>
+      </c>
+      <c r="I427" t="n">
+        <v>21.29999923706055</v>
+      </c>
+      <c r="J427" t="n">
+        <v>24.10000038146973</v>
+      </c>
+      <c r="K427" t="n">
+        <v>411783</v>
+      </c>
+      <c r="L427" t="n">
+        <v>13.15</v>
+      </c>
+      <c r="M427" t="inlineStr">
+        <is>
+          <t>CFEL Stock Price and Chart — NSE:CFEL - TradingView</t>
+        </is>
+      </c>
+      <c r="N427" t="inlineStr">
+        <is>
+          <t>CFEL Stock Price and Chart — NSE:CFEL - TradingView</t>
+        </is>
+      </c>
+      <c r="O427" t="inlineStr"/>
+      <c r="P427" t="inlineStr"/>
+      <c r="Q427" t="inlineStr"/>
+    </row>
+    <row r="428">
+      <c r="A428" t="inlineStr">
+        <is>
+          <t>2026-09-04 20:18:15 IST</t>
+        </is>
+      </c>
+      <c r="B428" t="n">
+        <v>7</v>
+      </c>
+      <c r="C428" t="inlineStr">
+        <is>
+          <t>PCJEWELLER.NS</t>
+        </is>
+      </c>
+      <c r="D428" t="inlineStr">
+        <is>
+          <t>PC Jeweller Limited</t>
+        </is>
+      </c>
+      <c r="E428" t="n">
+        <v>10.60000038146973</v>
+      </c>
+      <c r="F428" t="n">
+        <v>12.17000007629395</v>
+      </c>
+      <c r="G428" t="n">
+        <v>10.51000022888184</v>
+      </c>
+      <c r="H428" t="n">
+        <v>11.85999965667725</v>
+      </c>
+      <c r="I428" t="n">
+        <v>10.52000045776367</v>
+      </c>
+      <c r="J428" t="n">
+        <v>11.85999965667725</v>
+      </c>
+      <c r="K428" t="n">
+        <v>1088882385</v>
+      </c>
+      <c r="L428" t="n">
+        <v>12.74</v>
+      </c>
+      <c r="M428" t="inlineStr">
+        <is>
+          <t>PC Jewellers Share Price - Live NSE: PCJEWELLER Stock Price &amp; Chart - Upstox</t>
+        </is>
+      </c>
+      <c r="N428" t="inlineStr">
+        <is>
+          <t>PC Jewellers Share Price - Live NSE: PCJEWELLER Stock Price &amp; Chart - Upstox</t>
+        </is>
+      </c>
+      <c r="O428" t="inlineStr"/>
+      <c r="P428" t="inlineStr"/>
+      <c r="Q428" t="inlineStr"/>
+    </row>
+    <row r="429">
+      <c r="A429" t="inlineStr">
+        <is>
+          <t>2026-09-04 20:18:15 IST</t>
+        </is>
+      </c>
+      <c r="B429" t="n">
+        <v>8</v>
+      </c>
+      <c r="C429" t="inlineStr">
+        <is>
+          <t>BIRLAPREC.NS</t>
+        </is>
+      </c>
+      <c r="D429" t="inlineStr">
+        <is>
+          <t>Birla Precision Technologies Limited</t>
+        </is>
+      </c>
+      <c r="E429" t="n">
+        <v>53.25</v>
+      </c>
+      <c r="F429" t="n">
+        <v>59.79000091552734</v>
+      </c>
+      <c r="G429" t="n">
+        <v>52.72999954223633</v>
+      </c>
+      <c r="H429" t="n">
+        <v>57.91999816894531</v>
+      </c>
+      <c r="I429" t="n">
+        <v>51.66999816894531</v>
+      </c>
+      <c r="J429" t="n">
+        <v>57.91999816894531</v>
+      </c>
+      <c r="K429" t="n">
+        <v>2568069</v>
+      </c>
+      <c r="L429" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="M429" t="inlineStr">
+        <is>
+          <t>Birla Precision Technologies (BIRLAPREC.NS): Stock Eases Marginally, Nears Key Support Level - Symmetrical Triangle - vinanet.vn</t>
+        </is>
+      </c>
+      <c r="N429" t="inlineStr">
+        <is>
+          <t>Birla Precision Technologies Mar 2026 Earnings: Steady EPS Delivery Amid Modest Revenue Performance - Tangible Book Value - vinanet.vn</t>
+        </is>
+      </c>
+      <c r="O429" t="inlineStr">
+        <is>
+          <t>BIRLAPREC.NS Mar 2026 Earnings: Marginal EPS of ₹0.39 on Modest Revenue of ₹63.91 crore; Stock Slides 0.71% - ROA Comparison - vinanet.vn</t>
+        </is>
+      </c>
+      <c r="P429" t="inlineStr">
+        <is>
+          <t>Birla Precision Technologies Mar 2026 Earnings: Steady EPS Delivery Amid Modest Revenue Performance - Tangible Book Value - vinanet.vn</t>
+        </is>
+      </c>
+      <c r="Q429" t="inlineStr">
+        <is>
+          <t>Birla Precision Technologies Mar 2026 Earnings: Modest Profitability Amidst Stable Revenue - Revenue Warning Signal - vinanet.vn</t>
+        </is>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="inlineStr">
+        <is>
+          <t>2026-09-04 20:18:15 IST</t>
+        </is>
+      </c>
+      <c r="B430" t="n">
+        <v>9</v>
+      </c>
+      <c r="C430" t="inlineStr">
+        <is>
+          <t>MARALOVER.NS</t>
+        </is>
+      </c>
+      <c r="D430" t="inlineStr">
+        <is>
+          <t>Maral Overseas Limited</t>
+        </is>
+      </c>
+      <c r="E430" t="n">
+        <v>55</v>
+      </c>
+      <c r="F430" t="n">
+        <v>65.69000244140625</v>
+      </c>
+      <c r="G430" t="n">
+        <v>55</v>
+      </c>
+      <c r="H430" t="n">
+        <v>61.83000183105469</v>
+      </c>
+      <c r="I430" t="n">
+        <v>55.2599983215332</v>
+      </c>
+      <c r="J430" t="n">
+        <v>61.83000183105469</v>
+      </c>
+      <c r="K430" t="n">
+        <v>313406</v>
+      </c>
+      <c r="L430" t="n">
+        <v>11.89</v>
+      </c>
+      <c r="M430" t="inlineStr">
+        <is>
+          <t>Maral Overseas Limited Reports Zero Physical Share Transfer Requests Under SEBI Special Window - scanx.trade</t>
+        </is>
+      </c>
+      <c r="N430" t="inlineStr">
+        <is>
+          <t>Maral Overseas Limited Reports Zero Physical Share Transfer Requests Under SEBI Special Window - scanx.trade</t>
+        </is>
+      </c>
+      <c r="O430" t="inlineStr">
+        <is>
+          <t>Maral Overseas schedules 37th AGM on August 25 via VC/OAVM - scanx.trade</t>
+        </is>
+      </c>
+      <c r="P430" t="inlineStr"/>
+      <c r="Q430" t="inlineStr"/>
+    </row>
+    <row r="431">
+      <c r="A431" t="inlineStr">
+        <is>
+          <t>2026-09-04 20:18:15 IST</t>
+        </is>
+      </c>
+      <c r="B431" t="n">
+        <v>10</v>
+      </c>
+      <c r="C431" t="inlineStr">
+        <is>
+          <t>CYBERMEDIA.NS</t>
+        </is>
+      </c>
+      <c r="D431" t="inlineStr">
+        <is>
+          <t>Cyber Media (India) Limited</t>
+        </is>
+      </c>
+      <c r="E431" t="n">
+        <v>25.89999961853027</v>
+      </c>
+      <c r="F431" t="n">
+        <v>28.45000076293945</v>
+      </c>
+      <c r="G431" t="n">
+        <v>22.20000076293945</v>
+      </c>
+      <c r="H431" t="n">
+        <v>26.39999961853027</v>
+      </c>
+      <c r="I431" t="n">
+        <v>23.8799991607666</v>
+      </c>
+      <c r="J431" t="n">
+        <v>26.39999961853027</v>
+      </c>
+      <c r="K431" t="n">
+        <v>2156723</v>
+      </c>
+      <c r="L431" t="n">
+        <v>10.55</v>
+      </c>
+      <c r="M431" t="inlineStr">
+        <is>
+          <t>Cyber Media (NSE: CYBERMEDIA) Price Analysis - Kalkine India</t>
+        </is>
+      </c>
+      <c r="N431" t="inlineStr">
+        <is>
+          <t>Cyber Media (NSE: CYBERMEDIA) Price Analysis - Kalkine India</t>
+        </is>
+      </c>
+      <c r="O431" t="inlineStr">
+        <is>
+          <t>Number of employees of Cyber Media (India) Limited Rights 2025-29.08.25 For Shares – BSE:CYBER_RE - TradingView</t>
+        </is>
+      </c>
+      <c r="P431" t="inlineStr"/>
+      <c r="Q431" t="inlineStr"/>
+    </row>
+    <row r="432">
+      <c r="A432" t="inlineStr">
+        <is>
+          <t>2026-09-04 20:18:15 IST</t>
+        </is>
+      </c>
+      <c r="B432" t="n">
+        <v>11</v>
+      </c>
+      <c r="C432" t="inlineStr">
+        <is>
+          <t>ZSARACOM.NS</t>
+        </is>
+      </c>
+      <c r="D432" t="inlineStr">
+        <is>
+          <t>Saraswati Commercial India Limited</t>
+        </is>
+      </c>
+      <c r="E432" t="n">
+        <v>10096</v>
+      </c>
+      <c r="F432" t="n">
+        <v>11600</v>
+      </c>
+      <c r="G432" t="n">
+        <v>9808</v>
+      </c>
+      <c r="H432" t="n">
+        <v>11302</v>
+      </c>
+      <c r="I432" t="n">
+        <v>10227</v>
+      </c>
+      <c r="J432" t="n">
+        <v>11302</v>
+      </c>
+      <c r="K432" t="n">
+        <v>221</v>
+      </c>
+      <c r="L432" t="n">
+        <v>10.51</v>
+      </c>
+      <c r="M432" t="inlineStr">
+        <is>
+          <t>Saraswati Commercial Share Price Rise on NBFC Valuation - Univest</t>
+        </is>
+      </c>
+      <c r="N432" t="inlineStr">
+        <is>
+          <t>Saraswati Commercial Share Price Rise on NBFC Valuation - Univest</t>
+        </is>
+      </c>
+      <c r="O432" t="inlineStr">
+        <is>
+          <t>Saraswati Commercial submits FY26 annual report to BSE - scanx.trade</t>
+        </is>
+      </c>
+      <c r="P432" t="inlineStr">
+        <is>
+          <t>Saraswati Commercial Q1FY27 net profit surges 169% YoY to ₹635.6 million - scanx.trade</t>
+        </is>
+      </c>
+      <c r="Q432" t="inlineStr"/>
+    </row>
+    <row r="433">
+      <c r="A433" t="inlineStr">
+        <is>
+          <t>2026-09-04 20:18:15 IST</t>
+        </is>
+      </c>
+      <c r="B433" t="n">
+        <v>12</v>
+      </c>
+      <c r="C433" t="inlineStr">
+        <is>
+          <t>MASTERTR.NS</t>
+        </is>
+      </c>
+      <c r="D433" t="inlineStr">
+        <is>
+          <t>Master Trust Limited</t>
+        </is>
+      </c>
+      <c r="E433" t="n">
+        <v>81.05000305175781</v>
+      </c>
+      <c r="F433" t="n">
+        <v>95.5</v>
+      </c>
+      <c r="G433" t="n">
+        <v>81.05000305175781</v>
+      </c>
+      <c r="H433" t="n">
+        <v>89.16000366210938</v>
+      </c>
+      <c r="I433" t="n">
+        <v>81.02999877929688</v>
+      </c>
+      <c r="J433" t="n">
+        <v>89.16000366210938</v>
+      </c>
+      <c r="K433" t="n">
+        <v>8359824</v>
+      </c>
+      <c r="L433" t="n">
+        <v>10.03</v>
+      </c>
+      <c r="M433" t="inlineStr">
+        <is>
+          <t>It's Down 26% But Master Trust Limited (NSE:MASTERTR) Could Be Riskier Than It Looks - simplywall.st</t>
+        </is>
+      </c>
+      <c r="N433" t="inlineStr">
+        <is>
+          <t>Master Trust Limited Q2 2026 Earnings: Revenue Declines Marginally, EPS Holds at ₹10.6 - Consensus Forecast Report - vinanet.vn</t>
+        </is>
+      </c>
+      <c r="O433" t="inlineStr">
+        <is>
+          <t>Master Trust Limited sees mild gains; support and resistance levels in focus - Price Surge Stocks - vinanet.vn</t>
+        </is>
+      </c>
+      <c r="P433" t="inlineStr">
+        <is>
+          <t>MASTERTR Stock Price and Chart — NSE:MASTERTR - TradingView</t>
+        </is>
+      </c>
+      <c r="Q433" t="inlineStr">
+        <is>
+          <t>Master Trust Limited (MASTERTR.NS) – Steady Gains Above Support Zone - Fear Greed Extreme - vinanet.vn</t>
+        </is>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="inlineStr">
+        <is>
+          <t>2026-09-04 20:18:15 IST</t>
+        </is>
+      </c>
+      <c r="B434" t="n">
+        <v>13</v>
+      </c>
+      <c r="C434" t="inlineStr">
+        <is>
+          <t>RHETAN.NS</t>
+        </is>
+      </c>
+      <c r="D434" t="inlineStr">
+        <is>
+          <t>Rhetan TMT Limited</t>
+        </is>
+      </c>
+      <c r="E434" t="n">
+        <v>25.42000007629395</v>
+      </c>
+      <c r="F434" t="n">
+        <v>25.42000007629395</v>
+      </c>
+      <c r="G434" t="n">
+        <v>25.40999984741211</v>
+      </c>
+      <c r="H434" t="n">
+        <v>25.42000007629395</v>
+      </c>
+      <c r="I434" t="n">
+        <v>23.11000061035156</v>
+      </c>
+      <c r="J434" t="n">
+        <v>25.42000007629395</v>
+      </c>
+      <c r="K434" t="n">
+        <v>5455318</v>
+      </c>
+      <c r="L434" t="n">
+        <v>10</v>
+      </c>
+      <c r="M434" t="inlineStr">
+        <is>
+          <t>Rhetan TMT stock surges 10% upper circuit; AGM on Sep 16 to consider and approve company borrowing limit to Rs. 300 crore for Business expansion - ThePrint</t>
+        </is>
+      </c>
+      <c r="N434" t="inlineStr">
+        <is>
+          <t>Rhetan TMT Stock Hits Upper Circuit: Key Triggers &amp; Q1 Results - The Daily Jagran</t>
+        </is>
+      </c>
+      <c r="O434" t="inlineStr">
+        <is>
+          <t>Small-cap stock under 50 hits 10% upper circuit despite stock market crash - Livemint</t>
+        </is>
+      </c>
+      <c r="P434" t="inlineStr">
+        <is>
+          <t>130% Return In 3 Years: Rhetan TMT Stock Jumps Post Q1 Result | Key Things To Know - Goodreturns</t>
+        </is>
+      </c>
+      <c r="Q434" t="inlineStr">
+        <is>
+          <t>Rhetan TMT Ltd. Share Price Jumps to Fresh One-Year High - Univest</t>
+        </is>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="inlineStr">
+        <is>
+          <t>2026-09-04 20:18:15 IST</t>
+        </is>
+      </c>
+      <c r="B435" t="n">
+        <v>14</v>
+      </c>
+      <c r="C435" t="inlineStr">
+        <is>
+          <t>RAMBHAJO.NS</t>
+        </is>
+      </c>
+      <c r="D435" t="inlineStr">
+        <is>
+          <t>Advit Jewels Limited</t>
+        </is>
+      </c>
+      <c r="E435" t="n">
+        <v>249.8999938964844</v>
+      </c>
+      <c r="F435" t="n">
+        <v>268.6799926757812</v>
+      </c>
+      <c r="G435" t="n">
+        <v>247.0599975585938</v>
+      </c>
+      <c r="H435" t="n">
+        <v>268.6799926757812</v>
+      </c>
+      <c r="I435" t="n">
+        <v>244.2599945068359</v>
+      </c>
+      <c r="J435" t="n">
+        <v>268.6799926757812</v>
+      </c>
+      <c r="K435" t="n">
+        <v>1915247</v>
+      </c>
+      <c r="L435" t="n">
+        <v>10</v>
+      </c>
+      <c r="M435" t="inlineStr">
+        <is>
+          <t>ADVIT JEWELS Share Price update: fundamentals and peers - Univest</t>
+        </is>
+      </c>
+      <c r="N435" t="inlineStr">
+        <is>
+          <t>ADVIT JEWELS Share Price update: fundamentals and peers - Univest</t>
+        </is>
+      </c>
+      <c r="O435" t="inlineStr"/>
+      <c r="P435" t="inlineStr"/>
+      <c r="Q435" t="inlineStr"/>
+    </row>
+    <row r="436">
+      <c r="A436" t="inlineStr">
+        <is>
+          <t>2026-09-04 20:18:15 IST</t>
+        </is>
+      </c>
+      <c r="B436" t="n">
+        <v>15</v>
+      </c>
+      <c r="C436" t="inlineStr">
+        <is>
+          <t>UNITECH.NS</t>
+        </is>
+      </c>
+      <c r="D436" t="inlineStr">
+        <is>
+          <t>Unitech Limited</t>
+        </is>
+      </c>
+      <c r="E436" t="n">
+        <v>3.710000038146973</v>
+      </c>
+      <c r="F436" t="n">
+        <v>4.079999923706055</v>
+      </c>
+      <c r="G436" t="n">
+        <v>3.710000038146973</v>
+      </c>
+      <c r="H436" t="n">
+        <v>4.079999923706055</v>
+      </c>
+      <c r="I436" t="n">
+        <v>3.710000038146973</v>
+      </c>
+      <c r="J436" t="n">
+        <v>4.079999923706055</v>
+      </c>
+      <c r="K436" t="n">
+        <v>14406516</v>
+      </c>
+      <c r="L436" t="n">
+        <v>9.970000000000001</v>
+      </c>
+      <c r="M436" t="inlineStr">
+        <is>
+          <t>Unitech Ltd Share Price Today: price action and valuation - Univest</t>
+        </is>
+      </c>
+      <c r="N436" t="inlineStr">
+        <is>
+          <t>Unitech Ltd Share Price Today: price action and valuation - Univest</t>
+        </is>
+      </c>
+      <c r="O436" t="inlineStr">
+        <is>
+          <t>InvestingPro’s Fair Value warned of 54% drop in Unitech shares By Investing.com - Investing.com India</t>
+        </is>
+      </c>
+      <c r="P436" t="inlineStr">
+        <is>
+          <t>Unitech Group files FY26 BRSR; awards 10 Lot-5 tenders - scanx.trade</t>
+        </is>
+      </c>
+      <c r="Q436" t="inlineStr">
+        <is>
+          <t>Unitech appoints Giridhar Aramane as Chairman and Managing Director - scanx.trade</t>
+        </is>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="inlineStr">
+        <is>
+          <t>2026-09-04 20:18:15 IST</t>
+        </is>
+      </c>
+      <c r="B437" t="n">
+        <v>16</v>
+      </c>
+      <c r="C437" t="inlineStr">
+        <is>
+          <t>AKI.NS</t>
+        </is>
+      </c>
+      <c r="D437" t="inlineStr">
+        <is>
+          <t>AKI India Limited</t>
+        </is>
+      </c>
+      <c r="E437" t="n">
+        <v>7.21999979019165</v>
+      </c>
+      <c r="F437" t="n">
+        <v>7.21999979019165</v>
+      </c>
+      <c r="G437" t="n">
+        <v>7.21999979019165</v>
+      </c>
+      <c r="H437" t="n">
+        <v>7.21999979019165</v>
+      </c>
+      <c r="I437" t="n">
+        <v>6.570000171661377</v>
+      </c>
+      <c r="J437" t="n">
+        <v>7.21999979019165</v>
+      </c>
+      <c r="K437" t="n">
+        <v>258805</v>
+      </c>
+      <c r="L437" t="n">
+        <v>9.890000000000001</v>
+      </c>
+      <c r="M437" t="inlineStr">
+        <is>
+          <t>Penny stock under 10 rupees: Upper circuit - Leather share jumps 74% in 4 sessions | Back-to-back surge for third day - TradingView</t>
+        </is>
+      </c>
+      <c r="N437" t="inlineStr">
+        <is>
+          <t>Penny stock under 10 rupees: Upper circuit - Leather share jumps 74% in 4 sessions | Back-to-back surge for third day - TradingView</t>
+        </is>
+      </c>
+      <c r="O437" t="inlineStr">
+        <is>
+          <t>AKI India Ltd Upgraded to Sell on Technical Improvements Despite Lingering Financial Challenges - MarketsMojo</t>
+        </is>
+      </c>
+      <c r="P437" t="inlineStr">
+        <is>
+          <t>AKI India Ltd leads gainers in 'B' group - Business Standard</t>
+        </is>
+      </c>
+      <c r="Q437" t="inlineStr">
+        <is>
+          <t>Volume shocker stocks: Why share price of EMS, Expleo Solutions, Windlas Biotech, AKI India, Heritage Foods are up today - Livemint</t>
+        </is>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="inlineStr">
+        <is>
+          <t>2026-09-04 20:18:15 IST</t>
+        </is>
+      </c>
+      <c r="B438" t="n">
+        <v>17</v>
+      </c>
+      <c r="C438" t="inlineStr">
+        <is>
+          <t>KSR.NS</t>
+        </is>
+      </c>
+      <c r="D438" t="inlineStr">
+        <is>
+          <t>KSR Footwear Limited</t>
+        </is>
+      </c>
+      <c r="E438" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="F438" t="n">
+        <v>34.68999862670898</v>
+      </c>
+      <c r="G438" t="n">
+        <v>31.89999961853027</v>
+      </c>
+      <c r="H438" t="n">
+        <v>34.61000061035156</v>
+      </c>
+      <c r="I438" t="n">
+        <v>31.54000091552734</v>
+      </c>
+      <c r="J438" t="n">
+        <v>34.61000061035156</v>
+      </c>
+      <c r="K438" t="n">
+        <v>388523</v>
+      </c>
+      <c r="L438" t="n">
+        <v>9.73</v>
+      </c>
+      <c r="M438" t="inlineStr">
+        <is>
+          <t>KSR Footwear Share Price: Alpa Wealth Buys 1.33% Stake - Univest</t>
+        </is>
+      </c>
+      <c r="N438" t="inlineStr">
+        <is>
+          <t>Mark Pope shares not-so-subtle response to losing Mark Mitchell - On3</t>
+        </is>
+      </c>
+      <c r="O438" t="inlineStr">
+        <is>
+          <t>KSR Footwear AGM passes FY26 results; promoters vote 100% in favour - scanx.trade</t>
+        </is>
+      </c>
+      <c r="P438" t="inlineStr">
+        <is>
+          <t>Mark Pope shares not-so-subtle response to losing Mark Mitchell - On3</t>
+        </is>
+      </c>
+      <c r="Q438" t="inlineStr">
+        <is>
+          <t>Kalen "Big K" Edwards Shares Words of Wisdom from the Changing Kentucky Trenches - On3</t>
+        </is>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="inlineStr">
+        <is>
+          <t>2026-09-04 20:18:15 IST</t>
+        </is>
+      </c>
+      <c r="B439" t="n">
+        <v>18</v>
+      </c>
+      <c r="C439" t="inlineStr">
+        <is>
+          <t>JISLJALEQS.NS</t>
+        </is>
+      </c>
+      <c r="D439" t="inlineStr">
+        <is>
+          <t>Jain Irrigation Systems Limited</t>
+        </is>
+      </c>
+      <c r="E439" t="n">
+        <v>28.29000091552734</v>
+      </c>
+      <c r="F439" t="n">
+        <v>32.38999938964844</v>
+      </c>
+      <c r="G439" t="n">
+        <v>28.25</v>
+      </c>
+      <c r="H439" t="n">
+        <v>30.8700008392334</v>
+      </c>
+      <c r="I439" t="n">
+        <v>28.15999984741211</v>
+      </c>
+      <c r="J439" t="n">
+        <v>30.8700008392334</v>
+      </c>
+      <c r="K439" t="n">
+        <v>29542567</v>
+      </c>
+      <c r="L439" t="n">
+        <v>9.619999999999999</v>
+      </c>
+      <c r="M439" t="inlineStr">
+        <is>
+          <t>Jain Irrigation (JISLDVREQS.NS) Slips Marginally to ₹21.0: Key Support and Resistance Levels in Focus - Volume Climax - siam.in</t>
+        </is>
+      </c>
+      <c r="N439" t="inlineStr">
+        <is>
+          <t>Jain Irrigation (JISLDVREQS.NS) Slips Marginally to ₹21.0: Key Support and Resistance Levels in Focus - Volume Climax - siam.in</t>
+        </is>
+      </c>
+      <c r="O439" t="inlineStr"/>
+      <c r="P439" t="inlineStr"/>
+      <c r="Q439" t="inlineStr"/>
+    </row>
+    <row r="440">
+      <c r="A440" t="inlineStr">
+        <is>
+          <t>2026-09-04 20:18:15 IST</t>
+        </is>
+      </c>
+      <c r="B440" t="n">
+        <v>19</v>
+      </c>
+      <c r="C440" t="inlineStr">
+        <is>
+          <t>CURAA.NS</t>
+        </is>
+      </c>
+      <c r="D440" t="inlineStr">
+        <is>
+          <t>Cura Technologies Limited</t>
+        </is>
+      </c>
+      <c r="E440" t="n">
+        <v>78.5</v>
+      </c>
+      <c r="F440" t="n">
+        <v>78.5</v>
+      </c>
+      <c r="G440" t="n">
+        <v>60</v>
+      </c>
+      <c r="H440" t="n">
+        <v>72.45999908447266</v>
+      </c>
+      <c r="I440" t="n">
+        <v>66.19999694824219</v>
+      </c>
+      <c r="J440" t="n">
+        <v>72.45999908447266</v>
+      </c>
+      <c r="K440" t="n">
+        <v>2020</v>
+      </c>
+      <c r="L440" t="n">
+        <v>9.460000000000001</v>
+      </c>
+      <c r="M440" t="inlineStr">
+        <is>
+          <t>D2C kitchenware startup Curaa raises Rs 40 crore led by 3one4 Capital - economictimes.com</t>
+        </is>
+      </c>
+      <c r="N440" t="inlineStr">
+        <is>
+          <t>D2C kitchenware startup Curaa raises Rs 40 crore led by 3one4 Capital - economictimes.com</t>
+        </is>
+      </c>
+      <c r="O440" t="inlineStr"/>
+      <c r="P440" t="inlineStr"/>
+      <c r="Q440" t="inlineStr"/>
+    </row>
+    <row r="441">
+      <c r="A441" t="inlineStr">
+        <is>
+          <t>2026-09-04 20:18:15 IST</t>
+        </is>
+      </c>
+      <c r="B441" t="n">
+        <v>20</v>
+      </c>
+      <c r="C441" t="inlineStr">
+        <is>
+          <t>LALITHAA.NS</t>
+        </is>
+      </c>
+      <c r="D441" t="inlineStr">
+        <is>
+          <t>Lalithaa Jewellery Mart Limited</t>
+        </is>
+      </c>
+      <c r="E441" t="n">
+        <v>283</v>
+      </c>
+      <c r="F441" t="n">
+        <v>308.2999877929688</v>
+      </c>
+      <c r="G441" t="n">
+        <v>280.6000061035156</v>
+      </c>
+      <c r="H441" t="n">
+        <v>306.7000122070312</v>
+      </c>
+      <c r="I441" t="n">
+        <v>280.2999877929688</v>
+      </c>
+      <c r="J441" t="n">
+        <v>306.7000122070312</v>
+      </c>
+      <c r="K441" t="n">
+        <v>23778911</v>
+      </c>
+      <c r="L441" t="n">
+        <v>9.42</v>
+      </c>
+      <c r="M441" t="inlineStr">
+        <is>
+          <t>Shanti Gold International Buys 1.44 Lakh Shares In Lalithaa Jewellery Mart For ₹3.88 Crore - Sahi</t>
+        </is>
+      </c>
+      <c r="N441" t="inlineStr">
+        <is>
+          <t>Lalithaa Jewellery Mart launches 65th showroom in Chennai - scanx.trade</t>
+        </is>
+      </c>
+      <c r="O441" t="inlineStr">
+        <is>
+          <t>Shanti Gold buys ₹3.88 crore stake in retail client Lalithaa Jewellery - Dealroom</t>
+        </is>
+      </c>
+      <c r="P441" t="inlineStr">
+        <is>
+          <t>Shanti Gold buys 42,130 more Lalithaa Jewellery shares for ₹1.11 crore - scanx.trade</t>
+        </is>
+      </c>
+      <c r="Q441" t="inlineStr">
+        <is>
+          <t>Lalithaa Jewellery shares make strong market debut at 32% premium; should you buy, sell or hold? - Moneycontrol.com</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:Q361"/>
@@ -28081,7 +29346,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q721"/>
+  <dimension ref="A1:Q741"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -72104,9 +73369,6 @@
           <t>With EPS Growth And More, Jayaswal Neco Industries (NSE:JAYNECOIND) Makes An Interesting Case - simplywall.st</t>
         </is>
       </c>
-      <c r="O702" t="inlineStr"/>
-      <c r="P702" t="inlineStr"/>
-      <c r="Q702" t="inlineStr"/>
     </row>
     <row r="703">
       <c r="A703" t="inlineStr">
@@ -72161,9 +73423,6 @@
           <t>Ugar Sugar Works director Hari Athawale retires, Prafulla Shirgaokar resigns from board - ChiniMandi</t>
         </is>
       </c>
-      <c r="O703" t="inlineStr"/>
-      <c r="P703" t="inlineStr"/>
-      <c r="Q703" t="inlineStr"/>
     </row>
     <row r="704">
       <c r="A704" t="inlineStr">
@@ -72982,8 +74241,6 @@
           <t>Five Star Business Finance Submits Business Responsibility and Sustainability Report for FY 2025-26 - scanx.trade</t>
         </is>
       </c>
-      <c r="P715" t="inlineStr"/>
-      <c r="Q715" t="inlineStr"/>
     </row>
     <row r="716">
       <c r="A716" t="inlineStr">
@@ -73112,8 +74369,6 @@
           <t>Rs 21,932 cr opportunity: 2 stocks powering India’s next manufacturing wave - financialexpress.com</t>
         </is>
       </c>
-      <c r="P717" t="inlineStr"/>
-      <c r="Q717" t="inlineStr"/>
     </row>
     <row r="718">
       <c r="A718" t="inlineStr">
@@ -73311,8 +74566,6 @@
           <t>NXG Infrastructure Income Fund Holds Ground at $56.30 as Market Waits for Direction - Fear Greed Extreme - vinanet.vn</t>
         </is>
       </c>
-      <c r="P720" t="inlineStr"/>
-      <c r="Q720" t="inlineStr"/>
     </row>
     <row r="721">
       <c r="A721" t="inlineStr">
@@ -73372,8 +74625,1326 @@
           <t>Power Mech Projects Publishes AGM Notice and E-Voting Details in Newspapers - TipRanks</t>
         </is>
       </c>
-      <c r="P721" t="inlineStr"/>
-      <c r="Q721" t="inlineStr"/>
+    </row>
+    <row r="722">
+      <c r="A722" t="inlineStr">
+        <is>
+          <t>2026-09-04 20:18:15 IST</t>
+        </is>
+      </c>
+      <c r="B722" t="n">
+        <v>1</v>
+      </c>
+      <c r="C722" t="inlineStr">
+        <is>
+          <t>DYCL.NS</t>
+        </is>
+      </c>
+      <c r="D722" t="inlineStr">
+        <is>
+          <t>Dynamic Cables Limited</t>
+        </is>
+      </c>
+      <c r="E722" t="n">
+        <v>541.9000244140625</v>
+      </c>
+      <c r="F722" t="n">
+        <v>546.7999877929688</v>
+      </c>
+      <c r="G722" t="n">
+        <v>484</v>
+      </c>
+      <c r="H722" t="n">
+        <v>487.8999938964844</v>
+      </c>
+      <c r="I722" t="n">
+        <v>544.2999877929688</v>
+      </c>
+      <c r="J722" t="n">
+        <v>487.8999938964844</v>
+      </c>
+      <c r="K722" t="n">
+        <v>1788207</v>
+      </c>
+      <c r="L722" t="n">
+        <v>-10.36</v>
+      </c>
+      <c r="M722" t="inlineStr">
+        <is>
+          <t>Dynamic Cables (NSE: DYCL) Stock Analysis - Kalkine India</t>
+        </is>
+      </c>
+      <c r="N722" t="inlineStr">
+        <is>
+          <t>Dynamic Cables (NSE: DYCL) Stock Analysis - Kalkine India</t>
+        </is>
+      </c>
+      <c r="O722" t="inlineStr"/>
+      <c r="P722" t="inlineStr"/>
+      <c r="Q722" t="inlineStr"/>
+    </row>
+    <row r="723">
+      <c r="A723" t="inlineStr">
+        <is>
+          <t>2026-09-04 20:18:15 IST</t>
+        </is>
+      </c>
+      <c r="B723" t="n">
+        <v>2</v>
+      </c>
+      <c r="C723" t="inlineStr">
+        <is>
+          <t>JAYNECOIND.NS</t>
+        </is>
+      </c>
+      <c r="D723" t="inlineStr">
+        <is>
+          <t>Jayaswal Neco Industries Limited</t>
+        </is>
+      </c>
+      <c r="E723" t="n">
+        <v>92</v>
+      </c>
+      <c r="F723" t="n">
+        <v>94.37000274658203</v>
+      </c>
+      <c r="G723" t="n">
+        <v>85.22000122070312</v>
+      </c>
+      <c r="H723" t="n">
+        <v>89.04000091552734</v>
+      </c>
+      <c r="I723" t="n">
+        <v>98.68000030517578</v>
+      </c>
+      <c r="J723" t="n">
+        <v>89.04000091552734</v>
+      </c>
+      <c r="K723" t="n">
+        <v>49816021</v>
+      </c>
+      <c r="L723" t="n">
+        <v>-9.77</v>
+      </c>
+      <c r="M723" t="inlineStr">
+        <is>
+          <t>With EPS Growth And More, Jayaswal Neco Industries (NSE:JAYNECOIND) Makes An Interesting Case - simplywall.st</t>
+        </is>
+      </c>
+      <c r="N723" t="inlineStr">
+        <is>
+          <t>With EPS Growth And More, Jayaswal Neco Industries (NSE:JAYNECOIND) Makes An Interesting Case - simplywall.st</t>
+        </is>
+      </c>
+      <c r="O723" t="inlineStr"/>
+      <c r="P723" t="inlineStr"/>
+      <c r="Q723" t="inlineStr"/>
+    </row>
+    <row r="724">
+      <c r="A724" t="inlineStr">
+        <is>
+          <t>2026-09-04 20:18:15 IST</t>
+        </is>
+      </c>
+      <c r="B724" t="n">
+        <v>3</v>
+      </c>
+      <c r="C724" t="inlineStr">
+        <is>
+          <t>UGARSUGAR.NS</t>
+        </is>
+      </c>
+      <c r="D724" t="inlineStr">
+        <is>
+          <t>The Ugar Sugar Works Limited</t>
+        </is>
+      </c>
+      <c r="E724" t="n">
+        <v>58.40000152587891</v>
+      </c>
+      <c r="F724" t="n">
+        <v>58.5</v>
+      </c>
+      <c r="G724" t="n">
+        <v>53.0099983215332</v>
+      </c>
+      <c r="H724" t="n">
+        <v>53.34999847412109</v>
+      </c>
+      <c r="I724" t="n">
+        <v>58.56000137329102</v>
+      </c>
+      <c r="J724" t="n">
+        <v>53.34999847412109</v>
+      </c>
+      <c r="K724" t="n">
+        <v>1343466</v>
+      </c>
+      <c r="L724" t="n">
+        <v>-8.9</v>
+      </c>
+      <c r="M724" t="inlineStr">
+        <is>
+          <t>Ugar Sugar Works (NSE: UGARSUGAR) Analysis - Kalkine India</t>
+        </is>
+      </c>
+      <c r="N724" t="inlineStr">
+        <is>
+          <t>Ugar Sugar Works (NSE: UGARSUGAR) Analysis - Kalkine India</t>
+        </is>
+      </c>
+      <c r="O724" t="inlineStr">
+        <is>
+          <t>The Ugar Sugar Works Share Price Today: Fall and Analysis - Univest</t>
+        </is>
+      </c>
+      <c r="P724" t="inlineStr">
+        <is>
+          <t>Ugar Sugar Works director Hari Athawale retires, Prafulla Shirgaokar resigns from board - ChiniMandi</t>
+        </is>
+      </c>
+      <c r="Q724" t="inlineStr"/>
+    </row>
+    <row r="725">
+      <c r="A725" t="inlineStr">
+        <is>
+          <t>2026-09-04 20:18:15 IST</t>
+        </is>
+      </c>
+      <c r="B725" t="n">
+        <v>4</v>
+      </c>
+      <c r="C725" t="inlineStr">
+        <is>
+          <t>JAYKAY.NS</t>
+        </is>
+      </c>
+      <c r="D725" t="inlineStr">
+        <is>
+          <t>Jaykay Enterprises Limited</t>
+        </is>
+      </c>
+      <c r="E725" t="n">
+        <v>165.3699951171875</v>
+      </c>
+      <c r="F725" t="n">
+        <v>167.8800048828125</v>
+      </c>
+      <c r="G725" t="n">
+        <v>151.7599945068359</v>
+      </c>
+      <c r="H725" t="n">
+        <v>153.6900024414062</v>
+      </c>
+      <c r="I725" t="n">
+        <v>166.4600067138672</v>
+      </c>
+      <c r="J725" t="n">
+        <v>153.6900024414062</v>
+      </c>
+      <c r="K725" t="n">
+        <v>470343</v>
+      </c>
+      <c r="L725" t="n">
+        <v>-7.67</v>
+      </c>
+      <c r="M725" t="inlineStr">
+        <is>
+          <t>Jaykay Enterprises board meets May 27 to approve FY26 results - scanx.trade</t>
+        </is>
+      </c>
+      <c r="N725" t="inlineStr">
+        <is>
+          <t>Federal-Mogul Goetze (India) Ltd leads losers in 'B' group - Business Standard</t>
+        </is>
+      </c>
+      <c r="O725" t="inlineStr">
+        <is>
+          <t>Jaykay Enterprises files Letter of Offer for ₹154.28 crore rights issue - scanx.trade</t>
+        </is>
+      </c>
+      <c r="P725" t="inlineStr">
+        <is>
+          <t>Jaykay Enterprises schedules 80th AGM for Sep 29 via video conferencing - scanx.trade</t>
+        </is>
+      </c>
+      <c r="Q725" t="inlineStr">
+        <is>
+          <t>Jaykay Enterprises Ltd. Key Financial Ratios – Valuation, Profitability &amp; More - Value Research</t>
+        </is>
+      </c>
+    </row>
+    <row r="726">
+      <c r="A726" t="inlineStr">
+        <is>
+          <t>2026-09-04 20:18:15 IST</t>
+        </is>
+      </c>
+      <c r="B726" t="n">
+        <v>5</v>
+      </c>
+      <c r="C726" t="inlineStr">
+        <is>
+          <t>HIKAL.NS</t>
+        </is>
+      </c>
+      <c r="D726" t="inlineStr">
+        <is>
+          <t>Hikal Limited</t>
+        </is>
+      </c>
+      <c r="E726" t="n">
+        <v>234</v>
+      </c>
+      <c r="F726" t="n">
+        <v>236.7400054931641</v>
+      </c>
+      <c r="G726" t="n">
+        <v>220.1000061035156</v>
+      </c>
+      <c r="H726" t="n">
+        <v>222.3000030517578</v>
+      </c>
+      <c r="I726" t="n">
+        <v>240.3600006103516</v>
+      </c>
+      <c r="J726" t="n">
+        <v>222.3000030517578</v>
+      </c>
+      <c r="K726" t="n">
+        <v>5351852</v>
+      </c>
+      <c r="L726" t="n">
+        <v>-7.51</v>
+      </c>
+      <c r="M726" t="inlineStr">
+        <is>
+          <t>Hikal Ltd Shares Hit Intraday Low Amid Price Pressure on 4 Sep 2026 - MarketsMojo</t>
+        </is>
+      </c>
+      <c r="N726" t="inlineStr">
+        <is>
+          <t>Hikal Ltd Shares Hit Intraday Low Amid Price Pressure on 4 Sep 2026 - MarketsMojo</t>
+        </is>
+      </c>
+      <c r="O726" t="inlineStr">
+        <is>
+          <t>Hikal Ltd. Share Price Rise: Price Action and Fundamentals - Univest</t>
+        </is>
+      </c>
+      <c r="P726" t="inlineStr">
+        <is>
+          <t>Don't Race Out To Buy Hikal Limited (NSE:HIKAL) Just Because It's Going Ex-Dividend - simplywall.st</t>
+        </is>
+      </c>
+      <c r="Q726" t="inlineStr">
+        <is>
+          <t>Hikal files FY26 sustainability report with ESG metrics - scanx.trade</t>
+        </is>
+      </c>
+    </row>
+    <row r="727">
+      <c r="A727" t="inlineStr">
+        <is>
+          <t>2026-09-04 20:18:15 IST</t>
+        </is>
+      </c>
+      <c r="B727" t="n">
+        <v>6</v>
+      </c>
+      <c r="C727" t="inlineStr">
+        <is>
+          <t>AUTOIND.NS</t>
+        </is>
+      </c>
+      <c r="D727" t="inlineStr">
+        <is>
+          <t>Autoline Industries Limited</t>
+        </is>
+      </c>
+      <c r="E727" t="n">
+        <v>94</v>
+      </c>
+      <c r="F727" t="n">
+        <v>95.90000152587891</v>
+      </c>
+      <c r="G727" t="n">
+        <v>85.20999908447266</v>
+      </c>
+      <c r="H727" t="n">
+        <v>86.44999694824219</v>
+      </c>
+      <c r="I727" t="n">
+        <v>92.75</v>
+      </c>
+      <c r="J727" t="n">
+        <v>86.44999694824219</v>
+      </c>
+      <c r="K727" t="n">
+        <v>591037</v>
+      </c>
+      <c r="L727" t="n">
+        <v>-6.79</v>
+      </c>
+      <c r="M727" t="inlineStr">
+        <is>
+          <t>Autoline Industries Share Price Rise; Valuation in Focus - Univest</t>
+        </is>
+      </c>
+      <c r="N727" t="inlineStr">
+        <is>
+          <t>Autoline Industries AUTOIND 30th AGM Notice September 2026 - Kalkine India</t>
+        </is>
+      </c>
+      <c r="O727" t="inlineStr">
+        <is>
+          <t>Autoline Industries Wins ₹100 Crore Tata Motors Order - HDFC Sky</t>
+        </is>
+      </c>
+      <c r="P727" t="inlineStr">
+        <is>
+          <t>ISTLTD Stock Price and Chart — NSE:ISTLTD - TradingView</t>
+        </is>
+      </c>
+      <c r="Q727" t="inlineStr">
+        <is>
+          <t>Autoline Industries Ltd. Share Price: Near 52-Week High - Univest</t>
+        </is>
+      </c>
+    </row>
+    <row r="728">
+      <c r="A728" t="inlineStr">
+        <is>
+          <t>2026-09-04 20:18:15 IST</t>
+        </is>
+      </c>
+      <c r="B728" t="n">
+        <v>7</v>
+      </c>
+      <c r="C728" t="inlineStr">
+        <is>
+          <t>RRKABEL.NS</t>
+        </is>
+      </c>
+      <c r="D728" t="inlineStr">
+        <is>
+          <t>R R Kabel Limited</t>
+        </is>
+      </c>
+      <c r="E728" t="n">
+        <v>2550</v>
+      </c>
+      <c r="F728" t="n">
+        <v>2609</v>
+      </c>
+      <c r="G728" t="n">
+        <v>2374.39990234375</v>
+      </c>
+      <c r="H728" t="n">
+        <v>2454.10009765625</v>
+      </c>
+      <c r="I728" t="n">
+        <v>2617.699951171875</v>
+      </c>
+      <c r="J728" t="n">
+        <v>2454.10009765625</v>
+      </c>
+      <c r="K728" t="n">
+        <v>2596647</v>
+      </c>
+      <c r="L728" t="n">
+        <v>-6.25</v>
+      </c>
+      <c r="M728" t="inlineStr">
+        <is>
+          <t>RR Kabel, KEI Industries, Polycab India shares tumble; JM Financial downgrades stocks, revises targets - businesstoday.in</t>
+        </is>
+      </c>
+      <c r="N728" t="inlineStr">
+        <is>
+          <t>RR Kabel, KEI Industries, Polycab India shares tumble; JM Financial downgrades stocks, revises targets - businesstoday.in</t>
+        </is>
+      </c>
+      <c r="O728" t="inlineStr">
+        <is>
+          <t>RR Kabel Share Price Near 52-Week High Analysis - Univest</t>
+        </is>
+      </c>
+      <c r="P728" t="inlineStr">
+        <is>
+          <t>RR Kabel Share Price at fresh 52-week high: analysis - Univest</t>
+        </is>
+      </c>
+      <c r="Q728" t="inlineStr">
+        <is>
+          <t>RR Kabel Share Price Falls 2.72%: Price, Valuation View - Univest</t>
+        </is>
+      </c>
+    </row>
+    <row r="729">
+      <c r="A729" t="inlineStr">
+        <is>
+          <t>2026-09-04 20:18:15 IST</t>
+        </is>
+      </c>
+      <c r="B729" t="n">
+        <v>8</v>
+      </c>
+      <c r="C729" t="inlineStr">
+        <is>
+          <t>LANDSMILL.NS</t>
+        </is>
+      </c>
+      <c r="D729" t="inlineStr">
+        <is>
+          <t>Landsmill Green Limited</t>
+        </is>
+      </c>
+      <c r="E729" t="n">
+        <v>0.6700000166893005</v>
+      </c>
+      <c r="F729" t="n">
+        <v>0.7099999785423279</v>
+      </c>
+      <c r="G729" t="n">
+        <v>0.6299999952316284</v>
+      </c>
+      <c r="H729" t="n">
+        <v>0.6299999952316284</v>
+      </c>
+      <c r="I729" t="n">
+        <v>0.6700000166893005</v>
+      </c>
+      <c r="J729" t="n">
+        <v>0.6299999952316284</v>
+      </c>
+      <c r="K729" t="n">
+        <v>10120631</v>
+      </c>
+      <c r="L729" t="n">
+        <v>-5.97</v>
+      </c>
+      <c r="M729" t="inlineStr">
+        <is>
+          <t>Landsmill Green - 14 penny stocks plunge up to 85% in 6 months. Are you holding any? - economictimes.com</t>
+        </is>
+      </c>
+      <c r="N729" t="inlineStr">
+        <is>
+          <t>Landsmill Green board to delete FMCG object, close subsidiary on Sep 4 - scanx.trade</t>
+        </is>
+      </c>
+      <c r="O729" t="inlineStr">
+        <is>
+          <t>Landsmill Green Q1 Results: Net profit up 987% YoY to ₹85.4 lakh - scanx.trade</t>
+        </is>
+      </c>
+      <c r="P729" t="inlineStr">
+        <is>
+          <t>Landsmill Green board to delete FMCG object, close subsidiary on Sep 4 - scanx.trade</t>
+        </is>
+      </c>
+      <c r="Q729" t="inlineStr"/>
+    </row>
+    <row r="730">
+      <c r="A730" t="inlineStr">
+        <is>
+          <t>2026-09-04 20:18:15 IST</t>
+        </is>
+      </c>
+      <c r="B730" t="n">
+        <v>9</v>
+      </c>
+      <c r="C730" t="inlineStr">
+        <is>
+          <t>POLYCAB.NS</t>
+        </is>
+      </c>
+      <c r="D730" t="inlineStr">
+        <is>
+          <t>Polycab India Limited</t>
+        </is>
+      </c>
+      <c r="E730" t="n">
+        <v>8500</v>
+      </c>
+      <c r="F730" t="n">
+        <v>8500</v>
+      </c>
+      <c r="G730" t="n">
+        <v>8250</v>
+      </c>
+      <c r="H730" t="n">
+        <v>8300</v>
+      </c>
+      <c r="I730" t="n">
+        <v>8807.5</v>
+      </c>
+      <c r="J730" t="n">
+        <v>8300</v>
+      </c>
+      <c r="K730" t="n">
+        <v>1559219</v>
+      </c>
+      <c r="L730" t="n">
+        <v>-5.76</v>
+      </c>
+      <c r="M730" t="inlineStr">
+        <is>
+          <t>Polycab, KEI Industries shares crash up to 9% after UltraTech Cement enters wires &amp; cables business. What - economictimes.com</t>
+        </is>
+      </c>
+      <c r="N730" t="inlineStr">
+        <is>
+          <t>Polycab falls 7% on UltraTech's foray into wires and cables even as JPMorgan allays fears; should you buy,... - Moneycontrol.com</t>
+        </is>
+      </c>
+      <c r="O730" t="inlineStr">
+        <is>
+          <t>Polycab, KEI Industries Shares up to 8% as Ultratech Enters Wires &amp; Cables Business with Ultravolt - India Infoline</t>
+        </is>
+      </c>
+      <c r="P730" t="inlineStr">
+        <is>
+          <t>Copper Shock Hits Cables Stocks: Polycab, Finolex, RR Kabel Slide Up To 6% After Price Hikes - NDTV Profit</t>
+        </is>
+      </c>
+      <c r="Q730" t="inlineStr">
+        <is>
+          <t>Polycab valuations correcting to these levels will be a buying opportunity, JPMorgan says - CNBC TV18</t>
+        </is>
+      </c>
+    </row>
+    <row r="731">
+      <c r="A731" t="inlineStr">
+        <is>
+          <t>2026-09-04 20:18:15 IST</t>
+        </is>
+      </c>
+      <c r="B731" t="n">
+        <v>10</v>
+      </c>
+      <c r="C731" t="inlineStr">
+        <is>
+          <t>SKYWAYS.NS</t>
+        </is>
+      </c>
+      <c r="D731" t="inlineStr">
+        <is>
+          <t>Skyways Air Services Limited</t>
+        </is>
+      </c>
+      <c r="E731" t="n">
+        <v>131.5</v>
+      </c>
+      <c r="F731" t="n">
+        <v>133.6499938964844</v>
+      </c>
+      <c r="G731" t="n">
+        <v>120.0999984741211</v>
+      </c>
+      <c r="H731" t="n">
+        <v>122.7200012207031</v>
+      </c>
+      <c r="I731" t="n">
+        <v>130.0599975585938</v>
+      </c>
+      <c r="J731" t="n">
+        <v>122.7200012207031</v>
+      </c>
+      <c r="K731" t="n">
+        <v>8334295</v>
+      </c>
+      <c r="L731" t="n">
+        <v>-5.64</v>
+      </c>
+      <c r="M731" t="inlineStr">
+        <is>
+          <t>Skyways Air Services shares list at 9% discount to IPO price on NSE, BSE - Moneycontrol.com</t>
+        </is>
+      </c>
+      <c r="N731" t="inlineStr">
+        <is>
+          <t>Skyways Air Services Shares List 10% Below IPO Price; Defies Grey Market Expectations - BW Businessworld</t>
+        </is>
+      </c>
+      <c r="O731" t="inlineStr">
+        <is>
+          <t>Skyways Air Services shares defy GMP expectations, list at 10% discount - Business Standard</t>
+        </is>
+      </c>
+      <c r="P731" t="inlineStr">
+        <is>
+          <t>Skyways Air Services tumble over 10% on market debut - BusinessLine</t>
+        </is>
+      </c>
+      <c r="Q731" t="inlineStr">
+        <is>
+          <t>Skyways Air Services listing: Shares list at 10.1% discount compare to IPO price on NSE - Upstox</t>
+        </is>
+      </c>
+    </row>
+    <row r="732">
+      <c r="A732" t="inlineStr">
+        <is>
+          <t>2026-09-04 20:18:15 IST</t>
+        </is>
+      </c>
+      <c r="B732" t="n">
+        <v>11</v>
+      </c>
+      <c r="C732" t="inlineStr">
+        <is>
+          <t>ANTELOPUS.NS</t>
+        </is>
+      </c>
+      <c r="D732" t="inlineStr">
+        <is>
+          <t>Antelopus Selan Energy Limited</t>
+        </is>
+      </c>
+      <c r="E732" t="n">
+        <v>1001</v>
+      </c>
+      <c r="F732" t="n">
+        <v>1028.800048828125</v>
+      </c>
+      <c r="G732" t="n">
+        <v>925.2000122070312</v>
+      </c>
+      <c r="H732" t="n">
+        <v>957.1500244140625</v>
+      </c>
+      <c r="I732" t="n">
+        <v>1013.299987792969</v>
+      </c>
+      <c r="J732" t="n">
+        <v>957.1500244140625</v>
+      </c>
+      <c r="K732" t="n">
+        <v>4816041</v>
+      </c>
+      <c r="L732" t="n">
+        <v>-5.54</v>
+      </c>
+      <c r="M732" t="inlineStr">
+        <is>
+          <t>Antelopus Selan Energy shares rally 20% to 52-week high; what investors need to know - Upstox</t>
+        </is>
+      </c>
+      <c r="N732" t="inlineStr">
+        <is>
+          <t>Why did Antelopus Selan Energy's shares jump over 32% in 4 days? | The stock has rallied 636% in 5 years | Inshorts - Inshorts</t>
+        </is>
+      </c>
+      <c r="O732" t="inlineStr">
+        <is>
+          <t>Antelopus Selan Energy share price up over 32% up in 3 days - What's behind continuous stock jump? Details here - Livemint</t>
+        </is>
+      </c>
+      <c r="P732" t="inlineStr">
+        <is>
+          <t>Multibagger Smallcap Stock Jumps Over 15% In Trade. Here's Why - NDTV Profit</t>
+        </is>
+      </c>
+      <c r="Q732" t="inlineStr">
+        <is>
+          <t>Antelopus Selan Energy promoter declares no encumbrance in FY26 - scanx.trade</t>
+        </is>
+      </c>
+    </row>
+    <row r="733">
+      <c r="A733" t="inlineStr">
+        <is>
+          <t>2026-09-04 20:18:15 IST</t>
+        </is>
+      </c>
+      <c r="B733" t="n">
+        <v>12</v>
+      </c>
+      <c r="C733" t="inlineStr">
+        <is>
+          <t>TCC.NS</t>
+        </is>
+      </c>
+      <c r="D733" t="inlineStr">
+        <is>
+          <t>TCC Concept Limited</t>
+        </is>
+      </c>
+      <c r="E733" t="n">
+        <v>47.33000183105469</v>
+      </c>
+      <c r="F733" t="n">
+        <v>49.22000122070312</v>
+      </c>
+      <c r="G733" t="n">
+        <v>43.79999923706055</v>
+      </c>
+      <c r="H733" t="n">
+        <v>44.09999847412109</v>
+      </c>
+      <c r="I733" t="n">
+        <v>46.62599945068359</v>
+      </c>
+      <c r="J733" t="n">
+        <v>44.09999847412109</v>
+      </c>
+      <c r="K733" t="n">
+        <v>578461</v>
+      </c>
+      <c r="L733" t="n">
+        <v>-5.42</v>
+      </c>
+      <c r="M733" t="inlineStr">
+        <is>
+          <t>TCC Concept signs MOU for 60 MW data centre campus in Pune - scanx.trade</t>
+        </is>
+      </c>
+      <c r="N733" t="inlineStr">
+        <is>
+          <t>Taiwan Cement stock falls as volume and margins draw focus - ad-hoc-news.de</t>
+        </is>
+      </c>
+      <c r="O733" t="inlineStr">
+        <is>
+          <t>Volume Gainers as of 12:25 PM IST, Mumbai, August 26: Indo Thai Securities, TCC Concept Lead Trading Surge - HDFC Sky</t>
+        </is>
+      </c>
+      <c r="P733" t="inlineStr">
+        <is>
+          <t>TCC CONCEPT Consolidated June 2026 Net Sales at Rs 128.28 crore, up 480.19% Y-o-Y - Moneycontrol.com</t>
+        </is>
+      </c>
+      <c r="Q733" t="inlineStr">
+        <is>
+          <t>TCC Concept fixes September 4 record date for 1:5 share split - scanx.trade</t>
+        </is>
+      </c>
+    </row>
+    <row r="734">
+      <c r="A734" t="inlineStr">
+        <is>
+          <t>2026-09-04 20:18:15 IST</t>
+        </is>
+      </c>
+      <c r="B734" t="n">
+        <v>13</v>
+      </c>
+      <c r="C734" t="inlineStr">
+        <is>
+          <t>MAKERSL.NS</t>
+        </is>
+      </c>
+      <c r="D734" t="inlineStr">
+        <is>
+          <t>Makers Laboratories Limited</t>
+        </is>
+      </c>
+      <c r="E734" t="n">
+        <v>206.8500061035156</v>
+      </c>
+      <c r="F734" t="n">
+        <v>206.8500061035156</v>
+      </c>
+      <c r="G734" t="n">
+        <v>188.3999938964844</v>
+      </c>
+      <c r="H734" t="n">
+        <v>189.8999938964844</v>
+      </c>
+      <c r="I734" t="n">
+        <v>200.7700042724609</v>
+      </c>
+      <c r="J734" t="n">
+        <v>189.8999938964844</v>
+      </c>
+      <c r="K734" t="n">
+        <v>6513</v>
+      </c>
+      <c r="L734" t="n">
+        <v>-5.41</v>
+      </c>
+      <c r="M734" t="inlineStr">
+        <is>
+          <t>Makers Laboratories Share Price rise: fundamentals and peers - Univest</t>
+        </is>
+      </c>
+      <c r="N734" t="inlineStr">
+        <is>
+          <t>Makers Laboratories Share Price rise: fundamentals and peers - Univest</t>
+        </is>
+      </c>
+      <c r="O734" t="inlineStr">
+        <is>
+          <t>Makers Laboratories Ltd. (MAKERSL) Fundamental and Financial Data - Stocktwits</t>
+        </is>
+      </c>
+      <c r="P734" t="inlineStr">
+        <is>
+          <t>Makers Laboratories Q1 Results: Consolidated Net Profit Surges 244% YoY to ₹150.43 lacs - scanx.trade</t>
+        </is>
+      </c>
+      <c r="Q734" t="inlineStr"/>
+    </row>
+    <row r="735">
+      <c r="A735" t="inlineStr">
+        <is>
+          <t>2026-09-04 20:18:15 IST</t>
+        </is>
+      </c>
+      <c r="B735" t="n">
+        <v>14</v>
+      </c>
+      <c r="C735" t="inlineStr">
+        <is>
+          <t>DHAMPURSUG.NS</t>
+        </is>
+      </c>
+      <c r="D735" t="inlineStr">
+        <is>
+          <t>Dhampur Sugar Mills Limited</t>
+        </is>
+      </c>
+      <c r="E735" t="n">
+        <v>176.4499969482422</v>
+      </c>
+      <c r="F735" t="n">
+        <v>176.4499969482422</v>
+      </c>
+      <c r="G735" t="n">
+        <v>165.6300048828125</v>
+      </c>
+      <c r="H735" t="n">
+        <v>167.5899963378906</v>
+      </c>
+      <c r="I735" t="n">
+        <v>177.0500030517578</v>
+      </c>
+      <c r="J735" t="n">
+        <v>167.5899963378906</v>
+      </c>
+      <c r="K735" t="n">
+        <v>831577</v>
+      </c>
+      <c r="L735" t="n">
+        <v>-5.34</v>
+      </c>
+      <c r="M735" t="inlineStr">
+        <is>
+          <t>Dhampur Sugar Mills Ltd. Share Price: 52-Week High Focus - Univest</t>
+        </is>
+      </c>
+      <c r="N735" t="inlineStr">
+        <is>
+          <t>Dhampur Sugar Mills net profit rises 569% to ₹6.09 crore in Q1FY27 - scanx.trade</t>
+        </is>
+      </c>
+      <c r="O735" t="inlineStr">
+        <is>
+          <t>Dhampur Sugar Mills net profit rises 569% to ₹6.09 crore in Q1FY27 - scanx.trade</t>
+        </is>
+      </c>
+      <c r="P735" t="inlineStr"/>
+      <c r="Q735" t="inlineStr"/>
+    </row>
+    <row r="736">
+      <c r="A736" t="inlineStr">
+        <is>
+          <t>2026-09-04 20:18:15 IST</t>
+        </is>
+      </c>
+      <c r="B736" t="n">
+        <v>15</v>
+      </c>
+      <c r="C736" t="inlineStr">
+        <is>
+          <t>ANNAPURNA.NS</t>
+        </is>
+      </c>
+      <c r="D736" t="inlineStr">
+        <is>
+          <t>Annapurna Swadisht Limited</t>
+        </is>
+      </c>
+      <c r="E736" t="n">
+        <v>151.4499969482422</v>
+      </c>
+      <c r="F736" t="n">
+        <v>151.4499969482422</v>
+      </c>
+      <c r="G736" t="n">
+        <v>139</v>
+      </c>
+      <c r="H736" t="n">
+        <v>140.1999969482422</v>
+      </c>
+      <c r="I736" t="n">
+        <v>147.7799987792969</v>
+      </c>
+      <c r="J736" t="n">
+        <v>140.1999969482422</v>
+      </c>
+      <c r="K736" t="n">
+        <v>96796</v>
+      </c>
+      <c r="L736" t="n">
+        <v>-5.13</v>
+      </c>
+      <c r="M736" t="inlineStr">
+        <is>
+          <t>Annapurna Swadisht Ltd. Shareholding Pattern – Promoters, FIIs &amp; DIIs - Value Research</t>
+        </is>
+      </c>
+      <c r="N736" t="inlineStr">
+        <is>
+          <t>Annapurna Studios expands distribution slate with Dulquer Salmaan’s I’m Game, Karthi’s Sardar 2 and... - Moneycontrol.com</t>
+        </is>
+      </c>
+      <c r="O736" t="inlineStr">
+        <is>
+          <t>Annapurna gets ‘Annapurna Bhandar’ benefits: Mamata Banerjee thanks CM Suvendu and leaves one wondering - Bhaskar English</t>
+        </is>
+      </c>
+      <c r="P736" t="inlineStr">
+        <is>
+          <t>Annapurna Studios expands distribution slate with Dulquer Salmaan’s I’m Game, Karthi’s Sardar 2 and... - Moneycontrol.com</t>
+        </is>
+      </c>
+      <c r="Q736" t="inlineStr"/>
+    </row>
+    <row r="737">
+      <c r="A737" t="inlineStr">
+        <is>
+          <t>2026-09-04 20:18:15 IST</t>
+        </is>
+      </c>
+      <c r="B737" t="n">
+        <v>16</v>
+      </c>
+      <c r="C737" t="inlineStr">
+        <is>
+          <t>TARMAT.NS</t>
+        </is>
+      </c>
+      <c r="D737" t="inlineStr">
+        <is>
+          <t>Tarmat Limited</t>
+        </is>
+      </c>
+      <c r="E737" t="n">
+        <v>64.48999786376953</v>
+      </c>
+      <c r="F737" t="n">
+        <v>64.79000091552734</v>
+      </c>
+      <c r="G737" t="n">
+        <v>60.54999923706055</v>
+      </c>
+      <c r="H737" t="n">
+        <v>61.22999954223633</v>
+      </c>
+      <c r="I737" t="n">
+        <v>64.48999786376953</v>
+      </c>
+      <c r="J737" t="n">
+        <v>61.22999954223633</v>
+      </c>
+      <c r="K737" t="n">
+        <v>36266</v>
+      </c>
+      <c r="L737" t="n">
+        <v>-5.06</v>
+      </c>
+      <c r="M737" t="inlineStr">
+        <is>
+          <t>Tarmat schedules AGM to approve board reappointments and salary hikes - scanx.trade</t>
+        </is>
+      </c>
+      <c r="N737" t="inlineStr">
+        <is>
+          <t>Tarmat schedules AGM to approve board reappointments and salary hikes - scanx.trade</t>
+        </is>
+      </c>
+      <c r="O737" t="inlineStr">
+        <is>
+          <t>Tarmat Ltd. Financials – Balance Sheet, Profit &amp; Loss, Cash Flow - Value Research</t>
+        </is>
+      </c>
+      <c r="P737" t="inlineStr">
+        <is>
+          <t>Tarmat Ltd. Share Price rise with market cap at Rs 128.43 Cr - Univest</t>
+        </is>
+      </c>
+      <c r="Q737" t="inlineStr">
+        <is>
+          <t>Tarmat consolidated net profit rises 121.74% in the June 2026 quarter - Business Standard</t>
+        </is>
+      </c>
+    </row>
+    <row r="738">
+      <c r="A738" t="inlineStr">
+        <is>
+          <t>2026-09-04 20:18:15 IST</t>
+        </is>
+      </c>
+      <c r="B738" t="n">
+        <v>17</v>
+      </c>
+      <c r="C738" t="inlineStr">
+        <is>
+          <t>NIRAJISPAT.NS</t>
+        </is>
+      </c>
+      <c r="D738" t="inlineStr">
+        <is>
+          <t>Niraj Ispat Industries Limited</t>
+        </is>
+      </c>
+      <c r="E738" t="n">
+        <v>387.7999877929688</v>
+      </c>
+      <c r="F738" t="n">
+        <v>387.7999877929688</v>
+      </c>
+      <c r="G738" t="n">
+        <v>387.7999877929688</v>
+      </c>
+      <c r="H738" t="n">
+        <v>387.7999877929688</v>
+      </c>
+      <c r="I738" t="n">
+        <v>408.2000122070312</v>
+      </c>
+      <c r="J738" t="n">
+        <v>387.7999877929688</v>
+      </c>
+      <c r="K738" t="n">
+        <v>601</v>
+      </c>
+      <c r="L738" t="n">
+        <v>-5</v>
+      </c>
+      <c r="M738" t="inlineStr">
+        <is>
+          <t>Niraj (NIRAJISPAT.NS) Stock: Closes with Little Net Change at ₹216.00 in the Available Record; Range Check: the Price Remains Bounded by the Supplied Support and Resistance for the Current Session - ALMA Signal - siam.in</t>
+        </is>
+      </c>
+      <c r="N738" t="inlineStr">
+        <is>
+          <t>Precision Wires and 11 Other Stocks That Hit the 20% Upper Circuit Today; Are You Holding Any? - tradebrains.in</t>
+        </is>
+      </c>
+      <c r="O738" t="inlineStr">
+        <is>
+          <t>Precision Wires and 11 Other Stocks That Hit the 20% Upper Circuit Today; Are You Holding Any? - tradebrains.in</t>
+        </is>
+      </c>
+      <c r="P738" t="inlineStr"/>
+      <c r="Q738" t="inlineStr"/>
+    </row>
+    <row r="739">
+      <c r="A739" t="inlineStr">
+        <is>
+          <t>2026-09-04 20:18:15 IST</t>
+        </is>
+      </c>
+      <c r="B739" t="n">
+        <v>18</v>
+      </c>
+      <c r="C739" t="inlineStr">
+        <is>
+          <t>KJMCFIN.NS</t>
+        </is>
+      </c>
+      <c r="D739" t="inlineStr">
+        <is>
+          <t>KJMC Financial Services Limited</t>
+        </is>
+      </c>
+      <c r="E739" t="n">
+        <v>66.79000091552734</v>
+      </c>
+      <c r="F739" t="n">
+        <v>68</v>
+      </c>
+      <c r="G739" t="n">
+        <v>63.13999938964844</v>
+      </c>
+      <c r="H739" t="n">
+        <v>63.13999938964844</v>
+      </c>
+      <c r="I739" t="n">
+        <v>66.45999908447266</v>
+      </c>
+      <c r="J739" t="n">
+        <v>63.13999938964844</v>
+      </c>
+      <c r="K739" t="n">
+        <v>2504</v>
+      </c>
+      <c r="L739" t="n">
+        <v>-5</v>
+      </c>
+      <c r="M739" t="inlineStr">
+        <is>
+          <t>KJMC Financial Services Ltd. (KJMCFIN) Share Price Today, Quote, Latest Discussions, Interactive Chart and News - Stocktwits</t>
+        </is>
+      </c>
+      <c r="N739" t="inlineStr">
+        <is>
+          <t>KJMC Financial Services Ltd. (KJMCFIN) Fundamental and Financial Data - Stocktwits</t>
+        </is>
+      </c>
+      <c r="O739" t="inlineStr">
+        <is>
+          <t>KJMC Financial Services Ltd. (KJMCFIN) Fundamental and Financial Data - Stocktwits</t>
+        </is>
+      </c>
+      <c r="P739" t="inlineStr">
+        <is>
+          <t>KJMC Financial Services Ltd. (KJMCFIN) sentiment score, message volume, participation score and buzz level - Stocktwits</t>
+        </is>
+      </c>
+      <c r="Q739" t="inlineStr"/>
+    </row>
+    <row r="740">
+      <c r="A740" t="inlineStr">
+        <is>
+          <t>2026-09-04 20:18:15 IST</t>
+        </is>
+      </c>
+      <c r="B740" t="n">
+        <v>19</v>
+      </c>
+      <c r="C740" t="inlineStr">
+        <is>
+          <t>ANNU.NS</t>
+        </is>
+      </c>
+      <c r="D740" t="inlineStr">
+        <is>
+          <t>Annu Projects Limited</t>
+        </is>
+      </c>
+      <c r="E740" t="n">
+        <v>68.23000335693359</v>
+      </c>
+      <c r="F740" t="n">
+        <v>69</v>
+      </c>
+      <c r="G740" t="n">
+        <v>68.23000335693359</v>
+      </c>
+      <c r="H740" t="n">
+        <v>68.23000335693359</v>
+      </c>
+      <c r="I740" t="n">
+        <v>71.81999969482422</v>
+      </c>
+      <c r="J740" t="n">
+        <v>68.23000335693359</v>
+      </c>
+      <c r="K740" t="n">
+        <v>412213</v>
+      </c>
+      <c r="L740" t="n">
+        <v>-5</v>
+      </c>
+      <c r="M740" t="inlineStr">
+        <is>
+          <t>Weak market debut: Annu Projects shares list at over 27% discount to its IPO price - Moneycontrol.com</t>
+        </is>
+      </c>
+      <c r="N740" t="inlineStr">
+        <is>
+          <t>ANNU PROJECTS LIMITED Share Price - Upstox</t>
+        </is>
+      </c>
+      <c r="O740" t="inlineStr">
+        <is>
+          <t>ANNU PROJECTS LIMITED Share Price - Upstox</t>
+        </is>
+      </c>
+      <c r="P740" t="inlineStr">
+        <is>
+          <t>Weak Start! Annu Projects shares list at 27% discount to IPO price - economictimes.com</t>
+        </is>
+      </c>
+      <c r="Q740" t="inlineStr">
+        <is>
+          <t>Annu Projects Shares List at 27% Discount on NSE - Groww</t>
+        </is>
+      </c>
+    </row>
+    <row r="741">
+      <c r="A741" t="inlineStr">
+        <is>
+          <t>2026-09-04 20:18:15 IST</t>
+        </is>
+      </c>
+      <c r="B741" t="n">
+        <v>20</v>
+      </c>
+      <c r="C741" t="inlineStr">
+        <is>
+          <t>RNBDENIMS.NS</t>
+        </is>
+      </c>
+      <c r="D741" t="inlineStr">
+        <is>
+          <t>R&amp;B Denims Limited</t>
+        </is>
+      </c>
+      <c r="E741" t="n">
+        <v>10.8100004196167</v>
+      </c>
+      <c r="F741" t="n">
+        <v>10.8100004196167</v>
+      </c>
+      <c r="G741" t="n">
+        <v>10.27000045776367</v>
+      </c>
+      <c r="H741" t="n">
+        <v>10.27000045776367</v>
+      </c>
+      <c r="I741" t="n">
+        <v>10.8100004196167</v>
+      </c>
+      <c r="J741" t="n">
+        <v>10.27000045776367</v>
+      </c>
+      <c r="K741" t="n">
+        <v>424488</v>
+      </c>
+      <c r="L741" t="n">
+        <v>-5</v>
+      </c>
+      <c r="M741" t="inlineStr">
+        <is>
+          <t>RNBDENIMS Stock Price and Chart — NSE:RNBDENIMS - TradingView</t>
+        </is>
+      </c>
+      <c r="N741" t="inlineStr">
+        <is>
+          <t>R&amp;B Denims (RNBDENIMS.NS) Slips 1.5%: Testing Key Support Near ₹9.89 - Defined Outcome ETF - vinanet.vn</t>
+        </is>
+      </c>
+      <c r="O741" t="inlineStr">
+        <is>
+          <t>R&amp;B Denims Schedules EGM for March 13 to Approve Stock Split and Corporate Actions - scanx.trade</t>
+        </is>
+      </c>
+      <c r="P741" t="inlineStr">
+        <is>
+          <t>R&amp;B Denims (RNBDENIMS.NS) Slips 1.5%: Testing Key Support Near ₹9.89 - Defined Outcome ETF - vinanet.vn</t>
+        </is>
+      </c>
+      <c r="Q741" t="inlineStr">
+        <is>
+          <t>R&amp;B Denims Limited (RNBDENIMS.NS) Faces Selling Pressure, Holds Above Key Support - Institutional Sentiment - vinanet.vn</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/NEWS_Daily_Report/output/history/NEWS_Daily_Report_History.xlsx
+++ b/NEWS_Daily_Report/output/history/NEWS_Daily_Report_History.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q441"/>
+  <dimension ref="A1:Q461"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21.42578125" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -28237,9 +28237,6 @@
           <t>NR Agarwal Industries Ltd. (NRAIL) Share Price Rises 12.36% Today - Univest</t>
         </is>
       </c>
-      <c r="O424" t="inlineStr"/>
-      <c r="P424" t="inlineStr"/>
-      <c r="Q424" t="inlineStr"/>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
@@ -28432,9 +28429,6 @@
           <t>CFEL Stock Price and Chart — NSE:CFEL - TradingView</t>
         </is>
       </c>
-      <c r="O427" t="inlineStr"/>
-      <c r="P427" t="inlineStr"/>
-      <c r="Q427" t="inlineStr"/>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
@@ -28489,9 +28483,6 @@
           <t>PC Jewellers Share Price - Live NSE: PCJEWELLER Stock Price &amp; Chart - Upstox</t>
         </is>
       </c>
-      <c r="O428" t="inlineStr"/>
-      <c r="P428" t="inlineStr"/>
-      <c r="Q428" t="inlineStr"/>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
@@ -28620,8 +28611,6 @@
           <t>Maral Overseas schedules 37th AGM on August 25 via VC/OAVM - scanx.trade</t>
         </is>
       </c>
-      <c r="P430" t="inlineStr"/>
-      <c r="Q430" t="inlineStr"/>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
@@ -28681,8 +28670,6 @@
           <t>Number of employees of Cyber Media (India) Limited Rights 2025-29.08.25 For Shares – BSE:CYBER_RE - TradingView</t>
         </is>
       </c>
-      <c r="P431" t="inlineStr"/>
-      <c r="Q431" t="inlineStr"/>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
@@ -28747,7 +28734,6 @@
           <t>Saraswati Commercial Q1FY27 net profit surges 169% YoY to ₹635.6 million - scanx.trade</t>
         </is>
       </c>
-      <c r="Q432" t="inlineStr"/>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
@@ -28940,9 +28926,6 @@
           <t>ADVIT JEWELS Share Price update: fundamentals and peers - Univest</t>
         </is>
       </c>
-      <c r="O435" t="inlineStr"/>
-      <c r="P435" t="inlineStr"/>
-      <c r="Q435" t="inlineStr"/>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
@@ -29204,9 +29187,6 @@
           <t>Jain Irrigation (JISLDVREQS.NS) Slips Marginally to ₹21.0: Key Support and Resistance Levels in Focus - Volume Climax - siam.in</t>
         </is>
       </c>
-      <c r="O439" t="inlineStr"/>
-      <c r="P439" t="inlineStr"/>
-      <c r="Q439" t="inlineStr"/>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
@@ -29261,9 +29241,6 @@
           <t>D2C kitchenware startup Curaa raises Rs 40 crore led by 3one4 Capital - economictimes.com</t>
         </is>
       </c>
-      <c r="O440" t="inlineStr"/>
-      <c r="P440" t="inlineStr"/>
-      <c r="Q440" t="inlineStr"/>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
@@ -29331,6 +29308,1362 @@
       <c r="Q441" t="inlineStr">
         <is>
           <t>Lalithaa Jewellery shares make strong market debut at 32% premium; should you buy, sell or hold? - Moneycontrol.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="inlineStr">
+        <is>
+          <t>2026-09-07 12:56:35 IST</t>
+        </is>
+      </c>
+      <c r="B442" t="n">
+        <v>1</v>
+      </c>
+      <c r="C442" t="inlineStr">
+        <is>
+          <t>ALKALI.NS</t>
+        </is>
+      </c>
+      <c r="D442" t="inlineStr">
+        <is>
+          <t>Alkali Metals Limited</t>
+        </is>
+      </c>
+      <c r="E442" t="n">
+        <v>69.98999786376953</v>
+      </c>
+      <c r="F442" t="n">
+        <v>78.66000366210938</v>
+      </c>
+      <c r="G442" t="n">
+        <v>68</v>
+      </c>
+      <c r="H442" t="n">
+        <v>78.66000366210938</v>
+      </c>
+      <c r="I442" t="n">
+        <v>65.55000305175781</v>
+      </c>
+      <c r="J442" t="n">
+        <v>78.66000366210938</v>
+      </c>
+      <c r="K442" t="n">
+        <v>70547</v>
+      </c>
+      <c r="L442" t="n">
+        <v>20</v>
+      </c>
+      <c r="M442" t="inlineStr">
+        <is>
+          <t>Momentum Stocks: Alkali Metals, Deepak Builders jump up to 15% on sheer momentum - Moneycontrol.com</t>
+        </is>
+      </c>
+      <c r="N442" t="inlineStr">
+        <is>
+          <t>Alkali Metals and Deepak Builders Surge on Momentum Trading - whalesbook.com</t>
+        </is>
+      </c>
+      <c r="O442" t="inlineStr">
+        <is>
+          <t>Lords Chloro Alkali Commissions 14.5 MW Solar Plant; Shares Rise 1.33% - HDFC Sky</t>
+        </is>
+      </c>
+      <c r="P442" t="inlineStr">
+        <is>
+          <t>Tuticorin Alkali Chemicals schedules 53rd AGM for September 25, 2026 - scanx.trade</t>
+        </is>
+      </c>
+      <c r="Q442" t="inlineStr">
+        <is>
+          <t>Don't Buy Alkali Metals Limited (NSE:ALKALI) For Its Next Dividend Without Doing These Checks - simplywall.st</t>
+        </is>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="inlineStr">
+        <is>
+          <t>2026-09-07 12:56:35 IST</t>
+        </is>
+      </c>
+      <c r="B443" t="n">
+        <v>2</v>
+      </c>
+      <c r="C443" t="inlineStr">
+        <is>
+          <t>PKTEA.NS</t>
+        </is>
+      </c>
+      <c r="D443" t="inlineStr">
+        <is>
+          <t>The Peria Karamalai Tea &amp; Produce Company Limited</t>
+        </is>
+      </c>
+      <c r="E443" t="n">
+        <v>808</v>
+      </c>
+      <c r="F443" t="n">
+        <v>963.1500244140625</v>
+      </c>
+      <c r="G443" t="n">
+        <v>808</v>
+      </c>
+      <c r="H443" t="n">
+        <v>963.1500244140625</v>
+      </c>
+      <c r="I443" t="n">
+        <v>802.6500244140625</v>
+      </c>
+      <c r="J443" t="n">
+        <v>963.1500244140625</v>
+      </c>
+      <c r="K443" t="n">
+        <v>10527</v>
+      </c>
+      <c r="L443" t="n">
+        <v>20</v>
+      </c>
+      <c r="M443" t="inlineStr">
+        <is>
+          <t>The Peria Karamalai Tea &amp; Produce Company Limited (NSE: PKTEA) Gains 20% as Stock Movement Draws Market Attention - Kalkine India</t>
+        </is>
+      </c>
+      <c r="N443" t="inlineStr">
+        <is>
+          <t>The Peria Karamalai Tea &amp; Produce Company Limited (NSE: PKTEA) Gains 20% as Stock Movement Draws Market Attention - Kalkine India</t>
+        </is>
+      </c>
+      <c r="O443" t="inlineStr">
+        <is>
+          <t>THE P K TEA PROD CO LTD Share Price - Upstox</t>
+        </is>
+      </c>
+      <c r="P443" t="inlineStr"/>
+      <c r="Q443" t="inlineStr"/>
+    </row>
+    <row r="444">
+      <c r="A444" t="inlineStr">
+        <is>
+          <t>2026-09-07 12:56:35 IST</t>
+        </is>
+      </c>
+      <c r="B444" t="n">
+        <v>3</v>
+      </c>
+      <c r="C444" t="inlineStr">
+        <is>
+          <t>ANDHRAPAP.NS</t>
+        </is>
+      </c>
+      <c r="D444" t="inlineStr">
+        <is>
+          <t>ANDHRA PAPER LIMITED</t>
+        </is>
+      </c>
+      <c r="E444" t="n">
+        <v>64.09999847412109</v>
+      </c>
+      <c r="F444" t="n">
+        <v>77.33999633789062</v>
+      </c>
+      <c r="G444" t="n">
+        <v>61.9900016784668</v>
+      </c>
+      <c r="H444" t="n">
+        <v>76.19999694824219</v>
+      </c>
+      <c r="I444" t="n">
+        <v>64.44999694824219</v>
+      </c>
+      <c r="J444" t="n">
+        <v>76.19999694824219</v>
+      </c>
+      <c r="K444" t="n">
+        <v>21270613</v>
+      </c>
+      <c r="L444" t="n">
+        <v>18.23</v>
+      </c>
+      <c r="M444" t="inlineStr">
+        <is>
+          <t>Andhra Paper Rises 3.3% to ₹61.93: Key Levels to Watch - Short Setup Alerts - siam.in</t>
+        </is>
+      </c>
+      <c r="N444" t="inlineStr">
+        <is>
+          <t>APPCB imposes ₹21 crore environmental compensation on Andhra Paper Limited - The Hindu</t>
+        </is>
+      </c>
+      <c r="O444" t="inlineStr">
+        <is>
+          <t>APPCB imposes ₹21 crore environmental compensation on Andhra Paper Limited - The Hindu</t>
+        </is>
+      </c>
+      <c r="P444" t="inlineStr">
+        <is>
+          <t>Andhra Pradesh Deputy CM Pawan Kalyan directs APPCB to initiate action against Andhra Paper Limited for ‘polluting’ Godavari river - The Hindu</t>
+        </is>
+      </c>
+      <c r="Q444" t="inlineStr">
+        <is>
+          <t>Andhra Paper reappoints Saurabh Bangur as MD for five years - scanx.trade</t>
+        </is>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" t="inlineStr">
+        <is>
+          <t>2026-09-07 12:56:35 IST</t>
+        </is>
+      </c>
+      <c r="B445" t="n">
+        <v>4</v>
+      </c>
+      <c r="C445" t="inlineStr">
+        <is>
+          <t>XTRANET.NS</t>
+        </is>
+      </c>
+      <c r="D445" t="inlineStr">
+        <is>
+          <t>Xtranet Technologies Limited</t>
+        </is>
+      </c>
+      <c r="E445" t="n">
+        <v>242</v>
+      </c>
+      <c r="F445" t="n">
+        <v>280</v>
+      </c>
+      <c r="G445" t="n">
+        <v>236.5800018310547</v>
+      </c>
+      <c r="H445" t="n">
+        <v>273.9800109863281</v>
+      </c>
+      <c r="I445" t="n">
+        <v>234.2400054931641</v>
+      </c>
+      <c r="J445" t="n">
+        <v>273.9800109863281</v>
+      </c>
+      <c r="K445" t="n">
+        <v>11559377</v>
+      </c>
+      <c r="L445" t="n">
+        <v>16.97</v>
+      </c>
+      <c r="M445" t="inlineStr">
+        <is>
+          <t>XTRANET TECHNOLOGIES LTD Share Price - Upstox</t>
+        </is>
+      </c>
+      <c r="N445" t="inlineStr">
+        <is>
+          <t>XTRANET TECHNOLOGIES LTD Share Price - Upstox</t>
+        </is>
+      </c>
+      <c r="O445" t="inlineStr">
+        <is>
+          <t>Xtranet Technologies Ltd (XTRANET) Share Price - Business Today</t>
+        </is>
+      </c>
+      <c r="P445" t="inlineStr">
+        <is>
+          <t>XTRANET Technologies Share Price Today after 9.86% gain - Univest</t>
+        </is>
+      </c>
+      <c r="Q445" t="inlineStr">
+        <is>
+          <t>1,970,100 Equity Shares of Xtranet Technologies Limited are subject to a Lock-Up Agreement Ending on 26-AUG-2026. - marketscreener.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" t="inlineStr">
+        <is>
+          <t>2026-09-07 12:56:35 IST</t>
+        </is>
+      </c>
+      <c r="B446" t="n">
+        <v>5</v>
+      </c>
+      <c r="C446" t="inlineStr">
+        <is>
+          <t>DBEIL.NS</t>
+        </is>
+      </c>
+      <c r="D446" t="inlineStr">
+        <is>
+          <t>Deepak Builders &amp; Engineers India Limited</t>
+        </is>
+      </c>
+      <c r="E446" t="n">
+        <v>6.610000133514404</v>
+      </c>
+      <c r="F446" t="n">
+        <v>7.710000038146973</v>
+      </c>
+      <c r="G446" t="n">
+        <v>6.610000133514404</v>
+      </c>
+      <c r="H446" t="n">
+        <v>7.440000057220459</v>
+      </c>
+      <c r="I446" t="n">
+        <v>6.429999828338623</v>
+      </c>
+      <c r="J446" t="n">
+        <v>7.440000057220459</v>
+      </c>
+      <c r="K446" t="n">
+        <v>2025752</v>
+      </c>
+      <c r="L446" t="n">
+        <v>15.71</v>
+      </c>
+      <c r="M446" t="inlineStr">
+        <is>
+          <t>Deepak Builders &amp; Engineers India Limited's (NSE:DBEIL) Stock Has Shown Weakness Lately But Financial Prospects Look Decent: Is The Market Wrong? - simplywall.st</t>
+        </is>
+      </c>
+      <c r="N446" t="inlineStr">
+        <is>
+          <t>Deepak Builders &amp; Engineers India (DBEIL.NS) Slides 4.93% – Key Support at ₹7.69 in Focus - PCR Spike - vinanet.vn</t>
+        </is>
+      </c>
+      <c r="O446" t="inlineStr">
+        <is>
+          <t>Deepak Builders Dispatches Postal Ballot Notice for 1:10 Stock Split Approval - scanx.trade</t>
+        </is>
+      </c>
+      <c r="P446" t="inlineStr">
+        <is>
+          <t>DEEPAK BUILDERS &amp; ENG I L Share Price - Upstox</t>
+        </is>
+      </c>
+      <c r="Q446" t="inlineStr">
+        <is>
+          <t>Deepak Builders &amp; Engineers India (DBEIL.NS) Slides 4.93% – Key Support at ₹7.69 in Focus - PCR Spike - vinanet.vn</t>
+        </is>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" t="inlineStr">
+        <is>
+          <t>2026-09-07 12:56:35 IST</t>
+        </is>
+      </c>
+      <c r="B447" t="n">
+        <v>6</v>
+      </c>
+      <c r="C447" t="inlineStr">
+        <is>
+          <t>GNRL.NS</t>
+        </is>
+      </c>
+      <c r="D447" t="inlineStr">
+        <is>
+          <t>Gujarat Natural Resources Limited</t>
+        </is>
+      </c>
+      <c r="E447" t="n">
+        <v>100</v>
+      </c>
+      <c r="F447" t="n">
+        <v>113.75</v>
+      </c>
+      <c r="G447" t="n">
+        <v>100</v>
+      </c>
+      <c r="H447" t="n">
+        <v>113.5899963378906</v>
+      </c>
+      <c r="I447" t="n">
+        <v>99.26999664306641</v>
+      </c>
+      <c r="J447" t="n">
+        <v>113.5899963378906</v>
+      </c>
+      <c r="K447" t="n">
+        <v>2021677</v>
+      </c>
+      <c r="L447" t="n">
+        <v>14.43</v>
+      </c>
+      <c r="M447" t="inlineStr">
+        <is>
+          <t>GNRL Jun 2026 Earnings: EPS of ₹0.69 Reported with Nil Revenue; Stock Falls 6.87% - Earnings Whisper Number - siam.in</t>
+        </is>
+      </c>
+      <c r="N447" t="inlineStr">
+        <is>
+          <t>Gujarat (GNRL.NS) Outlook: Finishes 0.29% Lower at ₹101.60 on the Day; Key Range: Price Remains Between ₹96.52 Support and ₹106.68 Resistance in the Latest Session - High Conviction Picks - siam.in</t>
+        </is>
+      </c>
+      <c r="O447" t="inlineStr">
+        <is>
+          <t>Gujarat Natural Resources Share Price Rises 8.06% Today - Univest</t>
+        </is>
+      </c>
+      <c r="P447" t="inlineStr">
+        <is>
+          <t>Gujarat (GNRL.NS) Outlook: Finishes 0.29% Lower at ₹101.60 on the Day; Key Range: Price Remains Between ₹96.52 Support and ₹106.68 Resistance in the Latest Session - High Conviction Picks - siam.in</t>
+        </is>
+      </c>
+      <c r="Q447" t="inlineStr">
+        <is>
+          <t>GNRL.NS Jun 2026 Earnings: EPS at ₹0.69 Despite Nil Revenue; Shares Slip 2.72% - Analyst Coverage Count - siam.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" t="inlineStr">
+        <is>
+          <t>2026-09-07 12:56:35 IST</t>
+        </is>
+      </c>
+      <c r="B448" t="n">
+        <v>7</v>
+      </c>
+      <c r="C448" t="inlineStr">
+        <is>
+          <t>PCJEWELLER.NS</t>
+        </is>
+      </c>
+      <c r="D448" t="inlineStr">
+        <is>
+          <t>PC Jeweller Limited</t>
+        </is>
+      </c>
+      <c r="E448" t="n">
+        <v>12.28999996185303</v>
+      </c>
+      <c r="F448" t="n">
+        <v>13.68000030517578</v>
+      </c>
+      <c r="G448" t="n">
+        <v>12.21000003814697</v>
+      </c>
+      <c r="H448" t="n">
+        <v>13.52000045776367</v>
+      </c>
+      <c r="I448" t="n">
+        <v>11.85999965667725</v>
+      </c>
+      <c r="J448" t="n">
+        <v>13.52000045776367</v>
+      </c>
+      <c r="K448" t="n">
+        <v>1551586213</v>
+      </c>
+      <c r="L448" t="n">
+        <v>14</v>
+      </c>
+      <c r="M448" t="inlineStr">
+        <is>
+          <t>PC Jewellers Share Price - Live NSE: PCJEWELLER Stock Price &amp; Chart - Upstox</t>
+        </is>
+      </c>
+      <c r="N448" t="inlineStr">
+        <is>
+          <t>PC Jeweller Stock Update: Shares Jump 11% on Debt Repayment Progress - LatestLY</t>
+        </is>
+      </c>
+      <c r="O448" t="inlineStr">
+        <is>
+          <t>Pc Jeweller Stock Price Forecast. Should You Buy PCJEWELLER.NS? - StockInvest.us</t>
+        </is>
+      </c>
+      <c r="P448" t="inlineStr">
+        <is>
+          <t>PC Jeweller (PCJEWELLER) Share Price Falls 5.09% Today; Stock Analysis and Valuation Check - Univest</t>
+        </is>
+      </c>
+      <c r="Q448" t="inlineStr">
+        <is>
+          <t>Most Active Equities, August 11, 2026, 3:30 PM IST - HDFC Sky</t>
+        </is>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" t="inlineStr">
+        <is>
+          <t>2026-09-07 12:56:35 IST</t>
+        </is>
+      </c>
+      <c r="B449" t="n">
+        <v>8</v>
+      </c>
+      <c r="C449" t="inlineStr">
+        <is>
+          <t>CENTUM.NS</t>
+        </is>
+      </c>
+      <c r="D449" t="inlineStr">
+        <is>
+          <t>Centum Electronics Limited</t>
+        </is>
+      </c>
+      <c r="E449" t="n">
+        <v>3778.199951171875</v>
+      </c>
+      <c r="F449" t="n">
+        <v>4341</v>
+      </c>
+      <c r="G449" t="n">
+        <v>3778.199951171875</v>
+      </c>
+      <c r="H449" t="n">
+        <v>4253.2998046875</v>
+      </c>
+      <c r="I449" t="n">
+        <v>3767.300048828125</v>
+      </c>
+      <c r="J449" t="n">
+        <v>4253.2998046875</v>
+      </c>
+      <c r="K449" t="n">
+        <v>249894</v>
+      </c>
+      <c r="L449" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="M449" t="inlineStr">
+        <is>
+          <t>Centum Electronics Share Price Today Near One-Year High - Univest</t>
+        </is>
+      </c>
+      <c r="N449" t="inlineStr">
+        <is>
+          <t>Centum Electronics Share Price Today Near One-Year High - Univest</t>
+        </is>
+      </c>
+      <c r="O449" t="inlineStr">
+        <is>
+          <t>Centum Electronics Ltd. Stock News - Value Research</t>
+        </is>
+      </c>
+      <c r="P449" t="inlineStr">
+        <is>
+          <t>Centum Electronics to Host Virtual Analyst and Investor Meet on September 9 - theglobeandmail.com</t>
+        </is>
+      </c>
+      <c r="Q449" t="inlineStr">
+        <is>
+          <t>Centum Electronics Ltd. Share Price Today: key stock move - Univest</t>
+        </is>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" t="inlineStr">
+        <is>
+          <t>2026-09-07 12:56:35 IST</t>
+        </is>
+      </c>
+      <c r="B450" t="n">
+        <v>9</v>
+      </c>
+      <c r="C450" t="inlineStr">
+        <is>
+          <t>THEMISMED.NS</t>
+        </is>
+      </c>
+      <c r="D450" t="inlineStr">
+        <is>
+          <t>Themis Medicare Limited</t>
+        </is>
+      </c>
+      <c r="E450" t="n">
+        <v>121.379997253418</v>
+      </c>
+      <c r="F450" t="n">
+        <v>136.25</v>
+      </c>
+      <c r="G450" t="n">
+        <v>119.1699981689453</v>
+      </c>
+      <c r="H450" t="n">
+        <v>135.8899993896484</v>
+      </c>
+      <c r="I450" t="n">
+        <v>120.4199981689453</v>
+      </c>
+      <c r="J450" t="n">
+        <v>135.8899993896484</v>
+      </c>
+      <c r="K450" t="n">
+        <v>2052487</v>
+      </c>
+      <c r="L450" t="n">
+        <v>12.85</v>
+      </c>
+      <c r="M450" t="inlineStr">
+        <is>
+          <t>Themis Medicare Holds Gains at ₹104.51: Key Levels to Monitor for THEMISMED.NS - Jurik MA - siam.in</t>
+        </is>
+      </c>
+      <c r="N450" t="inlineStr">
+        <is>
+          <t>THEMISMED Share Price News: Price Action and Fundamentals - Univest</t>
+        </is>
+      </c>
+      <c r="O450" t="inlineStr">
+        <is>
+          <t>THEMISMED Share Price News: Price Action and Fundamentals - Univest</t>
+        </is>
+      </c>
+      <c r="P450" t="inlineStr">
+        <is>
+          <t>Themis Medicare Share Price Today: price rise and valuation - Univest</t>
+        </is>
+      </c>
+      <c r="Q450" t="inlineStr"/>
+    </row>
+    <row r="451">
+      <c r="A451" t="inlineStr">
+        <is>
+          <t>2026-09-07 12:56:35 IST</t>
+        </is>
+      </c>
+      <c r="B451" t="n">
+        <v>10</v>
+      </c>
+      <c r="C451" t="inlineStr">
+        <is>
+          <t>ARFIN.NS</t>
+        </is>
+      </c>
+      <c r="D451" t="inlineStr">
+        <is>
+          <t>Arfin India Limited</t>
+        </is>
+      </c>
+      <c r="E451" t="n">
+        <v>88.69999694824219</v>
+      </c>
+      <c r="F451" t="n">
+        <v>97.44000244140625</v>
+      </c>
+      <c r="G451" t="n">
+        <v>87.72000122070312</v>
+      </c>
+      <c r="H451" t="n">
+        <v>97.33000183105469</v>
+      </c>
+      <c r="I451" t="n">
+        <v>87.23999786376953</v>
+      </c>
+      <c r="J451" t="n">
+        <v>97.33000183105469</v>
+      </c>
+      <c r="K451" t="n">
+        <v>2916534</v>
+      </c>
+      <c r="L451" t="n">
+        <v>11.57</v>
+      </c>
+      <c r="M451" t="inlineStr">
+        <is>
+          <t>Arfin India sets September 19 date for 34th AGM and e-voting - scanx.trade</t>
+        </is>
+      </c>
+      <c r="N451" t="inlineStr">
+        <is>
+          <t>Mufin Green Finance: செப்டம்பர் 28-ல் முக்கிய பொதுக்குழு கூட்டம்! லாபம் **39%** உயர்வு - whalesbook.com</t>
+        </is>
+      </c>
+      <c r="O451" t="inlineStr">
+        <is>
+          <t>Arfin (ARFIN.NS) Q2 2026 Earnings: The Company Releases Its Current Earnings Data under the Current Snapshot; Trading Move: Shares Move 0.68% Up for the Current Session - Revenue Recognition Risk - siam.in</t>
+        </is>
+      </c>
+      <c r="P451" t="inlineStr">
+        <is>
+          <t>Arfin India Consolidated June 2026 Net Sales at Rs 212.77 crore, up 95.46% Y-o-Y - Moneycontrol.com</t>
+        </is>
+      </c>
+      <c r="Q451" t="inlineStr">
+        <is>
+          <t>Arfin India consolidated net profit rises 276.85% in the June 2026 quarter - Business Standard</t>
+        </is>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" t="inlineStr">
+        <is>
+          <t>2026-09-07 12:56:35 IST</t>
+        </is>
+      </c>
+      <c r="B452" t="n">
+        <v>11</v>
+      </c>
+      <c r="C452" t="inlineStr">
+        <is>
+          <t>UDAYJEW.NS</t>
+        </is>
+      </c>
+      <c r="D452" t="inlineStr">
+        <is>
+          <t>Uday Jewellery Industries Limited</t>
+        </is>
+      </c>
+      <c r="E452" t="n">
+        <v>168.3999938964844</v>
+      </c>
+      <c r="F452" t="n">
+        <v>168.3999938964844</v>
+      </c>
+      <c r="G452" t="n">
+        <v>148</v>
+      </c>
+      <c r="H452" t="n">
+        <v>158</v>
+      </c>
+      <c r="I452" t="n">
+        <v>143</v>
+      </c>
+      <c r="J452" t="n">
+        <v>158</v>
+      </c>
+      <c r="K452" t="n">
+        <v>170308</v>
+      </c>
+      <c r="L452" t="n">
+        <v>10.49</v>
+      </c>
+      <c r="M452" t="inlineStr">
+        <is>
+          <t>Technical Analysis of Uday Jewellery Industries Ltd. (NSE:UDAYJEW) - TradingView</t>
+        </is>
+      </c>
+      <c r="N452" t="inlineStr">
+        <is>
+          <t>Uday Jewellery Industries Share Price Rises 8.82% Today - Univest</t>
+        </is>
+      </c>
+      <c r="O452" t="inlineStr">
+        <is>
+          <t>Uday Jewellery Industries Share Price Rises 8.82% Today - Univest</t>
+        </is>
+      </c>
+      <c r="P452" t="inlineStr">
+        <is>
+          <t>Uday Jewellery Industries Ltd. (UDAYJEW) sentiment score, message volume, participation score and buzz level - Stocktwits</t>
+        </is>
+      </c>
+      <c r="Q452" t="inlineStr">
+        <is>
+          <t>Uday Jewellery Promoters Acquire 73.34 Lakh Shares Through Merger Scheme - scanx.trade</t>
+        </is>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" t="inlineStr">
+        <is>
+          <t>2026-09-07 12:56:35 IST</t>
+        </is>
+      </c>
+      <c r="B453" t="n">
+        <v>12</v>
+      </c>
+      <c r="C453" t="inlineStr">
+        <is>
+          <t>CURAA.NS</t>
+        </is>
+      </c>
+      <c r="D453" t="inlineStr">
+        <is>
+          <t>Cura Technologies Limited</t>
+        </is>
+      </c>
+      <c r="E453" t="n">
+        <v>76</v>
+      </c>
+      <c r="F453" t="n">
+        <v>80</v>
+      </c>
+      <c r="G453" t="n">
+        <v>76</v>
+      </c>
+      <c r="H453" t="n">
+        <v>80</v>
+      </c>
+      <c r="I453" t="n">
+        <v>72.45999908447266</v>
+      </c>
+      <c r="J453" t="n">
+        <v>80</v>
+      </c>
+      <c r="K453" t="n">
+        <v>1681</v>
+      </c>
+      <c r="L453" t="n">
+        <v>10.41</v>
+      </c>
+      <c r="M453" t="inlineStr">
+        <is>
+          <t>D2C kitchenware startup Curaa raises Rs 40 crore led by 3one4 Capital - The Economic Times</t>
+        </is>
+      </c>
+      <c r="N453" t="inlineStr">
+        <is>
+          <t>D2C kitchenware startup Curaa raises Rs 40 crore led by 3one4 Capital - The Economic Times</t>
+        </is>
+      </c>
+      <c r="O453" t="inlineStr"/>
+      <c r="P453" t="inlineStr"/>
+      <c r="Q453" t="inlineStr"/>
+    </row>
+    <row r="454">
+      <c r="A454" t="inlineStr">
+        <is>
+          <t>2026-09-07 12:56:35 IST</t>
+        </is>
+      </c>
+      <c r="B454" t="n">
+        <v>13</v>
+      </c>
+      <c r="C454" t="inlineStr">
+        <is>
+          <t>STAR.NS</t>
+        </is>
+      </c>
+      <c r="D454" t="inlineStr">
+        <is>
+          <t>Strides Pharma Science Limited</t>
+        </is>
+      </c>
+      <c r="E454" t="n">
+        <v>1058.699951171875</v>
+      </c>
+      <c r="F454" t="n">
+        <v>1171.300048828125</v>
+      </c>
+      <c r="G454" t="n">
+        <v>1045</v>
+      </c>
+      <c r="H454" t="n">
+        <v>1168.199951171875</v>
+      </c>
+      <c r="I454" t="n">
+        <v>1059.599975585938</v>
+      </c>
+      <c r="J454" t="n">
+        <v>1168.199951171875</v>
+      </c>
+      <c r="K454" t="n">
+        <v>1010895</v>
+      </c>
+      <c r="L454" t="n">
+        <v>10.25</v>
+      </c>
+      <c r="M454" t="inlineStr">
+        <is>
+          <t>Asia tech shares rally, others hesitant as oil rises - The Star</t>
+        </is>
+      </c>
+      <c r="N454" t="inlineStr">
+        <is>
+          <t>Asia tech shares rally, others hesitant as oil rises - The Star</t>
+        </is>
+      </c>
+      <c r="O454" t="inlineStr">
+        <is>
+          <t>Evan, formerly ENHYPEN’s Heeseung, reveals his cancer battle for the first time - t2ONLINE</t>
+        </is>
+      </c>
+      <c r="P454" t="inlineStr">
+        <is>
+          <t>5-Star Analyst Resets Intel Stock Price Target on Weaker PC Demand - TradingView</t>
+        </is>
+      </c>
+      <c r="Q454" t="inlineStr">
+        <is>
+          <t>Forget Rolls-Royce shares: OXB is a rising FTSE 250 star tipped to gain 68% in the coming year! - The Twelfth Magpie</t>
+        </is>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" t="inlineStr">
+        <is>
+          <t>2026-09-07 12:56:35 IST</t>
+        </is>
+      </c>
+      <c r="B455" t="n">
+        <v>14</v>
+      </c>
+      <c r="C455" t="inlineStr">
+        <is>
+          <t>RADHIKAJWE.NS</t>
+        </is>
+      </c>
+      <c r="D455" t="inlineStr">
+        <is>
+          <t>Radhika Jeweltech Limited</t>
+        </is>
+      </c>
+      <c r="E455" t="n">
+        <v>84.62000274658203</v>
+      </c>
+      <c r="F455" t="n">
+        <v>93.76000213623047</v>
+      </c>
+      <c r="G455" t="n">
+        <v>84.61000061035156</v>
+      </c>
+      <c r="H455" t="n">
+        <v>91.65000152587891</v>
+      </c>
+      <c r="I455" t="n">
+        <v>83.16000366210938</v>
+      </c>
+      <c r="J455" t="n">
+        <v>91.65000152587891</v>
+      </c>
+      <c r="K455" t="n">
+        <v>16755953</v>
+      </c>
+      <c r="L455" t="n">
+        <v>10.21</v>
+      </c>
+      <c r="M455" t="inlineStr">
+        <is>
+          <t>Here's Why Radhika Jeweltech (NSE:RADHIKAJWE) Has Caught The Eye Of Investors - simplywall.st</t>
+        </is>
+      </c>
+      <c r="N455" t="inlineStr">
+        <is>
+          <t>Radhika Jeweltech (RADHIKAJWE.NS) Gains 5.15% as Bullish Momentum Builds - Virgin POC - siam.in</t>
+        </is>
+      </c>
+      <c r="O455" t="inlineStr">
+        <is>
+          <t>Radhika Jeweltech (RADHIKAJWE.NS) Gains 5.15% as Bullish Momentum Builds - Virgin POC - siam.in</t>
+        </is>
+      </c>
+      <c r="P455" t="inlineStr">
+        <is>
+          <t>Radhika Jeweltech Holds Steady Near Support; Resistance at ₹58.24 in Focus - Stock Analysis - vinanet.vn</t>
+        </is>
+      </c>
+      <c r="Q455" t="inlineStr">
+        <is>
+          <t>RADHIKAJWE Stock Price and Chart — NSE:RADHIKAJWE - TradingView</t>
+        </is>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" t="inlineStr">
+        <is>
+          <t>2026-09-07 12:56:35 IST</t>
+        </is>
+      </c>
+      <c r="B456" t="n">
+        <v>15</v>
+      </c>
+      <c r="C456" t="inlineStr">
+        <is>
+          <t>HIKAL.NS</t>
+        </is>
+      </c>
+      <c r="D456" t="inlineStr">
+        <is>
+          <t>Hikal Limited</t>
+        </is>
+      </c>
+      <c r="E456" t="n">
+        <v>222.0099945068359</v>
+      </c>
+      <c r="F456" t="n">
+        <v>257</v>
+      </c>
+      <c r="G456" t="n">
+        <v>218.8200073242188</v>
+      </c>
+      <c r="H456" t="n">
+        <v>244.6799926757812</v>
+      </c>
+      <c r="I456" t="n">
+        <v>222.3000030517578</v>
+      </c>
+      <c r="J456" t="n">
+        <v>244.6799926757812</v>
+      </c>
+      <c r="K456" t="n">
+        <v>14712371</v>
+      </c>
+      <c r="L456" t="n">
+        <v>10.07</v>
+      </c>
+      <c r="M456" t="inlineStr">
+        <is>
+          <t>Hikal FY26 net loss of ₹49 crore on exceptional items - scanx.trade</t>
+        </is>
+      </c>
+      <c r="N456" t="inlineStr">
+        <is>
+          <t>Hikal FY26 net loss of ₹49 crore on exceptional items - scanx.trade</t>
+        </is>
+      </c>
+      <c r="O456" t="inlineStr">
+        <is>
+          <t>Hikal Ltd. Share Price Rise: Price Action and Fundamentals - Univest</t>
+        </is>
+      </c>
+      <c r="P456" t="inlineStr">
+        <is>
+          <t>Don't Race Out To Buy Hikal Limited (NSE:HIKAL) Just Because It's Going Ex-Dividend - simplywall.st</t>
+        </is>
+      </c>
+      <c r="Q456" t="inlineStr">
+        <is>
+          <t>Hikal Ltd Shares Hit Intraday Low Amid Price Pressure on 4 Sep 2026 - MarketsMojo</t>
+        </is>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" t="inlineStr">
+        <is>
+          <t>2026-09-07 12:56:35 IST</t>
+        </is>
+      </c>
+      <c r="B457" t="n">
+        <v>16</v>
+      </c>
+      <c r="C457" t="inlineStr">
+        <is>
+          <t>FCL.NS</t>
+        </is>
+      </c>
+      <c r="D457" t="inlineStr">
+        <is>
+          <t>Fineotex Chemical Limited</t>
+        </is>
+      </c>
+      <c r="E457" t="n">
+        <v>52.25</v>
+      </c>
+      <c r="F457" t="n">
+        <v>56.65999984741211</v>
+      </c>
+      <c r="G457" t="n">
+        <v>52.18999862670898</v>
+      </c>
+      <c r="H457" t="n">
+        <v>56.65999984741211</v>
+      </c>
+      <c r="I457" t="n">
+        <v>51.5099983215332</v>
+      </c>
+      <c r="J457" t="n">
+        <v>56.65999984741211</v>
+      </c>
+      <c r="K457" t="n">
+        <v>36901422</v>
+      </c>
+      <c r="L457" t="n">
+        <v>10</v>
+      </c>
+      <c r="M457" t="inlineStr">
+        <is>
+          <t>Why FINEOS Corporation (ASX: FCL) Could Be a Stock to Watch Into the Final Months of 2026 - Kalkine</t>
+        </is>
+      </c>
+      <c r="N457" t="inlineStr">
+        <is>
+          <t>Why FINEOS Corporation (ASX: FCL) Could Be a Stock to Watch Into the Final Months of 2026 - Kalkine</t>
+        </is>
+      </c>
+      <c r="O457" t="inlineStr">
+        <is>
+          <t>Average basic shares outstanding of FCL-X FIRE SAFETY INC – TSXV:FCLX - TradingView</t>
+        </is>
+      </c>
+      <c r="P457" t="inlineStr">
+        <is>
+          <t>Full Circle Lithium Rebrands as FCL-X Fire &amp; Safety Inc. and Provides Corporate Update - Stock Titan</t>
+        </is>
+      </c>
+      <c r="Q457" t="inlineStr">
+        <is>
+          <t>Fineos (ASX:FCL) Shares Edge Lower Amid Weaker Technology Sector Sentiment - Kalkine</t>
+        </is>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" t="inlineStr">
+        <is>
+          <t>2026-09-07 12:56:35 IST</t>
+        </is>
+      </c>
+      <c r="B458" t="n">
+        <v>17</v>
+      </c>
+      <c r="C458" t="inlineStr">
+        <is>
+          <t>BODALCHEM.NS</t>
+        </is>
+      </c>
+      <c r="D458" t="inlineStr">
+        <is>
+          <t>Bodal Chemicals Limited</t>
+        </is>
+      </c>
+      <c r="E458" t="n">
+        <v>168</v>
+      </c>
+      <c r="F458" t="n">
+        <v>171.1799926757812</v>
+      </c>
+      <c r="G458" t="n">
+        <v>162.8000030517578</v>
+      </c>
+      <c r="H458" t="n">
+        <v>171.1799926757812</v>
+      </c>
+      <c r="I458" t="n">
+        <v>155.6199951171875</v>
+      </c>
+      <c r="J458" t="n">
+        <v>171.1799926757812</v>
+      </c>
+      <c r="K458" t="n">
+        <v>4822306</v>
+      </c>
+      <c r="L458" t="n">
+        <v>10</v>
+      </c>
+      <c r="M458" t="inlineStr">
+        <is>
+          <t>With EPS Growth And More, Bodal Chemicals (NSE:BODALCHEM) Makes An Interesting Case - simplywall.st</t>
+        </is>
+      </c>
+      <c r="N458" t="inlineStr">
+        <is>
+          <t>Bodal Chemicals Sets Virtual AGM to Approve FY26 Accounts and Board Changes - TipRanks</t>
+        </is>
+      </c>
+      <c r="O458" t="inlineStr">
+        <is>
+          <t>Bodal Chemicals Share Price news with valuation context - Univest</t>
+        </is>
+      </c>
+      <c r="P458" t="inlineStr">
+        <is>
+          <t>Bodal Chemicals Ltd. (BODALCHEM) Share Price Rises 9.21% Today; Key Levels, Valuation and Peer View - Univest</t>
+        </is>
+      </c>
+      <c r="Q458" t="inlineStr">
+        <is>
+          <t>Bodal Chemicals Sets Virtual AGM to Approve FY26 Accounts and Board Changes - TipRanks</t>
+        </is>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" t="inlineStr">
+        <is>
+          <t>2026-09-07 12:56:35 IST</t>
+        </is>
+      </c>
+      <c r="B459" t="n">
+        <v>18</v>
+      </c>
+      <c r="C459" t="inlineStr">
+        <is>
+          <t>TBZ.NS</t>
+        </is>
+      </c>
+      <c r="D459" t="inlineStr">
+        <is>
+          <t>Tribhovandas Bhimji Zaveri Limited</t>
+        </is>
+      </c>
+      <c r="E459" t="n">
+        <v>528.9000244140625</v>
+      </c>
+      <c r="F459" t="n">
+        <v>528.9000244140625</v>
+      </c>
+      <c r="G459" t="n">
+        <v>528.9000244140625</v>
+      </c>
+      <c r="H459" t="n">
+        <v>528.9000244140625</v>
+      </c>
+      <c r="I459" t="n">
+        <v>480.8500061035156</v>
+      </c>
+      <c r="J459" t="n">
+        <v>528.9000244140625</v>
+      </c>
+      <c r="K459" t="n">
+        <v>281857</v>
+      </c>
+      <c r="L459" t="n">
+        <v>9.99</v>
+      </c>
+      <c r="M459" t="inlineStr">
+        <is>
+          <t>Jewellery Stocks In Focus: PC Jeweller Surges 15%, TBZ Hits 10% Upper Circuit; Shankesh Gains 8% — Know Why - NDTV Profit</t>
+        </is>
+      </c>
+      <c r="N459" t="inlineStr">
+        <is>
+          <t>Jewellery Stocks In Focus: PC Jeweller Surges 15%, TBZ Hits 10% Upper Circuit; Shankesh Gains 8% — Know Why - NDTV Profit</t>
+        </is>
+      </c>
+      <c r="O459" t="inlineStr">
+        <is>
+          <t>Multibagger stock: Why TBZ shares are locked at 20% upper circuit - Business Standard</t>
+        </is>
+      </c>
+      <c r="P459" t="inlineStr">
+        <is>
+          <t>Tribhovandas Bhimji Zaveri is now GRT's jewel - Finshots</t>
+        </is>
+      </c>
+      <c r="Q459" t="inlineStr">
+        <is>
+          <t>TBZ shares zoom 20%, hit upper circuit after GRT Jewellers open offer - The Economic Times</t>
+        </is>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" t="inlineStr">
+        <is>
+          <t>2026-09-07 12:56:35 IST</t>
+        </is>
+      </c>
+      <c r="B460" t="n">
+        <v>19</v>
+      </c>
+      <c r="C460" t="inlineStr">
+        <is>
+          <t>DHATRE.NS</t>
+        </is>
+      </c>
+      <c r="D460" t="inlineStr">
+        <is>
+          <t>Dhatre Udyog Limited</t>
+        </is>
+      </c>
+      <c r="E460" t="n">
+        <v>4.349999904632568</v>
+      </c>
+      <c r="F460" t="n">
+        <v>5.170000076293945</v>
+      </c>
+      <c r="G460" t="n">
+        <v>4.210000038146973</v>
+      </c>
+      <c r="H460" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="I460" t="n">
+        <v>4.329999923706055</v>
+      </c>
+      <c r="J460" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="K460" t="n">
+        <v>105820</v>
+      </c>
+      <c r="L460" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="M460" t="inlineStr">
+        <is>
+          <t>DHATRE Stock Price and Chart — NSE:DHATRE - TradingView</t>
+        </is>
+      </c>
+      <c r="N460" t="inlineStr">
+        <is>
+          <t>Dhatre Udyog corrects 31st AGM time to 11 am on Sept 26 - scanx.trade</t>
+        </is>
+      </c>
+      <c r="O460" t="inlineStr">
+        <is>
+          <t>Dhatre Udyog Q1FY26 net profit hits ₹573 lakh on OCI surge - scanx.trade</t>
+        </is>
+      </c>
+      <c r="P460" t="inlineStr">
+        <is>
+          <t>Dhatre Udyog Ltd. (DHATRE) Profile, Company FAQs &amp; Facts, Industry, Sector, Employee Strength - Stocktwits</t>
+        </is>
+      </c>
+      <c r="Q460" t="inlineStr">
+        <is>
+          <t>Dhatre Udyog Q1 FY27 Results: Revenue and PAT Highlights - Univest</t>
+        </is>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" t="inlineStr">
+        <is>
+          <t>2026-09-07 12:56:35 IST</t>
+        </is>
+      </c>
+      <c r="B461" t="n">
+        <v>20</v>
+      </c>
+      <c r="C461" t="inlineStr">
+        <is>
+          <t>MMP.NS</t>
+        </is>
+      </c>
+      <c r="D461" t="inlineStr">
+        <is>
+          <t>MMP Industries Limited</t>
+        </is>
+      </c>
+      <c r="E461" t="n">
+        <v>405.8999938964844</v>
+      </c>
+      <c r="F461" t="n">
+        <v>455.6000061035156</v>
+      </c>
+      <c r="G461" t="n">
+        <v>404.5</v>
+      </c>
+      <c r="H461" t="n">
+        <v>443.1499938964844</v>
+      </c>
+      <c r="I461" t="n">
+        <v>404.1499938964844</v>
+      </c>
+      <c r="J461" t="n">
+        <v>443.1499938964844</v>
+      </c>
+      <c r="K461" t="n">
+        <v>301815</v>
+      </c>
+      <c r="L461" t="n">
+        <v>9.65</v>
+      </c>
+      <c r="M461" t="inlineStr">
+        <is>
+          <t>MMP Industries confirms no encumbrance on promoter shares in FY26 - scanx.trade</t>
+        </is>
+      </c>
+      <c r="N461" t="inlineStr">
+        <is>
+          <t>MMP Industries confirms no encumbrance on promoter shares in FY26 - scanx.trade</t>
+        </is>
+      </c>
+      <c r="O461" t="inlineStr">
+        <is>
+          <t>MMP Industries Drops 2.6% to ₹383.25; Support at ₹364.09 Holds Key - Option Strike Build - siam.in</t>
+        </is>
+      </c>
+      <c r="P461" t="inlineStr">
+        <is>
+          <t>MMP Industries Share Price Rises 8.51%: Price, Valuation - Univest</t>
+        </is>
+      </c>
+      <c r="Q461" t="inlineStr">
+        <is>
+          <t>MMP Industries Consolidated June 2026 Net Sales at Rs 232.60 crore, up 26.9% Y-o-Y - Moneycontrol.com</t>
         </is>
       </c>
     </row>
@@ -29346,7 +30679,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q741"/>
+  <dimension ref="A1:Q761"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -74679,9 +76012,6 @@
           <t>Dynamic Cables (NSE: DYCL) Stock Analysis - Kalkine India</t>
         </is>
       </c>
-      <c r="O722" t="inlineStr"/>
-      <c r="P722" t="inlineStr"/>
-      <c r="Q722" t="inlineStr"/>
     </row>
     <row r="723">
       <c r="A723" t="inlineStr">
@@ -74736,9 +76066,6 @@
           <t>With EPS Growth And More, Jayaswal Neco Industries (NSE:JAYNECOIND) Makes An Interesting Case - simplywall.st</t>
         </is>
       </c>
-      <c r="O723" t="inlineStr"/>
-      <c r="P723" t="inlineStr"/>
-      <c r="Q723" t="inlineStr"/>
     </row>
     <row r="724">
       <c r="A724" t="inlineStr">
@@ -74803,7 +76130,6 @@
           <t>Ugar Sugar Works director Hari Athawale retires, Prafulla Shirgaokar resigns from board - ChiniMandi</t>
         </is>
       </c>
-      <c r="Q724" t="inlineStr"/>
     </row>
     <row r="725">
       <c r="A725" t="inlineStr">
@@ -75144,7 +76470,6 @@
           <t>Landsmill Green board to delete FMCG object, close subsidiary on Sep 4 - scanx.trade</t>
         </is>
       </c>
-      <c r="Q729" t="inlineStr"/>
     </row>
     <row r="730">
       <c r="A730" t="inlineStr">
@@ -75485,7 +76810,6 @@
           <t>Makers Laboratories Q1 Results: Consolidated Net Profit Surges 244% YoY to ₹150.43 lacs - scanx.trade</t>
         </is>
       </c>
-      <c r="Q734" t="inlineStr"/>
     </row>
     <row r="735">
       <c r="A735" t="inlineStr">
@@ -75545,8 +76869,6 @@
           <t>Dhampur Sugar Mills net profit rises 569% to ₹6.09 crore in Q1FY27 - scanx.trade</t>
         </is>
       </c>
-      <c r="P735" t="inlineStr"/>
-      <c r="Q735" t="inlineStr"/>
     </row>
     <row r="736">
       <c r="A736" t="inlineStr">
@@ -75611,7 +76933,6 @@
           <t>Annapurna Studios expands distribution slate with Dulquer Salmaan’s I’m Game, Karthi’s Sardar 2 and... - Moneycontrol.com</t>
         </is>
       </c>
-      <c r="Q736" t="inlineStr"/>
     </row>
     <row r="737">
       <c r="A737" t="inlineStr">
@@ -75740,8 +77061,6 @@
           <t>Precision Wires and 11 Other Stocks That Hit the 20% Upper Circuit Today; Are You Holding Any? - tradebrains.in</t>
         </is>
       </c>
-      <c r="P738" t="inlineStr"/>
-      <c r="Q738" t="inlineStr"/>
     </row>
     <row r="739">
       <c r="A739" t="inlineStr">
@@ -75806,7 +77125,6 @@
           <t>KJMC Financial Services Ltd. (KJMCFIN) sentiment score, message volume, participation score and buzz level - Stocktwits</t>
         </is>
       </c>
-      <c r="Q739" t="inlineStr"/>
     </row>
     <row r="740">
       <c r="A740" t="inlineStr">
@@ -75943,6 +77261,1354 @@
       <c r="Q741" t="inlineStr">
         <is>
           <t>R&amp;B Denims Limited (RNBDENIMS.NS) Faces Selling Pressure, Holds Above Key Support - Institutional Sentiment - vinanet.vn</t>
+        </is>
+      </c>
+    </row>
+    <row r="742">
+      <c r="A742" t="inlineStr">
+        <is>
+          <t>2026-09-07 12:56:35 IST</t>
+        </is>
+      </c>
+      <c r="B742" t="n">
+        <v>1</v>
+      </c>
+      <c r="C742" t="inlineStr">
+        <is>
+          <t>HEG.NS</t>
+        </is>
+      </c>
+      <c r="D742" t="inlineStr">
+        <is>
+          <t>HEG Limited</t>
+        </is>
+      </c>
+      <c r="E742" t="n">
+        <v>260</v>
+      </c>
+      <c r="F742" t="n">
+        <v>273</v>
+      </c>
+      <c r="G742" t="n">
+        <v>250</v>
+      </c>
+      <c r="H742" t="n">
+        <v>265.5499877929688</v>
+      </c>
+      <c r="I742" t="n">
+        <v>728.25</v>
+      </c>
+      <c r="J742" t="n">
+        <v>265.5499877929688</v>
+      </c>
+      <c r="K742" t="n">
+        <v>2092808</v>
+      </c>
+      <c r="L742" t="n">
+        <v>-63.54</v>
+      </c>
+      <c r="M742" t="inlineStr">
+        <is>
+          <t>HEG Demerger Record Date Today. What It Means For Shareholders? All You Need To Know - NDTV Profit</t>
+        </is>
+      </c>
+      <c r="N742" t="inlineStr">
+        <is>
+          <t>Did HEG shares really crash 64% in one day? Here’s how the demerger math works - The Economic Times</t>
+        </is>
+      </c>
+      <c r="O742" t="inlineStr">
+        <is>
+          <t>Did HEG shares really crash 64% in one day? Here’s how the demerger math works - The Economic Times</t>
+        </is>
+      </c>
+      <c r="P742" t="inlineStr">
+        <is>
+          <t>HEG demerger news: Record date today | Ratio, latest updates, other details in 5 points - Livemint</t>
+        </is>
+      </c>
+      <c r="Q742" t="inlineStr">
+        <is>
+          <t>HEG Advanced Material shares see discovered price of ₹260 on the bourses; Here's what you need to know - CNBC TV18</t>
+        </is>
+      </c>
+    </row>
+    <row r="743">
+      <c r="A743" t="inlineStr">
+        <is>
+          <t>2026-09-07 12:56:35 IST</t>
+        </is>
+      </c>
+      <c r="B743" t="n">
+        <v>2</v>
+      </c>
+      <c r="C743" t="inlineStr">
+        <is>
+          <t>ICDSLTD.NS</t>
+        </is>
+      </c>
+      <c r="D743" t="inlineStr">
+        <is>
+          <t>ICDS Limited</t>
+        </is>
+      </c>
+      <c r="E743" t="n">
+        <v>71.55999755859375</v>
+      </c>
+      <c r="F743" t="n">
+        <v>77.69000244140625</v>
+      </c>
+      <c r="G743" t="n">
+        <v>64.30999755859375</v>
+      </c>
+      <c r="H743" t="n">
+        <v>65.18000030517578</v>
+      </c>
+      <c r="I743" t="n">
+        <v>71.44999694824219</v>
+      </c>
+      <c r="J743" t="n">
+        <v>65.18000030517578</v>
+      </c>
+      <c r="K743" t="n">
+        <v>94965</v>
+      </c>
+      <c r="L743" t="n">
+        <v>-8.779999999999999</v>
+      </c>
+      <c r="M743" t="inlineStr">
+        <is>
+          <t>ICDS Limited (ICDSLTD.NS) Surges Over 7.8%: Strong Momentum or Resistance Ahead? - Bear Pennant - vinanet.vn</t>
+        </is>
+      </c>
+      <c r="N743" t="inlineStr">
+        <is>
+          <t>ICDS Limited (ICDSLTD.NS): Mild Decline Amid Consolidation, Key Levels Hold - Value ETF - vinanet.vn</t>
+        </is>
+      </c>
+      <c r="O743" t="inlineStr">
+        <is>
+          <t>ICDS Ltd Sees Decline: Stock Slips 3.85% Amidst Key Support Test - Day Trade Opportunities - vinanet.vn</t>
+        </is>
+      </c>
+      <c r="P743" t="inlineStr">
+        <is>
+          <t>ICDS Share Price - Live NSE: ICDSLTD Stock Price &amp; Chart - Upstox</t>
+        </is>
+      </c>
+      <c r="Q743" t="inlineStr">
+        <is>
+          <t>ICDSLTD Stock Price and Chart — NSE:ICDSLTD - TradingView</t>
+        </is>
+      </c>
+    </row>
+    <row r="744">
+      <c r="A744" t="inlineStr">
+        <is>
+          <t>2026-09-07 12:56:35 IST</t>
+        </is>
+      </c>
+      <c r="B744" t="n">
+        <v>3</v>
+      </c>
+      <c r="C744" t="inlineStr">
+        <is>
+          <t>SVGLOBAL.NS</t>
+        </is>
+      </c>
+      <c r="D744" t="inlineStr">
+        <is>
+          <t>S V Global Mill Limited</t>
+        </is>
+      </c>
+      <c r="E744" t="n">
+        <v>160</v>
+      </c>
+      <c r="F744" t="n">
+        <v>160</v>
+      </c>
+      <c r="G744" t="n">
+        <v>152</v>
+      </c>
+      <c r="H744" t="n">
+        <v>152</v>
+      </c>
+      <c r="I744" t="n">
+        <v>163.6199951171875</v>
+      </c>
+      <c r="J744" t="n">
+        <v>152</v>
+      </c>
+      <c r="K744" t="n">
+        <v>15396</v>
+      </c>
+      <c r="L744" t="n">
+        <v>-7.1</v>
+      </c>
+      <c r="M744" t="inlineStr">
+        <is>
+          <t>S V Global Mill Ltd (SVGLOBAL) Profile, Company FAQs &amp; Facts, Industry, Sector, Employee Strength - Stocktwits</t>
+        </is>
+      </c>
+      <c r="N744" t="inlineStr">
+        <is>
+          <t>SV Global Mill Ltd. Share Price Rise Streak: Price Action - Univest</t>
+        </is>
+      </c>
+      <c r="O744" t="inlineStr">
+        <is>
+          <t>SV Global Mill Share Price gains 19.99% amid market focus - Univest</t>
+        </is>
+      </c>
+      <c r="P744" t="inlineStr">
+        <is>
+          <t>SV Global Mill Share Price today: price rise and valuation - Univest</t>
+        </is>
+      </c>
+      <c r="Q744" t="inlineStr">
+        <is>
+          <t>SV Global Mill Ltd. Share Price Fall and Stock Analysis - Univest</t>
+        </is>
+      </c>
+    </row>
+    <row r="745">
+      <c r="A745" t="inlineStr">
+        <is>
+          <t>2026-09-07 12:56:35 IST</t>
+        </is>
+      </c>
+      <c r="B745" t="n">
+        <v>4</v>
+      </c>
+      <c r="C745" t="inlineStr">
+        <is>
+          <t>NAGREEKEXP.NS</t>
+        </is>
+      </c>
+      <c r="D745" t="inlineStr">
+        <is>
+          <t>Nagreeka Exports Limited</t>
+        </is>
+      </c>
+      <c r="E745" t="n">
+        <v>22.67000007629395</v>
+      </c>
+      <c r="F745" t="n">
+        <v>23.8700008392334</v>
+      </c>
+      <c r="G745" t="n">
+        <v>22.20000076293945</v>
+      </c>
+      <c r="H745" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="I745" t="n">
+        <v>24.10000038146973</v>
+      </c>
+      <c r="J745" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="K745" t="n">
+        <v>46834</v>
+      </c>
+      <c r="L745" t="n">
+        <v>-6.64</v>
+      </c>
+      <c r="M745" t="inlineStr">
+        <is>
+          <t>Nagreeka Exports Limited (NSE: NAGREEKEXP) Falls 5.23% as Stock Movement Draws Market Attention - Kalkine India</t>
+        </is>
+      </c>
+      <c r="N745" t="inlineStr">
+        <is>
+          <t>Nagreeka Exports Limited (NSE: NAGREEKEXP) Falls 5.23% as Stock Movement Draws Market Attention - Kalkine India</t>
+        </is>
+      </c>
+      <c r="O745" t="inlineStr">
+        <is>
+          <t>Nagreeka Exports Holds Near ₹21.3: Consolidation Persists for NAGREEKEXP on NSE - Rounding Top - siam.in</t>
+        </is>
+      </c>
+      <c r="P745" t="inlineStr">
+        <is>
+          <t>CFEL Stock Price and Chart — NSE:CFEL - TradingView</t>
+        </is>
+      </c>
+      <c r="Q745" t="inlineStr">
+        <is>
+          <t>Nagreeka Exports files revised FY26 annual report to fix clerical error - scanx.trade</t>
+        </is>
+      </c>
+    </row>
+    <row r="746">
+      <c r="A746" t="inlineStr">
+        <is>
+          <t>2026-09-07 12:56:35 IST</t>
+        </is>
+      </c>
+      <c r="B746" t="n">
+        <v>5</v>
+      </c>
+      <c r="C746" t="inlineStr">
+        <is>
+          <t>RPEL.NS</t>
+        </is>
+      </c>
+      <c r="D746" t="inlineStr">
+        <is>
+          <t>Raghav Productivity Enhancers Limited</t>
+        </is>
+      </c>
+      <c r="E746" t="n">
+        <v>1819.099975585938</v>
+      </c>
+      <c r="F746" t="n">
+        <v>1821.5</v>
+      </c>
+      <c r="G746" t="n">
+        <v>1635.599975585938</v>
+      </c>
+      <c r="H746" t="n">
+        <v>1687.199951171875</v>
+      </c>
+      <c r="I746" t="n">
+        <v>1807.199951171875</v>
+      </c>
+      <c r="J746" t="n">
+        <v>1687.199951171875</v>
+      </c>
+      <c r="K746" t="n">
+        <v>227646</v>
+      </c>
+      <c r="L746" t="n">
+        <v>-6.64</v>
+      </c>
+      <c r="M746" t="inlineStr">
+        <is>
+          <t>Raghav Productivity Enhancers Ltd. Share Price Near High - Univest</t>
+        </is>
+      </c>
+      <c r="N746" t="inlineStr">
+        <is>
+          <t>Raghav Productivity Enhancers Ltd. Share Price Near High - Univest</t>
+        </is>
+      </c>
+      <c r="O746" t="inlineStr"/>
+      <c r="P746" t="inlineStr"/>
+      <c r="Q746" t="inlineStr"/>
+    </row>
+    <row r="747">
+      <c r="A747" t="inlineStr">
+        <is>
+          <t>2026-09-07 12:56:35 IST</t>
+        </is>
+      </c>
+      <c r="B747" t="n">
+        <v>6</v>
+      </c>
+      <c r="C747" t="inlineStr">
+        <is>
+          <t>SAICAPI.NS</t>
+        </is>
+      </c>
+      <c r="D747" t="inlineStr">
+        <is>
+          <t>Sai Capital Limited</t>
+        </is>
+      </c>
+      <c r="E747" t="n">
+        <v>158.3399963378906</v>
+      </c>
+      <c r="F747" t="n">
+        <v>158.3399963378906</v>
+      </c>
+      <c r="G747" t="n">
+        <v>147.9299926757812</v>
+      </c>
+      <c r="H747" t="n">
+        <v>147.9299926757812</v>
+      </c>
+      <c r="I747" t="n">
+        <v>157.5599975585938</v>
+      </c>
+      <c r="J747" t="n">
+        <v>147.9299926757812</v>
+      </c>
+      <c r="K747" t="n">
+        <v>91</v>
+      </c>
+      <c r="L747" t="n">
+        <v>-6.11</v>
+      </c>
+      <c r="M747" t="inlineStr">
+        <is>
+          <t>SAICAPI Stock Price and Chart — NSE:SAICAPI - TradingView</t>
+        </is>
+      </c>
+      <c r="N747" t="inlineStr">
+        <is>
+          <t>SAICAPI Stock Price and Chart — NSE:SAICAPI - TradingView</t>
+        </is>
+      </c>
+      <c r="O747" t="inlineStr">
+        <is>
+          <t>Sai Capital Ltd. (SAICAPI) News, Articles, Events &amp; Latest Updates - Stocktwits</t>
+        </is>
+      </c>
+      <c r="P747" t="inlineStr">
+        <is>
+          <t>Sai Capital Q1 Results: Standalone and consolidated financials approved - scanx.trade</t>
+        </is>
+      </c>
+      <c r="Q747" t="inlineStr">
+        <is>
+          <t>Sai Capital Ltd. (SAICAPI) Share Price Today, Quote, Latest Discussions, Interactive Chart and News - Stocktwits</t>
+        </is>
+      </c>
+    </row>
+    <row r="748">
+      <c r="A748" t="inlineStr">
+        <is>
+          <t>2026-09-07 12:56:35 IST</t>
+        </is>
+      </c>
+      <c r="B748" t="n">
+        <v>7</v>
+      </c>
+      <c r="C748" t="inlineStr">
+        <is>
+          <t>TCC.NS</t>
+        </is>
+      </c>
+      <c r="D748" t="inlineStr">
+        <is>
+          <t>TCC Concept Limited</t>
+        </is>
+      </c>
+      <c r="E748" t="n">
+        <v>44</v>
+      </c>
+      <c r="F748" t="n">
+        <v>44.47000122070312</v>
+      </c>
+      <c r="G748" t="n">
+        <v>40.70999908447266</v>
+      </c>
+      <c r="H748" t="n">
+        <v>41.40999984741211</v>
+      </c>
+      <c r="I748" t="n">
+        <v>44.09999847412109</v>
+      </c>
+      <c r="J748" t="n">
+        <v>41.40999984741211</v>
+      </c>
+      <c r="K748" t="n">
+        <v>406600</v>
+      </c>
+      <c r="L748" t="n">
+        <v>-6.1</v>
+      </c>
+      <c r="M748" t="inlineStr">
+        <is>
+          <t>TCC CONCPAR: Shareholders Board Members Managers and Company Profile | INE887D01016 - marketscreener.com</t>
+        </is>
+      </c>
+      <c r="N748" t="inlineStr">
+        <is>
+          <t>TCC CONCPAR: Shareholders Board Members Managers and Company Profile | INE887D01016 - marketscreener.com</t>
+        </is>
+      </c>
+      <c r="O748" t="inlineStr">
+        <is>
+          <t>TCC Concept Stock Falls: Key Levels to Watch - Kalkine India</t>
+        </is>
+      </c>
+      <c r="P748" t="inlineStr">
+        <is>
+          <t>TCC CONCEPT Consolidated June 2026 Net Sales at Rs 128.28 crore, up 480.19% Y-o-Y - Moneycontrol.com</t>
+        </is>
+      </c>
+      <c r="Q748" t="inlineStr">
+        <is>
+          <t>TCC Concept fixes September 4 record date for 1:5 share split - scanx.trade</t>
+        </is>
+      </c>
+    </row>
+    <row r="749">
+      <c r="A749" t="inlineStr">
+        <is>
+          <t>2026-09-07 12:56:35 IST</t>
+        </is>
+      </c>
+      <c r="B749" t="n">
+        <v>8</v>
+      </c>
+      <c r="C749" t="inlineStr">
+        <is>
+          <t>PVRINOX.NS</t>
+        </is>
+      </c>
+      <c r="D749" t="inlineStr">
+        <is>
+          <t>PVR INOX Limited</t>
+        </is>
+      </c>
+      <c r="E749" t="n">
+        <v>1199.099975585938</v>
+      </c>
+      <c r="F749" t="n">
+        <v>1199.099975585938</v>
+      </c>
+      <c r="G749" t="n">
+        <v>1125.699951171875</v>
+      </c>
+      <c r="H749" t="n">
+        <v>1162.300048828125</v>
+      </c>
+      <c r="I749" t="n">
+        <v>1227.199951171875</v>
+      </c>
+      <c r="J749" t="n">
+        <v>1162.300048828125</v>
+      </c>
+      <c r="K749" t="n">
+        <v>2523836</v>
+      </c>
+      <c r="L749" t="n">
+        <v>-5.29</v>
+      </c>
+      <c r="M749" t="inlineStr">
+        <is>
+          <t>PVR INOX Limited (NSE: PVRINOX) Falls 6.79% as Stock Movement Draws Market Attention - Kalkine India</t>
+        </is>
+      </c>
+      <c r="N749" t="inlineStr">
+        <is>
+          <t>PVR INOX Limited (NSE: PVRINOX) Falls 6.79% as Stock Movement Draws Market Attention - Kalkine India</t>
+        </is>
+      </c>
+      <c r="O749" t="inlineStr">
+        <is>
+          <t>PVR Inox Share Price - Live NSE: PVRINOX Stock Price &amp; Chart - Upstox</t>
+        </is>
+      </c>
+      <c r="P749" t="inlineStr">
+        <is>
+          <t>PVRINOX Outlook for the Week - equitypandit.com</t>
+        </is>
+      </c>
+      <c r="Q749" t="inlineStr">
+        <is>
+          <t>PVR INOX Limited announces an Equity Buyback for 2,068,965 shares, representing 2.11% for INR 3,000 million. - marketscreener.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="750">
+      <c r="A750" t="inlineStr">
+        <is>
+          <t>2026-09-07 12:56:35 IST</t>
+        </is>
+      </c>
+      <c r="B750" t="n">
+        <v>9</v>
+      </c>
+      <c r="C750" t="inlineStr">
+        <is>
+          <t>ANNU.NS</t>
+        </is>
+      </c>
+      <c r="D750" t="inlineStr">
+        <is>
+          <t>Annu Projects Limited</t>
+        </is>
+      </c>
+      <c r="E750" t="n">
+        <v>64.81999969482422</v>
+      </c>
+      <c r="F750" t="n">
+        <v>64.81999969482422</v>
+      </c>
+      <c r="G750" t="n">
+        <v>64.81999969482422</v>
+      </c>
+      <c r="H750" t="n">
+        <v>64.81999969482422</v>
+      </c>
+      <c r="I750" t="n">
+        <v>68.23000335693359</v>
+      </c>
+      <c r="J750" t="n">
+        <v>64.81999969482422</v>
+      </c>
+      <c r="K750" t="n">
+        <v>102987</v>
+      </c>
+      <c r="L750" t="n">
+        <v>-5</v>
+      </c>
+      <c r="M750" t="inlineStr">
+        <is>
+          <t>Weak market debut: Annu Projects shares list at over 27% discount to its IPO price - Moneycontrol.com</t>
+        </is>
+      </c>
+      <c r="N750" t="inlineStr">
+        <is>
+          <t>Annu Projects Ltd. Share Price Today - Annu Projects Ltd. Stock Price Live NSE/BSE - CNBC TV18</t>
+        </is>
+      </c>
+      <c r="O750" t="inlineStr">
+        <is>
+          <t>Annu Projects Shares List at 27% Discount on NSE - Groww</t>
+        </is>
+      </c>
+      <c r="P750" t="inlineStr">
+        <is>
+          <t>Total common shares outstanding of Annu Projects Limited – NSE:ANNU - TradingView</t>
+        </is>
+      </c>
+      <c r="Q750" t="inlineStr">
+        <is>
+          <t>Annu Projects Ltd. Share Price Today - Annu Projects Ltd. Stock Price Live NSE/BSE - CNBC TV18</t>
+        </is>
+      </c>
+    </row>
+    <row r="751">
+      <c r="A751" t="inlineStr">
+        <is>
+          <t>2026-09-07 12:56:35 IST</t>
+        </is>
+      </c>
+      <c r="B751" t="n">
+        <v>10</v>
+      </c>
+      <c r="C751" t="inlineStr">
+        <is>
+          <t>NIRAJISPAT.NS</t>
+        </is>
+      </c>
+      <c r="D751" t="inlineStr">
+        <is>
+          <t>Niraj Ispat Industries Limited</t>
+        </is>
+      </c>
+      <c r="E751" t="n">
+        <v>368.4500122070312</v>
+      </c>
+      <c r="F751" t="n">
+        <v>368.4500122070312</v>
+      </c>
+      <c r="G751" t="n">
+        <v>368.4500122070312</v>
+      </c>
+      <c r="H751" t="n">
+        <v>368.4500122070312</v>
+      </c>
+      <c r="I751" t="n">
+        <v>387.7999877929688</v>
+      </c>
+      <c r="J751" t="n">
+        <v>368.4500122070312</v>
+      </c>
+      <c r="K751" t="n">
+        <v>70</v>
+      </c>
+      <c r="L751" t="n">
+        <v>-4.99</v>
+      </c>
+      <c r="M751" t="inlineStr">
+        <is>
+          <t>Niraj (NIRAJISPAT.NS) Price Update: Ends Down by 3.00% at ₹205.65 for the Current Session - siam.in</t>
+        </is>
+      </c>
+      <c r="N751" t="inlineStr">
+        <is>
+          <t>Precision Wires and 11 Other Stocks That Hit the 20% Upper Circuit Today; Are You Holding Any? - Trade Brains</t>
+        </is>
+      </c>
+      <c r="O751" t="inlineStr">
+        <is>
+          <t>Niraj (NIRAJISPAT.NS) Session: Finishes Nearly Flat at ₹216.00; Levels: the ₹205.20 to ₹226.80 Range Remains in Focus in the Available Record - PSAR Stop - siam.in</t>
+        </is>
+      </c>
+      <c r="P751" t="inlineStr">
+        <is>
+          <t>Precision Wires and 11 Other Stocks That Hit the 20% Upper Circuit Today; Are You Holding Any? - Trade Brains</t>
+        </is>
+      </c>
+      <c r="Q751" t="inlineStr"/>
+    </row>
+    <row r="752">
+      <c r="A752" t="inlineStr">
+        <is>
+          <t>2026-09-07 12:56:35 IST</t>
+        </is>
+      </c>
+      <c r="B752" t="n">
+        <v>11</v>
+      </c>
+      <c r="C752" t="inlineStr">
+        <is>
+          <t>BIRLACABLE.NS</t>
+        </is>
+      </c>
+      <c r="D752" t="inlineStr">
+        <is>
+          <t>Birla Cable Limited</t>
+        </is>
+      </c>
+      <c r="E752" t="n">
+        <v>395</v>
+      </c>
+      <c r="F752" t="n">
+        <v>395</v>
+      </c>
+      <c r="G752" t="n">
+        <v>357.75</v>
+      </c>
+      <c r="H752" t="n">
+        <v>357.75</v>
+      </c>
+      <c r="I752" t="n">
+        <v>376.5499877929688</v>
+      </c>
+      <c r="J752" t="n">
+        <v>357.75</v>
+      </c>
+      <c r="K752" t="n">
+        <v>763650</v>
+      </c>
+      <c r="L752" t="n">
+        <v>-4.99</v>
+      </c>
+      <c r="M752" t="inlineStr">
+        <is>
+          <t>Birla Cable Limited Files Quarterly Compliance Certificate for Q4 FY26 Under SEBI Regulations - scanx.trade</t>
+        </is>
+      </c>
+      <c r="N752" t="inlineStr">
+        <is>
+          <t>Birla Cable Limited Files Quarterly Compliance Certificate for Q4 FY26 Under SEBI Regulations - scanx.trade</t>
+        </is>
+      </c>
+      <c r="O752" t="inlineStr"/>
+      <c r="P752" t="inlineStr"/>
+      <c r="Q752" t="inlineStr"/>
+    </row>
+    <row r="753">
+      <c r="A753" t="inlineStr">
+        <is>
+          <t>2026-09-07 12:56:35 IST</t>
+        </is>
+      </c>
+      <c r="B753" t="n">
+        <v>12</v>
+      </c>
+      <c r="C753" t="inlineStr">
+        <is>
+          <t>CALSOFT.NS</t>
+        </is>
+      </c>
+      <c r="D753" t="inlineStr">
+        <is>
+          <t>California Software Company Limited</t>
+        </is>
+      </c>
+      <c r="E753" t="n">
+        <v>38.93999862670898</v>
+      </c>
+      <c r="F753" t="n">
+        <v>38.93999862670898</v>
+      </c>
+      <c r="G753" t="n">
+        <v>38.93999862670898</v>
+      </c>
+      <c r="H753" t="n">
+        <v>38.93999862670898</v>
+      </c>
+      <c r="I753" t="n">
+        <v>40.97999954223633</v>
+      </c>
+      <c r="J753" t="n">
+        <v>38.93999862670898</v>
+      </c>
+      <c r="K753" t="n">
+        <v>62294</v>
+      </c>
+      <c r="L753" t="n">
+        <v>-4.98</v>
+      </c>
+      <c r="M753" t="inlineStr">
+        <is>
+          <t>CALSOFT Stock Price and Chart — NSE:CALSOFT - TradingView</t>
+        </is>
+      </c>
+      <c r="N753" t="inlineStr">
+        <is>
+          <t>California Software profit rises to ₹411.64 lakh in Q1FY27 - scanx.trade</t>
+        </is>
+      </c>
+      <c r="O753" t="inlineStr">
+        <is>
+          <t>California Software profit rises to ₹411.64 lakh in Q1FY27 - scanx.trade</t>
+        </is>
+      </c>
+      <c r="P753" t="inlineStr">
+        <is>
+          <t>GRMN Q2 2026 Earnings: EPS Blowout Beats Estimates by 22.72%, Yet Shares Slip 1.61% - Pre-Earnings Setup - vinanet.vn</t>
+        </is>
+      </c>
+      <c r="Q753" t="inlineStr"/>
+    </row>
+    <row r="754">
+      <c r="A754" t="inlineStr">
+        <is>
+          <t>2026-09-07 12:56:35 IST</t>
+        </is>
+      </c>
+      <c r="B754" t="n">
+        <v>13</v>
+      </c>
+      <c r="C754" t="inlineStr">
+        <is>
+          <t>SUPTANERY.NS</t>
+        </is>
+      </c>
+      <c r="D754" t="inlineStr">
+        <is>
+          <t>Super Tannery Limited</t>
+        </is>
+      </c>
+      <c r="E754" t="n">
+        <v>12.59000015258789</v>
+      </c>
+      <c r="F754" t="n">
+        <v>12.59000015258789</v>
+      </c>
+      <c r="G754" t="n">
+        <v>12.59000015258789</v>
+      </c>
+      <c r="H754" t="n">
+        <v>12.59000015258789</v>
+      </c>
+      <c r="I754" t="n">
+        <v>13.25</v>
+      </c>
+      <c r="J754" t="n">
+        <v>12.59000015258789</v>
+      </c>
+      <c r="K754" t="n">
+        <v>38042</v>
+      </c>
+      <c r="L754" t="n">
+        <v>-4.98</v>
+      </c>
+      <c r="M754" t="inlineStr">
+        <is>
+          <t>SUPTANERY Stock Price and Chart — NSE:SUPTANERY - TradingView</t>
+        </is>
+      </c>
+      <c r="N754" t="inlineStr">
+        <is>
+          <t>Super Tannery Ltd. (SUPTANERY) Profile, Company FAQs &amp; Facts, Industry, Sector, Employee Strength - Stocktwits</t>
+        </is>
+      </c>
+      <c r="O754" t="inlineStr">
+        <is>
+          <t>SUPTANERY Historical Data - equitypandit.com</t>
+        </is>
+      </c>
+      <c r="P754" t="inlineStr">
+        <is>
+          <t>Super Tannery Ltd. (SUPTANERY) Profile, Company FAQs &amp; Facts, Industry, Sector, Employee Strength - Stocktwits</t>
+        </is>
+      </c>
+      <c r="Q754" t="inlineStr">
+        <is>
+          <t>Super Tannery Ltd. (SUPTANERY) Fundamental and Financial Data - Stocktwits</t>
+        </is>
+      </c>
+    </row>
+    <row r="755">
+      <c r="A755" t="inlineStr">
+        <is>
+          <t>2026-09-07 12:56:35 IST</t>
+        </is>
+      </c>
+      <c r="B755" t="n">
+        <v>14</v>
+      </c>
+      <c r="C755" t="inlineStr">
+        <is>
+          <t>BURNPUR.NS</t>
+        </is>
+      </c>
+      <c r="D755" t="inlineStr">
+        <is>
+          <t>Burnpur Cement Limited</t>
+        </is>
+      </c>
+      <c r="E755" t="n">
+        <v>22.6299991607666</v>
+      </c>
+      <c r="F755" t="n">
+        <v>22.6299991607666</v>
+      </c>
+      <c r="G755" t="n">
+        <v>20.48999977111816</v>
+      </c>
+      <c r="H755" t="n">
+        <v>20.48999977111816</v>
+      </c>
+      <c r="I755" t="n">
+        <v>21.55999946594238</v>
+      </c>
+      <c r="J755" t="n">
+        <v>20.48999977111816</v>
+      </c>
+      <c r="K755" t="n">
+        <v>371470</v>
+      </c>
+      <c r="L755" t="n">
+        <v>-4.96</v>
+      </c>
+      <c r="M755" t="inlineStr">
+        <is>
+          <t>Burnpur Cement dispatches web links for 40th AGM and FY26 annual report - scanx.trade</t>
+        </is>
+      </c>
+      <c r="N755" t="inlineStr">
+        <is>
+          <t>Price Band Hitters on September 7, 2026 at 12:00 PM - HDFC Sky</t>
+        </is>
+      </c>
+      <c r="O755" t="inlineStr">
+        <is>
+          <t>Burnpur Cement Share Price - Upstox</t>
+        </is>
+      </c>
+      <c r="P755" t="inlineStr">
+        <is>
+          <t>Burnpur Cement Ltd Locks at Upper Circuit With 4.96% Gain — Buyers Queue, Sellers Absent - MarketsMojo</t>
+        </is>
+      </c>
+      <c r="Q755" t="inlineStr">
+        <is>
+          <t>Burnpur Cement FY26 Results: Net loss widens 87% to ₹792 crore - scanx.trade</t>
+        </is>
+      </c>
+    </row>
+    <row r="756">
+      <c r="A756" t="inlineStr">
+        <is>
+          <t>2026-09-07 12:56:35 IST</t>
+        </is>
+      </c>
+      <c r="B756" t="n">
+        <v>15</v>
+      </c>
+      <c r="C756" t="inlineStr">
+        <is>
+          <t>ELITECON.NS</t>
+        </is>
+      </c>
+      <c r="D756" t="inlineStr">
+        <is>
+          <t>Elitecon International Limited</t>
+        </is>
+      </c>
+      <c r="E756" t="n">
+        <v>8.25</v>
+      </c>
+      <c r="F756" t="n">
+        <v>8.909999847412109</v>
+      </c>
+      <c r="G756" t="n">
+        <v>8.25</v>
+      </c>
+      <c r="H756" t="n">
+        <v>8.25</v>
+      </c>
+      <c r="I756" t="n">
+        <v>8.680000305175781</v>
+      </c>
+      <c r="J756" t="n">
+        <v>8.25</v>
+      </c>
+      <c r="K756" t="n">
+        <v>3864394</v>
+      </c>
+      <c r="L756" t="n">
+        <v>-4.95</v>
+      </c>
+      <c r="M756" t="inlineStr">
+        <is>
+          <t>Elitecon International Fined ₹1.12 Lakh by BSE for Late Financial Results Submission - scanx.trade</t>
+        </is>
+      </c>
+      <c r="N756" t="inlineStr">
+        <is>
+          <t>Elitecon International Fined ₹1.12 Lakh by BSE for Late Financial Results Submission - scanx.trade</t>
+        </is>
+      </c>
+      <c r="O756" t="inlineStr">
+        <is>
+          <t>Elitecon International Ltd. Shareholding Pattern – Promoters, FIIs &amp; DIIs - Value Research</t>
+        </is>
+      </c>
+      <c r="P756" t="inlineStr">
+        <is>
+          <t>Small-cap stock under Rs.50 hits 5% upper circuit following stock market rebound - TradingView</t>
+        </is>
+      </c>
+      <c r="Q756" t="inlineStr">
+        <is>
+          <t>Elitecon International Declines 4.92% to ₹11.2: Support at ₹10.64 Holds Key - Jurik MA - siam.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="757">
+      <c r="A757" t="inlineStr">
+        <is>
+          <t>2026-09-07 12:56:35 IST</t>
+        </is>
+      </c>
+      <c r="B757" t="n">
+        <v>16</v>
+      </c>
+      <c r="C757" t="inlineStr">
+        <is>
+          <t>TIJARIA.NS</t>
+        </is>
+      </c>
+      <c r="D757" t="inlineStr">
+        <is>
+          <t>Tijaria Polypipes Limited</t>
+        </is>
+      </c>
+      <c r="E757" t="n">
+        <v>9.739999771118164</v>
+      </c>
+      <c r="F757" t="n">
+        <v>9.800000190734863</v>
+      </c>
+      <c r="G757" t="n">
+        <v>9.069999694824219</v>
+      </c>
+      <c r="H757" t="n">
+        <v>9.069999694824219</v>
+      </c>
+      <c r="I757" t="n">
+        <v>9.539999961853027</v>
+      </c>
+      <c r="J757" t="n">
+        <v>9.069999694824219</v>
+      </c>
+      <c r="K757" t="n">
+        <v>141636</v>
+      </c>
+      <c r="L757" t="n">
+        <v>-4.93</v>
+      </c>
+      <c r="M757" t="inlineStr">
+        <is>
+          <t>Tijaria Polypipes (NSE: TIJARIA) Gains Momentum - Kalkine India</t>
+        </is>
+      </c>
+      <c r="N757" t="inlineStr">
+        <is>
+          <t>Tijaria Polypipes Ltd Locks at Upper Circuit With 4.95% Gain — Buyers Queue, Sellers Absent - MarketsMojo</t>
+        </is>
+      </c>
+      <c r="O757" t="inlineStr">
+        <is>
+          <t>Tijaria Polypipes Ltd Locks at Upper Circuit With 4.95% Gain — Buyers Queue, Sellers Absent - MarketsMojo</t>
+        </is>
+      </c>
+      <c r="P757" t="inlineStr">
+        <is>
+          <t>Tijaria Polypipes (NSE: TIJARIA) Sees Sharp Upmove - Kalkine India</t>
+        </is>
+      </c>
+      <c r="Q757" t="inlineStr">
+        <is>
+          <t>Tijaria Polypipes posts ₹36.11 crore loss in Q1FY27 as revenue remains zero - scanx.trade</t>
+        </is>
+      </c>
+    </row>
+    <row r="758">
+      <c r="A758" t="inlineStr">
+        <is>
+          <t>2026-09-07 12:56:35 IST</t>
+        </is>
+      </c>
+      <c r="B758" t="n">
+        <v>17</v>
+      </c>
+      <c r="C758" t="inlineStr">
+        <is>
+          <t>EASTSILK.NS</t>
+        </is>
+      </c>
+      <c r="D758" t="inlineStr">
+        <is>
+          <t>Eastern Silk Industries Limited</t>
+        </is>
+      </c>
+      <c r="E758" t="n">
+        <v>60.79999923706055</v>
+      </c>
+      <c r="F758" t="n">
+        <v>60.79999923706055</v>
+      </c>
+      <c r="G758" t="n">
+        <v>58.02000045776367</v>
+      </c>
+      <c r="H758" t="n">
+        <v>58.04000091552734</v>
+      </c>
+      <c r="I758" t="n">
+        <v>61</v>
+      </c>
+      <c r="J758" t="n">
+        <v>58.04000091552734</v>
+      </c>
+      <c r="K758" t="n">
+        <v>330</v>
+      </c>
+      <c r="L758" t="n">
+        <v>-4.85</v>
+      </c>
+      <c r="M758" t="inlineStr">
+        <is>
+          <t>Eastern Silk Industries Limited Schedules Board Meeting on May 27, 2026 to Approve FY26 Audited Financial Results - scanx.trade</t>
+        </is>
+      </c>
+      <c r="N758" t="inlineStr">
+        <is>
+          <t>EASTSILK Q2 2026 Earnings: Revenue Grows 8.48% to ₹23.71 Crore, but EPS Loss of ₹27.2 Dents Sentiment - siam.in</t>
+        </is>
+      </c>
+      <c r="O758" t="inlineStr">
+        <is>
+          <t>EASTSILK Q2 2026 Earnings: Revenue Grows 8.48% to ₹23.71 Crore, but EPS Loss of ₹27.2 Dents Sentiment - siam.in</t>
+        </is>
+      </c>
+      <c r="P758" t="inlineStr">
+        <is>
+          <t>Eastern Silk Industries Trades Flat Near ₹50.5; Key Support and Resistance Levels in Focus - Beta Neutral Pair - vinanet.vn</t>
+        </is>
+      </c>
+      <c r="Q758" t="inlineStr">
+        <is>
+          <t>Eastern Silk Industries Limited Announces Q3 FY26 Financial Results - scanx.trade</t>
+        </is>
+      </c>
+    </row>
+    <row r="759">
+      <c r="A759" t="inlineStr">
+        <is>
+          <t>2026-09-07 12:56:35 IST</t>
+        </is>
+      </c>
+      <c r="B759" t="n">
+        <v>18</v>
+      </c>
+      <c r="C759" t="inlineStr">
+        <is>
+          <t>PIONRINV.NS</t>
+        </is>
+      </c>
+      <c r="D759" t="inlineStr">
+        <is>
+          <t>Pioneer Investcorp Limited</t>
+        </is>
+      </c>
+      <c r="E759" t="n">
+        <v>79.75</v>
+      </c>
+      <c r="F759" t="n">
+        <v>79.84999847412109</v>
+      </c>
+      <c r="G759" t="n">
+        <v>79.75</v>
+      </c>
+      <c r="H759" t="n">
+        <v>79.84999847412109</v>
+      </c>
+      <c r="I759" t="n">
+        <v>83.88999938964844</v>
+      </c>
+      <c r="J759" t="n">
+        <v>79.84999847412109</v>
+      </c>
+      <c r="K759" t="n">
+        <v>1426</v>
+      </c>
+      <c r="L759" t="n">
+        <v>-4.82</v>
+      </c>
+      <c r="M759" t="inlineStr">
+        <is>
+          <t>Pioneer Investcorp Limited (PIONRINV.NS) Mar 2026 Earnings: EPS of ₹2.18 Reported Amid Modest Revenue; Stock Declines 3.55% - Revenue Growth Report - vinanet.vn</t>
+        </is>
+      </c>
+      <c r="N759" t="inlineStr">
+        <is>
+          <t>Pioneer Investcorp Limited (PIONRINV.NS) Mar 2026 Earnings: EPS of ₹2.18 Reported Amid Modest Revenue; Stock Declines 3.55% - Revenue Growth Report - vinanet.vn</t>
+        </is>
+      </c>
+      <c r="O759" t="inlineStr">
+        <is>
+          <t>Technical Analysis of Pioneer Investcorp Limited (NSE:PIONRINV) - TradingView</t>
+        </is>
+      </c>
+      <c r="P759" t="inlineStr">
+        <is>
+          <t>Pioneer Investcorp (PIONRINV.NS) Slips 3.26%: Support at ₹85.5 in Focus - Momentum Surge Alerts - vinanet.vn</t>
+        </is>
+      </c>
+      <c r="Q759" t="inlineStr">
+        <is>
+          <t>Pioneer Investcorp Limited (PIONRINV.NS) Mar 2026 Earnings: Net Profit Scales Higher – EPS of ₹2.18; Revenue at ₹1.9 Crore - Performance Review - vinanet.vn</t>
+        </is>
+      </c>
+    </row>
+    <row r="760">
+      <c r="A760" t="inlineStr">
+        <is>
+          <t>2026-09-07 12:56:35 IST</t>
+        </is>
+      </c>
+      <c r="B760" t="n">
+        <v>19</v>
+      </c>
+      <c r="C760" t="inlineStr">
+        <is>
+          <t>DIVGIITTS.NS</t>
+        </is>
+      </c>
+      <c r="D760" t="inlineStr">
+        <is>
+          <t>Divgi Torqtransfer Systems Limited</t>
+        </is>
+      </c>
+      <c r="E760" t="n">
+        <v>1242</v>
+      </c>
+      <c r="F760" t="n">
+        <v>1285.199951171875</v>
+      </c>
+      <c r="G760" t="n">
+        <v>1155.199951171875</v>
+      </c>
+      <c r="H760" t="n">
+        <v>1176.5</v>
+      </c>
+      <c r="I760" t="n">
+        <v>1235.800048828125</v>
+      </c>
+      <c r="J760" t="n">
+        <v>1176.5</v>
+      </c>
+      <c r="K760" t="n">
+        <v>167874</v>
+      </c>
+      <c r="L760" t="n">
+        <v>-4.8</v>
+      </c>
+      <c r="M760" t="inlineStr">
+        <is>
+          <t>Divgi (DIVGIITTS.NS) Session: Finishes 2.96% Down at ₹1,226.05; Level Watch: the Supplied Trading Band Runs From ₹1,164.75 to ₹1,287.35 in Latest Trading - Momentum Trade - siam.in</t>
+        </is>
+      </c>
+      <c r="N760" t="inlineStr">
+        <is>
+          <t>Divgi TorqTransfer Systems to Meet Investors in Non-Deal Roadshow - TipRanks</t>
+        </is>
+      </c>
+      <c r="O760" t="inlineStr">
+        <is>
+          <t>Divgi Torqtransfer Slips 0.99% to ₹1219.75: Key Support and Resistance Levels in Focus - Sector Leader Stocks - siam.in</t>
+        </is>
+      </c>
+      <c r="P760" t="inlineStr">
+        <is>
+          <t>Divgi Torqtransfer Systems Share Price Hits One-Year High - Univest</t>
+        </is>
+      </c>
+      <c r="Q760" t="inlineStr">
+        <is>
+          <t>Divgi TorqTransfer Stock Surges 13% As Q1 FY27 PAT Jumps 183% To ₹25.2 Cr - Trade Brains</t>
+        </is>
+      </c>
+    </row>
+    <row r="761">
+      <c r="A761" t="inlineStr">
+        <is>
+          <t>2026-09-07 12:56:35 IST</t>
+        </is>
+      </c>
+      <c r="B761" t="n">
+        <v>20</v>
+      </c>
+      <c r="C761" t="inlineStr">
+        <is>
+          <t>BETA.NS</t>
+        </is>
+      </c>
+      <c r="D761" t="inlineStr">
+        <is>
+          <t>Beta Drugs Limited</t>
+        </is>
+      </c>
+      <c r="E761" t="n">
+        <v>2204</v>
+      </c>
+      <c r="F761" t="n">
+        <v>2204</v>
+      </c>
+      <c r="G761" t="n">
+        <v>2087.89990234375</v>
+      </c>
+      <c r="H761" t="n">
+        <v>2114.60009765625</v>
+      </c>
+      <c r="I761" t="n">
+        <v>2218.5</v>
+      </c>
+      <c r="J761" t="n">
+        <v>2114.60009765625</v>
+      </c>
+      <c r="K761" t="n">
+        <v>34067</v>
+      </c>
+      <c r="L761" t="n">
+        <v>-4.68</v>
+      </c>
+      <c r="M761" t="inlineStr">
+        <is>
+          <t>Beta bionics CEO Sean Saint sells $113,258 in company stock - Investing.com India</t>
+        </is>
+      </c>
+      <c r="N761" t="inlineStr">
+        <is>
+          <t>Beta Technologies terminates security control agreement with US Defense Department - scanx.trade</t>
+        </is>
+      </c>
+      <c r="O761" t="inlineStr">
+        <is>
+          <t>Beta Technologies terminates security control agreement with US Defense Department - scanx.trade</t>
+        </is>
+      </c>
+      <c r="P761" t="inlineStr">
+        <is>
+          <t>What Is the Beta of a Stock? Meaning &amp; Formula - Britannica</t>
+        </is>
+      </c>
+      <c r="Q761" t="inlineStr">
+        <is>
+          <t>Independent Director of BETA Technologies Picks Up 1.5% More Stock - simplywall.st</t>
         </is>
       </c>
     </row>
